--- a/youzi/正经哥/index.xlsx
+++ b/youzi/正经哥/index.xlsx
@@ -45,49 +45,979 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0ABB1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF36AC51"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1D7E35"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,7 +1029,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,25 +1221,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,24 +1407,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -171,25 +1419,727 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,19 +2151,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1A702F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,61 +2181,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,25 +2235,439 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEBF6ED"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBF8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,37 +2691,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -393,601 +2739,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -999,7 +2763,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1011,1855 +2871,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7FBF8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2871,43 +2907,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDE4654"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8058,7 +8058,7 @@
       <c r="C2" t="str">
         <v>000665</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -2301.68万</v>
       </c>
       <c r="E2">
@@ -8073,40 +8073,40 @@
       <c r="H2">
         <v>10.06</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="7">
         <v>0</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="4">
         <v>10</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="1">
         <v>21.03</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="12">
         <v>30</v>
       </c>
       <c r="M2" s="8">
         <v>18.79</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="9">
         <v>10</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="5">
         <v>11.72</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="13">
         <v>10.17</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="2">
         <v>2.07</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="10">
         <v>-4.66</v>
       </c>
       <c r="S2" s="6">
         <v>-8.45</v>
       </c>
-      <c r="T2" s="7">
+      <c r="T2" s="3">
         <v>-18.1</v>
       </c>
     </row>
@@ -8135,40 +8135,40 @@
       <c r="H3">
         <v>9.95</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="18">
         <v>0</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="14">
         <v>10.06</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="19">
         <v>21.12</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="20">
         <v>9.77</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="24">
         <v>-1.15</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="15">
         <v>-8.76</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="23">
         <v>-11.35</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="21">
         <v>-12.36</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="22">
         <v>-13.22</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="25">
         <v>-21.84</v>
       </c>
-      <c r="S3" s="19">
+      <c r="S3" s="26">
         <v>-23.99</v>
       </c>
-      <c r="T3" s="20">
+      <c r="T3" s="16">
         <v>36.06</v>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       <c r="C4" t="str">
         <v>002300</v>
       </c>
-      <c r="D4" s="33" t="str">
+      <c r="D4" s="30" t="str">
         <v>净卖: -2576.68万</v>
       </c>
       <c r="E4">
@@ -8197,40 +8197,40 @@
       <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="31">
         <v>9.34</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="37">
         <v>-0.91</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="27">
         <v>-10.77</v>
       </c>
-      <c r="L4" s="37">
+      <c r="L4" s="38">
         <v>-17.64</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="39">
         <v>-19.97</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="32">
         <v>-20.88</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="33">
         <v>-21.66</v>
       </c>
       <c r="P4" s="34">
         <v>-29.44</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="28">
         <v>-31.39</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="29">
         <v>-28.92</v>
       </c>
-      <c r="S4" s="39">
+      <c r="S4" s="35">
         <v>-27.63</v>
       </c>
-      <c r="T4" s="35">
+      <c r="T4" s="36">
         <v>22.83</v>
       </c>
     </row>
@@ -8259,40 +8259,40 @@
       <c r="H5">
         <v>9.93</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="48">
         <v>0</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="46">
         <v>9.95</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="51">
         <v>20.98</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="49">
         <v>30.17</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="50">
         <v>17.15</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="52">
         <v>8.58</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="40">
         <v>10.57</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="41">
         <v>-0.46</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="42">
         <v>-5.36</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="44">
         <v>-5.05</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="43">
         <v>-4.29</v>
       </c>
-      <c r="T5" s="40">
+      <c r="T5" s="47">
         <v>-10.11</v>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="53" t="str">
         <v>净卖: -7396.08万</v>
       </c>
       <c r="E6">
@@ -8321,40 +8321,40 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="54">
         <v>7.59</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="55">
         <v>-3.16</v>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="56">
         <v>-10.25</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="60">
         <v>-8.61</v>
       </c>
-      <c r="M6" s="61">
+      <c r="M6" s="57">
         <v>-17.72</v>
       </c>
-      <c r="N6" s="53">
+      <c r="N6" s="63">
         <v>-21.77</v>
       </c>
-      <c r="O6" s="56">
+      <c r="O6" s="61">
         <v>-21.52</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="58">
         <v>-20.89</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="59">
         <v>-16.71</v>
       </c>
       <c r="R6" s="62">
         <v>-20.76</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="64">
         <v>-17.09</v>
       </c>
-      <c r="T6" s="58">
+      <c r="T6" s="65">
         <v>-25.7</v>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       <c r="C7" t="str">
         <v>600697</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="71" t="str">
         <v>净卖: -2819.93万</v>
       </c>
       <c r="E7">
@@ -8383,40 +8383,40 @@
       <c r="H7">
         <v>-9.28</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="72">
         <v>3.2</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="73">
         <v>6.95</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="78">
         <v>17.66</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="66">
         <v>13.12</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="74">
         <v>1.95</v>
       </c>
-      <c r="N7" s="78">
+      <c r="N7" s="67">
         <v>0</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="76">
         <v>4.3</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="68">
         <v>-1.72</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="77">
         <v>-5.31</v>
       </c>
-      <c r="R7" s="68">
+      <c r="R7" s="75">
         <v>-5.23</v>
       </c>
       <c r="S7" s="69">
         <v>-7.97</v>
       </c>
-      <c r="T7" s="72">
+      <c r="T7" s="70">
         <v>-8.2</v>
       </c>
     </row>
@@ -8430,7 +8430,7 @@
       <c r="C8" t="str">
         <v>600828</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="84" t="str">
         <v>净买: 1425.83万</v>
       </c>
       <c r="E8">
@@ -8445,40 +8445,40 @@
       <c r="H8">
         <v>10.11</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="85">
         <v>0</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="89">
         <v>10.02</v>
       </c>
-      <c r="K8" s="89">
+      <c r="K8" s="90">
         <v>7.31</v>
       </c>
-      <c r="L8" s="90">
+      <c r="L8" s="86">
         <v>5.01</v>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="91">
         <v>10.65</v>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="82">
         <v>5.43</v>
       </c>
-      <c r="O8" s="81">
+      <c r="O8" s="87">
         <v>-5.01</v>
       </c>
-      <c r="P8" s="91">
+      <c r="P8" s="79">
         <v>-10.02</v>
       </c>
-      <c r="Q8" s="79">
+      <c r="Q8" s="81">
         <v>-12.73</v>
       </c>
-      <c r="R8" s="86">
+      <c r="R8" s="80">
         <v>-11.69</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="88">
         <v>-10.65</v>
       </c>
-      <c r="T8" s="82">
+      <c r="T8" s="83">
         <v>10.23</v>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       <c r="C9" t="str">
         <v>600828</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="101" t="str">
         <v>净卖: -1514.63万</v>
       </c>
       <c r="E9">
@@ -8507,40 +8507,40 @@
       <c r="H9">
         <v>-0.21</v>
       </c>
-      <c r="I9" s="103">
+      <c r="I9" s="98">
         <v>10.25</v>
       </c>
-      <c r="J9" s="104">
+      <c r="J9" s="96">
         <v>7.53</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="99">
         <v>5.23</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="102">
         <v>10.88</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="103">
         <v>5.65</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="97">
         <v>-4.81</v>
       </c>
-      <c r="O9" s="99">
+      <c r="O9" s="104">
         <v>-9.83</v>
       </c>
-      <c r="P9" s="100">
+      <c r="P9" s="92">
         <v>-12.55</v>
       </c>
-      <c r="Q9" s="94">
+      <c r="Q9" s="93">
         <v>-11.51</v>
       </c>
-      <c r="R9" s="93">
+      <c r="R9" s="94">
         <v>-10.46</v>
       </c>
       <c r="S9" s="95">
         <v>-12.34</v>
       </c>
-      <c r="T9" s="102">
+      <c r="T9" s="100">
         <v>10.46</v>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       <c r="C10" t="str">
         <v>002909</v>
       </c>
-      <c r="D10" s="115" t="str">
+      <c r="D10" s="109" t="str">
         <v>净卖: -879.53万</v>
       </c>
       <c r="E10">
@@ -8569,40 +8569,40 @@
       <c r="H10">
         <v>-1.91</v>
       </c>
-      <c r="I10" s="109">
+      <c r="I10" s="115">
         <v>-8.28</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="116">
         <v>-16.44</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="110">
         <v>-21.07</v>
       </c>
       <c r="L10" s="117">
         <v>-21.8</v>
       </c>
-      <c r="M10" s="105">
+      <c r="M10" s="106">
         <v>-23.39</v>
       </c>
-      <c r="N10" s="106">
+      <c r="N10" s="112">
         <v>-23.02</v>
       </c>
       <c r="O10" s="107">
         <v>-22.66</v>
       </c>
-      <c r="P10" s="108">
+      <c r="P10" s="111">
         <v>-23.87</v>
       </c>
       <c r="Q10" s="113">
         <v>-23.26</v>
       </c>
-      <c r="R10" s="110">
+      <c r="R10" s="114">
         <v>-24.12</v>
       </c>
-      <c r="S10" s="111">
+      <c r="S10" s="108">
         <v>-23.87</v>
       </c>
-      <c r="T10" s="114">
+      <c r="T10" s="105">
         <v>-22.41</v>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
       <c r="C11" t="str">
         <v>603639</v>
       </c>
-      <c r="D11" s="130" t="str">
+      <c r="D11" s="118" t="str">
         <v>净买: 1633.37万</v>
       </c>
       <c r="E11">
@@ -8631,40 +8631,40 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="125">
+      <c r="I11" s="124">
         <v>0</v>
       </c>
-      <c r="J11" s="123">
+      <c r="J11" s="125">
         <v>-6.63</v>
       </c>
-      <c r="K11" s="127">
+      <c r="K11" s="126">
         <v>-12.9</v>
       </c>
-      <c r="L11" s="118">
+      <c r="L11" s="128">
         <v>-12.16</v>
       </c>
       <c r="M11" s="119">
         <v>-13.76</v>
       </c>
-      <c r="N11" s="128">
+      <c r="N11" s="120">
         <v>-9.83</v>
       </c>
-      <c r="O11" s="120">
+      <c r="O11" s="121">
         <v>-10.63</v>
       </c>
-      <c r="P11" s="121">
+      <c r="P11" s="129">
         <v>-9.46</v>
       </c>
-      <c r="Q11" s="124">
+      <c r="Q11" s="123">
         <v>-10.44</v>
       </c>
-      <c r="R11" s="126">
+      <c r="R11" s="127">
         <v>-10.01</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="122">
         <v>-8.17</v>
       </c>
-      <c r="T11" s="122">
+      <c r="T11" s="130">
         <v>-18.92</v>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       <c r="C12" t="str">
         <v>002235</v>
       </c>
-      <c r="D12" s="131" t="str">
+      <c r="D12" s="140" t="str">
         <v>净买: 1768.35万</v>
       </c>
       <c r="E12">
@@ -8693,40 +8693,40 @@
       <c r="H12">
         <v>10.05</v>
       </c>
-      <c r="I12" s="142">
+      <c r="I12" s="138">
         <v>0</v>
       </c>
-      <c r="J12" s="140">
+      <c r="J12" s="134">
         <v>3.19</v>
       </c>
       <c r="K12" s="143">
         <v>6.23</v>
       </c>
-      <c r="L12" s="132">
+      <c r="L12" s="131">
         <v>16.81</v>
       </c>
-      <c r="M12" s="133">
+      <c r="M12" s="141">
         <v>18.99</v>
       </c>
-      <c r="N12" s="141">
+      <c r="N12" s="135">
         <v>30.87</v>
       </c>
-      <c r="O12" s="134">
+      <c r="O12" s="139">
         <v>43.91</v>
       </c>
-      <c r="P12" s="135">
+      <c r="P12" s="132">
         <v>42.17</v>
       </c>
       <c r="Q12" s="136">
         <v>36.52</v>
       </c>
-      <c r="R12" s="138">
+      <c r="R12" s="137">
         <v>43.48</v>
       </c>
-      <c r="S12" s="139">
+      <c r="S12" s="133">
         <v>44.93</v>
       </c>
-      <c r="T12" s="137">
+      <c r="T12" s="142">
         <v>37.1</v>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       <c r="C13" t="str">
         <v>603776</v>
       </c>
-      <c r="D13" s="150" t="str">
+      <c r="D13" s="144" t="str">
         <v>净买: 1894.22万</v>
       </c>
       <c r="E13">
@@ -8755,40 +8755,40 @@
       <c r="H13">
         <v>10</v>
       </c>
-      <c r="I13" s="151">
+      <c r="I13" s="147">
         <v>0</v>
       </c>
-      <c r="J13" s="152">
+      <c r="J13" s="155">
         <v>-9.72</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="145">
         <v>-10.95</v>
       </c>
-      <c r="L13" s="154">
+      <c r="L13" s="150">
         <v>-8.45</v>
       </c>
-      <c r="M13" s="147">
+      <c r="M13" s="151">
         <v>-7.04</v>
       </c>
-      <c r="N13" s="153">
+      <c r="N13" s="146">
         <v>-11.27</v>
       </c>
-      <c r="O13" s="155">
+      <c r="O13" s="152">
         <v>-2.41</v>
       </c>
       <c r="P13" s="148">
         <v>2.36</v>
       </c>
-      <c r="Q13" s="149">
+      <c r="Q13" s="153">
         <v>-2.64</v>
       </c>
-      <c r="R13" s="144">
+      <c r="R13" s="156">
         <v>-2.32</v>
       </c>
-      <c r="S13" s="156">
+      <c r="S13" s="154">
         <v>-2.23</v>
       </c>
-      <c r="T13" s="145">
+      <c r="T13" s="149">
         <v>-8.86</v>
       </c>
     </row>
@@ -8802,7 +8802,7 @@
       <c r="C14" t="str">
         <v>603776</v>
       </c>
-      <c r="D14" s="163" t="str">
+      <c r="D14" s="160" t="str">
         <v>净卖: -2197.25万</v>
       </c>
       <c r="E14">
@@ -8817,40 +8817,40 @@
       <c r="H14">
         <v>-2.32</v>
       </c>
-      <c r="I14" s="158">
+      <c r="I14" s="157">
         <v>-7.58</v>
       </c>
-      <c r="J14" s="166">
+      <c r="J14" s="161">
         <v>-8.84</v>
       </c>
-      <c r="K14" s="168">
+      <c r="K14" s="162">
         <v>-6.28</v>
       </c>
-      <c r="L14" s="159">
+      <c r="L14" s="158">
         <v>-4.84</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="159">
         <v>-9.16</v>
       </c>
-      <c r="N14" s="169">
+      <c r="N14" s="167">
         <v>-0.09</v>
       </c>
-      <c r="O14" s="164">
+      <c r="O14" s="163">
         <v>4.79</v>
       </c>
-      <c r="P14" s="157">
+      <c r="P14" s="164">
         <v>-0.33</v>
       </c>
-      <c r="Q14" s="161">
+      <c r="Q14" s="165">
         <v>0</v>
       </c>
-      <c r="R14" s="165">
+      <c r="R14" s="168">
         <v>0.09</v>
       </c>
-      <c r="S14" s="167">
+      <c r="S14" s="169">
         <v>0</v>
       </c>
-      <c r="T14" s="162">
+      <c r="T14" s="166">
         <v>-6.7</v>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       <c r="C15" t="str">
         <v>001360</v>
       </c>
-      <c r="D15" s="174" t="str">
+      <c r="D15" s="177" t="str">
         <v>净买: 1803.24万</v>
       </c>
       <c r="E15">
@@ -8879,40 +8879,40 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="175">
+      <c r="I15" s="171">
         <v>0</v>
       </c>
-      <c r="J15" s="176">
+      <c r="J15" s="172">
         <v>10.01</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="175">
         <v>-0.95</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="182">
         <v>-10.85</v>
       </c>
-      <c r="M15" s="181">
+      <c r="M15" s="178">
         <v>-13.18</v>
       </c>
-      <c r="N15" s="178">
+      <c r="N15" s="170">
         <v>-14.29</v>
       </c>
-      <c r="O15" s="170">
+      <c r="O15" s="179">
         <v>-15.25</v>
       </c>
-      <c r="P15" s="179">
+      <c r="P15" s="180">
         <v>-14.56</v>
       </c>
-      <c r="Q15" s="173">
+      <c r="Q15" s="176">
         <v>-16.52</v>
       </c>
-      <c r="R15" s="180">
+      <c r="R15" s="181">
         <v>-16.36</v>
       </c>
-      <c r="S15" s="171">
+      <c r="S15" s="173">
         <v>-16.15</v>
       </c>
-      <c r="T15" s="182">
+      <c r="T15" s="174">
         <v>15.83</v>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       <c r="C16" t="str">
         <v>601669</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="192" t="str">
         <v>净买: 9396.35万</v>
       </c>
       <c r="E16">
@@ -8941,40 +8941,40 @@
       <c r="H16">
         <v>10.08</v>
       </c>
-      <c r="I16" s="185">
+      <c r="I16" s="184">
         <v>0</v>
       </c>
-      <c r="J16" s="186">
+      <c r="J16" s="193">
         <v>10.04</v>
       </c>
-      <c r="K16" s="191">
+      <c r="K16" s="185">
         <v>6.65</v>
       </c>
-      <c r="L16" s="187">
+      <c r="L16" s="194">
         <v>3.84</v>
       </c>
-      <c r="M16" s="194">
+      <c r="M16" s="186">
         <v>5.76</v>
       </c>
-      <c r="N16" s="195">
+      <c r="N16" s="183">
         <v>0.44</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="189">
         <v>0.89</v>
       </c>
-      <c r="P16" s="192">
+      <c r="P16" s="190">
         <v>-3.69</v>
       </c>
-      <c r="Q16" s="193">
+      <c r="Q16" s="191">
         <v>-4.58</v>
       </c>
-      <c r="R16" s="183">
+      <c r="R16" s="195">
         <v>-5.17</v>
       </c>
-      <c r="S16" s="184">
+      <c r="S16" s="187">
         <v>-6.5</v>
       </c>
-      <c r="T16" s="189">
+      <c r="T16" s="188">
         <v>-15.66</v>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
       <c r="C17" t="str">
         <v>001360</v>
       </c>
-      <c r="D17" s="201" t="str">
+      <c r="D17" s="197" t="str">
         <v>净卖: -1800.16万</v>
       </c>
       <c r="E17">
@@ -9003,40 +9003,40 @@
       <c r="H17">
         <v>0.1</v>
       </c>
-      <c r="I17" s="200">
+      <c r="I17" s="198">
         <v>-10.05</v>
       </c>
-      <c r="J17" s="202">
+      <c r="J17" s="204">
         <v>-19.04</v>
       </c>
-      <c r="K17" s="205">
+      <c r="K17" s="199">
         <v>-21.15</v>
       </c>
-      <c r="L17" s="203">
+      <c r="L17" s="205">
         <v>-22.16</v>
       </c>
-      <c r="M17" s="197">
+      <c r="M17" s="207">
         <v>-23.03</v>
       </c>
       <c r="N17" s="206">
         <v>-22.4</v>
       </c>
-      <c r="O17" s="207">
+      <c r="O17" s="208">
         <v>-24.18</v>
       </c>
-      <c r="P17" s="198">
+      <c r="P17" s="200">
         <v>-24.04</v>
       </c>
-      <c r="Q17" s="204">
+      <c r="Q17" s="196">
         <v>-23.85</v>
       </c>
-      <c r="R17" s="199">
+      <c r="R17" s="202">
         <v>-24.28</v>
       </c>
-      <c r="S17" s="208">
+      <c r="S17" s="203">
         <v>-24.47</v>
       </c>
-      <c r="T17" s="196">
+      <c r="T17" s="201">
         <v>5.19</v>
       </c>
     </row>
@@ -9050,7 +9050,7 @@
       <c r="C18" t="str">
         <v>001360</v>
       </c>
-      <c r="D18" s="219" t="str">
+      <c r="D18" s="216" t="str">
         <v>净卖: -1799.99万</v>
       </c>
       <c r="E18">
@@ -9065,40 +9065,40 @@
       <c r="H18">
         <v>-9.14</v>
       </c>
-      <c r="I18" s="215">
+      <c r="I18" s="217">
         <v>-0.94</v>
       </c>
-      <c r="J18" s="220">
+      <c r="J18" s="210">
         <v>-3.53</v>
       </c>
-      <c r="K18" s="221">
+      <c r="K18" s="218">
         <v>-4.76</v>
       </c>
-      <c r="L18" s="209">
+      <c r="L18" s="214">
         <v>-5.82</v>
       </c>
-      <c r="M18" s="216">
+      <c r="M18" s="212">
         <v>-5.06</v>
       </c>
-      <c r="N18" s="217">
+      <c r="N18" s="219">
         <v>-7.24</v>
       </c>
-      <c r="O18" s="213">
+      <c r="O18" s="220">
         <v>-7.06</v>
       </c>
-      <c r="P18" s="214">
+      <c r="P18" s="215">
         <v>-6.82</v>
       </c>
-      <c r="Q18" s="218">
+      <c r="Q18" s="221">
         <v>-7.35</v>
       </c>
-      <c r="R18" s="210">
+      <c r="R18" s="213">
         <v>-7.59</v>
       </c>
-      <c r="S18" s="211">
+      <c r="S18" s="209">
         <v>-6.59</v>
       </c>
-      <c r="T18" s="212">
+      <c r="T18" s="211">
         <v>28.71</v>
       </c>
     </row>
@@ -9112,7 +9112,7 @@
       <c r="C19" t="str">
         <v>300620</v>
       </c>
-      <c r="D19" s="223" t="str">
+      <c r="D19" s="228" t="str">
         <v>净买: 1215.21万</v>
       </c>
       <c r="E19">
@@ -9127,40 +9127,40 @@
       <c r="H19">
         <v>19.99</v>
       </c>
-      <c r="I19" s="230">
+      <c r="I19" s="229">
         <v>0</v>
       </c>
-      <c r="J19" s="233">
+      <c r="J19" s="230">
         <v>20.01</v>
       </c>
-      <c r="K19" s="231">
+      <c r="K19" s="222">
         <v>21.14</v>
       </c>
-      <c r="L19" s="234">
+      <c r="L19" s="233">
         <v>24.09</v>
       </c>
-      <c r="M19" s="228">
+      <c r="M19" s="223">
         <v>46.79</v>
       </c>
       <c r="N19" s="224">
         <v>50.73</v>
       </c>
-      <c r="O19" s="232">
+      <c r="O19" s="226">
         <v>40.57</v>
       </c>
-      <c r="P19" s="225">
+      <c r="P19" s="231">
         <v>31.96</v>
       </c>
-      <c r="Q19" s="226">
+      <c r="Q19" s="234">
         <v>34.41</v>
       </c>
-      <c r="R19" s="229">
+      <c r="R19" s="225">
         <v>39.6</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S19" s="232">
         <v>34.69</v>
       </c>
-      <c r="T19" s="222">
+      <c r="T19" s="227">
         <v>281.1</v>
       </c>
     </row>
@@ -9174,7 +9174,7 @@
       <c r="C20" t="str">
         <v>002177</v>
       </c>
-      <c r="D20" s="243" t="str">
+      <c r="D20" s="245" t="str">
         <v>净卖: -3762.63万</v>
       </c>
       <c r="E20">
@@ -9189,40 +9189,40 @@
       <c r="H20">
         <v>3.85</v>
       </c>
-      <c r="I20" s="244">
+      <c r="I20" s="247">
         <v>5.93</v>
       </c>
-      <c r="J20" s="240">
+      <c r="J20" s="242">
         <v>1.38</v>
       </c>
-      <c r="K20" s="241">
+      <c r="K20" s="237">
         <v>-1.17</v>
       </c>
-      <c r="L20" s="246">
+      <c r="L20" s="238">
         <v>-10.91</v>
       </c>
-      <c r="M20" s="242">
+      <c r="M20" s="239">
         <v>-11.76</v>
       </c>
-      <c r="N20" s="245">
+      <c r="N20" s="243">
         <v>-12.39</v>
       </c>
-      <c r="O20" s="247">
+      <c r="O20" s="246">
         <v>-9.96</v>
       </c>
-      <c r="P20" s="235">
+      <c r="P20" s="240">
         <v>-15.15</v>
       </c>
-      <c r="Q20" s="237">
+      <c r="Q20" s="235">
         <v>-17.9</v>
       </c>
-      <c r="R20" s="238">
+      <c r="R20" s="244">
         <v>-19.39</v>
       </c>
-      <c r="S20" s="239">
+      <c r="S20" s="236">
         <v>-18.11</v>
       </c>
-      <c r="T20" s="236">
+      <c r="T20" s="241">
         <v>-16.53</v>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       <c r="C21" t="str">
         <v>301517</v>
       </c>
-      <c r="D21" s="258" t="str">
+      <c r="D21" s="250" t="str">
         <v>净买: 1391.15万</v>
       </c>
       <c r="E21">
@@ -9251,40 +9251,40 @@
       <c r="H21">
         <v>20</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="256">
         <v>-14.18</v>
       </c>
-      <c r="J21" s="259">
+      <c r="J21" s="257">
         <v>-19.79</v>
       </c>
-      <c r="K21" s="249">
+      <c r="K21" s="248">
         <v>-18.67</v>
       </c>
-      <c r="L21" s="253">
+      <c r="L21" s="249">
         <v>-21.09</v>
       </c>
-      <c r="M21" s="260">
+      <c r="M21" s="251">
         <v>-22.21</v>
       </c>
-      <c r="N21" s="256">
+      <c r="N21" s="252">
         <v>-18.54</v>
       </c>
-      <c r="O21" s="254">
+      <c r="O21" s="258">
         <v>-22.58</v>
       </c>
-      <c r="P21" s="250">
+      <c r="P21" s="253">
         <v>-27.04</v>
       </c>
-      <c r="Q21" s="257">
+      <c r="Q21" s="254">
         <v>-25.09</v>
       </c>
-      <c r="R21" s="255">
+      <c r="R21" s="259">
         <v>-21.88</v>
       </c>
-      <c r="S21" s="251">
+      <c r="S21" s="260">
         <v>-25.85</v>
       </c>
-      <c r="T21" s="252">
+      <c r="T21" s="255">
         <v>19.65</v>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       <c r="C22" t="str">
         <v>002547</v>
       </c>
-      <c r="D22" s="269" t="str">
+      <c r="D22" s="262" t="str">
         <v>净买: 4862.70万</v>
       </c>
       <c r="E22">
@@ -9313,40 +9313,40 @@
       <c r="H22">
         <v>10.1</v>
       </c>
-      <c r="I22" s="270">
+      <c r="I22" s="268">
         <v>0</v>
       </c>
-      <c r="J22" s="261">
+      <c r="J22" s="269">
         <v>7.01</v>
       </c>
-      <c r="K22" s="266">
+      <c r="K22" s="264">
         <v>0.36</v>
       </c>
-      <c r="L22" s="262">
+      <c r="L22" s="270">
         <v>4.68</v>
       </c>
-      <c r="M22" s="263">
+      <c r="M22" s="271">
         <v>15.11</v>
       </c>
-      <c r="N22" s="271">
+      <c r="N22" s="272">
         <v>21.76</v>
       </c>
-      <c r="O22" s="264">
+      <c r="O22" s="265">
         <v>22.66</v>
       </c>
-      <c r="P22" s="267">
+      <c r="P22" s="273">
         <v>17.81</v>
       </c>
-      <c r="Q22" s="272">
+      <c r="Q22" s="266">
         <v>9.17</v>
       </c>
-      <c r="R22" s="265">
+      <c r="R22" s="267">
         <v>12.59</v>
       </c>
-      <c r="S22" s="268">
+      <c r="S22" s="261">
         <v>7.01</v>
       </c>
-      <c r="T22" s="273">
+      <c r="T22" s="263">
         <v>-38.13</v>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       <c r="C23" t="str">
         <v>002547</v>
       </c>
-      <c r="D23" s="275" t="str">
+      <c r="D23" s="283" t="str">
         <v>净卖: -5175.09万</v>
       </c>
       <c r="E23">
@@ -9375,40 +9375,40 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23" s="280">
+      <c r="I23" s="276">
         <v>7.01</v>
       </c>
-      <c r="J23" s="281">
+      <c r="J23" s="284">
         <v>0.36</v>
       </c>
       <c r="K23" s="277">
         <v>4.68</v>
       </c>
-      <c r="L23" s="282">
+      <c r="L23" s="278">
         <v>15.11</v>
       </c>
-      <c r="M23" s="283">
+      <c r="M23" s="285">
         <v>21.76</v>
       </c>
-      <c r="N23" s="276">
+      <c r="N23" s="286">
         <v>22.66</v>
       </c>
-      <c r="O23" s="278">
+      <c r="O23" s="279">
         <v>17.81</v>
       </c>
-      <c r="P23" s="284">
+      <c r="P23" s="280">
         <v>9.17</v>
       </c>
-      <c r="Q23" s="285">
+      <c r="Q23" s="274">
         <v>12.59</v>
       </c>
-      <c r="R23" s="286">
+      <c r="R23" s="275">
         <v>7.01</v>
       </c>
-      <c r="S23" s="279">
+      <c r="S23" s="281">
         <v>8.09</v>
       </c>
-      <c r="T23" s="274">
+      <c r="T23" s="282">
         <v>-38.13</v>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       <c r="C24" t="str">
         <v>920020</v>
       </c>
-      <c r="D24" s="299" t="str">
+      <c r="D24" s="294" t="str">
         <v>净卖: -668.61万</v>
       </c>
       <c r="E24">
@@ -9437,40 +9437,40 @@
       <c r="H24">
         <v>-9.66</v>
       </c>
-      <c r="I24" s="287">
+      <c r="I24" s="289">
         <v>14.02</v>
       </c>
-      <c r="J24" s="288">
+      <c r="J24" s="291">
         <v>2.92</v>
       </c>
-      <c r="K24" s="294">
+      <c r="K24" s="295">
         <v>1.38</v>
       </c>
-      <c r="L24" s="291">
+      <c r="L24" s="292">
         <v>0.51</v>
       </c>
-      <c r="M24" s="292">
+      <c r="M24" s="290">
         <v>-0.82</v>
       </c>
-      <c r="N24" s="293">
+      <c r="N24" s="296">
         <v>-0.87</v>
       </c>
-      <c r="O24" s="295">
+      <c r="O24" s="293">
         <v>0.87</v>
       </c>
-      <c r="P24" s="296">
+      <c r="P24" s="297">
         <v>-2.4</v>
       </c>
-      <c r="Q24" s="297">
+      <c r="Q24" s="298">
         <v>-5.17</v>
       </c>
-      <c r="R24" s="289">
+      <c r="R24" s="299">
         <v>-4.76</v>
       </c>
-      <c r="S24" s="298">
+      <c r="S24" s="287">
         <v>-4.35</v>
       </c>
-      <c r="T24" s="290">
+      <c r="T24" s="288">
         <v>-18.47</v>
       </c>
     </row>
@@ -9484,7 +9484,7 @@
       <c r="C25" t="str">
         <v>605178</v>
       </c>
-      <c r="D25" s="304" t="str">
+      <c r="D25" s="305" t="str">
         <v>净买: 3874.18万</v>
       </c>
       <c r="E25">
@@ -9499,40 +9499,40 @@
       <c r="H25">
         <v>10</v>
       </c>
-      <c r="I25" s="308">
+      <c r="I25" s="309">
         <v>0</v>
       </c>
-      <c r="J25" s="309">
+      <c r="J25" s="310">
         <v>10</v>
       </c>
-      <c r="K25" s="310">
+      <c r="K25" s="312">
         <v>0.58</v>
       </c>
-      <c r="L25" s="301">
+      <c r="L25" s="306">
         <v>4.74</v>
       </c>
-      <c r="M25" s="311">
+      <c r="M25" s="301">
         <v>13.42</v>
       </c>
-      <c r="N25" s="312">
+      <c r="N25" s="302">
         <v>19.72</v>
       </c>
-      <c r="O25" s="302">
+      <c r="O25" s="307">
         <v>26.01</v>
       </c>
-      <c r="P25" s="305">
+      <c r="P25" s="311">
         <v>16.89</v>
       </c>
-      <c r="Q25" s="306">
+      <c r="Q25" s="308">
         <v>6.52</v>
       </c>
-      <c r="R25" s="300">
+      <c r="R25" s="303">
         <v>10.9</v>
       </c>
-      <c r="S25" s="307">
+      <c r="S25" s="300">
         <v>12.81</v>
       </c>
-      <c r="T25" s="303">
+      <c r="T25" s="304">
         <v>36.81</v>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       <c r="C26" t="str">
         <v>000407</v>
       </c>
-      <c r="D26" s="315" t="str">
+      <c r="D26" s="322" t="str">
         <v>净买: 788.81万</v>
       </c>
       <c r="E26">
@@ -9561,40 +9561,40 @@
       <c r="H26">
         <v>10.1</v>
       </c>
-      <c r="I26" s="323">
+      <c r="I26" s="313">
         <v>0</v>
       </c>
       <c r="J26" s="321">
         <v>10.04</v>
       </c>
-      <c r="K26" s="316">
+      <c r="K26" s="323">
         <v>20.96</v>
       </c>
-      <c r="L26" s="324">
+      <c r="L26" s="314">
         <v>32.97</v>
       </c>
-      <c r="M26" s="325">
+      <c r="M26" s="324">
         <v>46.29</v>
       </c>
-      <c r="N26" s="317">
+      <c r="N26" s="315">
         <v>31.66</v>
       </c>
-      <c r="O26" s="313">
+      <c r="O26" s="325">
         <v>30.35</v>
       </c>
-      <c r="P26" s="314">
+      <c r="P26" s="316">
         <v>17.25</v>
       </c>
-      <c r="Q26" s="320">
+      <c r="Q26" s="317">
         <v>5.46</v>
       </c>
       <c r="R26" s="318">
         <v>5.9</v>
       </c>
-      <c r="S26" s="322">
+      <c r="S26" s="319">
         <v>12.45</v>
       </c>
-      <c r="T26" s="319">
+      <c r="T26" s="320">
         <v>1.31</v>
       </c>
     </row>
@@ -9623,40 +9623,40 @@
       <c r="H27">
         <v>9.96</v>
       </c>
-      <c r="I27" s="329">
+      <c r="I27" s="331">
         <v>0</v>
       </c>
-      <c r="J27" s="330">
+      <c r="J27" s="332">
         <v>-9.95</v>
       </c>
-      <c r="K27" s="336">
+      <c r="K27" s="333">
         <v>-19.01</v>
       </c>
-      <c r="L27" s="337">
+      <c r="L27" s="327">
         <v>-27.04</v>
       </c>
-      <c r="M27" s="332">
+      <c r="M27" s="337">
         <v>-30.61</v>
       </c>
-      <c r="N27" s="333">
+      <c r="N27" s="338">
         <v>-28.7</v>
       </c>
-      <c r="O27" s="338">
+      <c r="O27" s="326">
         <v>-31.89</v>
       </c>
-      <c r="P27" s="331">
+      <c r="P27" s="328">
         <v>-31.63</v>
       </c>
-      <c r="Q27" s="326">
+      <c r="Q27" s="336">
         <v>-28.95</v>
       </c>
       <c r="R27" s="334">
         <v>-26.53</v>
       </c>
-      <c r="S27" s="327">
+      <c r="S27" s="329">
         <v>-24.49</v>
       </c>
-      <c r="T27" s="328">
+      <c r="T27" s="330">
         <v>-24.23</v>
       </c>
     </row>
@@ -9670,7 +9670,7 @@
       <c r="C28" t="str">
         <v>300094</v>
       </c>
-      <c r="D28" s="351" t="str">
+      <c r="D28" s="341" t="str">
         <v>净卖: -3846.51万</v>
       </c>
       <c r="E28">
@@ -9685,40 +9685,40 @@
       <c r="H28">
         <v>0.37</v>
       </c>
-      <c r="I28" s="341">
+      <c r="I28" s="347">
         <v>-11.85</v>
       </c>
-      <c r="J28" s="348">
+      <c r="J28" s="342">
         <v>-12.41</v>
       </c>
-      <c r="K28" s="339">
+      <c r="K28" s="350">
         <v>-8.33</v>
       </c>
-      <c r="L28" s="342">
+      <c r="L28" s="348">
         <v>-17.96</v>
       </c>
-      <c r="M28" s="345">
+      <c r="M28" s="343">
         <v>-23.89</v>
       </c>
-      <c r="N28" s="349">
+      <c r="N28" s="351">
         <v>-22.96</v>
       </c>
-      <c r="O28" s="350">
+      <c r="O28" s="344">
         <v>-24.26</v>
       </c>
-      <c r="P28" s="343">
+      <c r="P28" s="339">
         <v>-23.15</v>
       </c>
-      <c r="Q28" s="346">
+      <c r="Q28" s="345">
         <v>-21.48</v>
       </c>
-      <c r="R28" s="344">
+      <c r="R28" s="340">
         <v>-21.85</v>
       </c>
-      <c r="S28" s="347">
+      <c r="S28" s="346">
         <v>-27.78</v>
       </c>
-      <c r="T28" s="340">
+      <c r="T28" s="349">
         <v>-42.22</v>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       <c r="C29" t="str">
         <v>002682</v>
       </c>
-      <c r="D29" s="352" t="str">
+      <c r="D29" s="356" t="str">
         <v>净卖: -2565.97万</v>
       </c>
       <c r="E29">
@@ -9747,40 +9747,40 @@
       <c r="H29">
         <v>-6.94</v>
       </c>
-      <c r="I29" s="353">
+      <c r="I29" s="360">
         <v>-3.35</v>
       </c>
-      <c r="J29" s="356">
+      <c r="J29" s="354">
         <v>-12.94</v>
       </c>
-      <c r="K29" s="354">
+      <c r="K29" s="357">
         <v>-17.2</v>
       </c>
-      <c r="L29" s="358">
+      <c r="L29" s="355">
         <v>-14.92</v>
       </c>
       <c r="M29" s="363">
         <v>-18.72</v>
       </c>
-      <c r="N29" s="359">
+      <c r="N29" s="358">
         <v>-18.42</v>
       </c>
-      <c r="O29" s="355">
+      <c r="O29" s="359">
         <v>-15.22</v>
       </c>
-      <c r="P29" s="360">
+      <c r="P29" s="361">
         <v>-12.33</v>
       </c>
       <c r="Q29" s="364">
         <v>-9.89</v>
       </c>
-      <c r="R29" s="361">
+      <c r="R29" s="352">
         <v>-0.91</v>
       </c>
       <c r="S29" s="362">
         <v>8.98</v>
       </c>
-      <c r="T29" s="357">
+      <c r="T29" s="353">
         <v>-9.59</v>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
       <c r="C30" t="str">
         <v>603069</v>
       </c>
-      <c r="D30" s="371" t="str">
+      <c r="D30" s="366" t="str">
         <v>净买: 2184.48万</v>
       </c>
       <c r="E30">
@@ -9812,22 +9812,22 @@
       <c r="I30" s="367">
         <v>0</v>
       </c>
-      <c r="J30" s="372">
+      <c r="J30" s="368">
         <v>1.25</v>
       </c>
-      <c r="K30" s="376">
+      <c r="K30" s="377">
         <v>-4.36</v>
       </c>
-      <c r="L30" s="368">
+      <c r="L30" s="374">
         <v>5.19</v>
       </c>
-      <c r="M30" s="373">
+      <c r="M30" s="372">
         <v>-1.42</v>
       </c>
-      <c r="N30" s="374">
+      <c r="N30" s="375">
         <v>-5.96</v>
       </c>
-      <c r="O30" s="375">
+      <c r="O30" s="376">
         <v>-5.99</v>
       </c>
       <c r="P30" s="369">
@@ -9836,13 +9836,13 @@
       <c r="Q30" s="370">
         <v>-13.64</v>
       </c>
-      <c r="R30" s="377">
+      <c r="R30" s="371">
         <v>-14.16</v>
       </c>
-      <c r="S30" s="365">
+      <c r="S30" s="373">
         <v>-15.27</v>
       </c>
-      <c r="T30" s="366">
+      <c r="T30" s="365">
         <v>-39.23</v>
       </c>
     </row>
@@ -9871,40 +9871,40 @@
       <c r="H31">
         <v>10</v>
       </c>
-      <c r="I31" s="384">
+      <c r="I31" s="383">
         <v>0</v>
       </c>
-      <c r="J31" s="378">
+      <c r="J31" s="379">
         <v>10.02</v>
       </c>
-      <c r="K31" s="389">
+      <c r="K31" s="384">
         <v>21.02</v>
       </c>
-      <c r="L31" s="381">
+      <c r="L31" s="378">
         <v>16.84</v>
       </c>
-      <c r="M31" s="385">
+      <c r="M31" s="380">
         <v>14.72</v>
       </c>
-      <c r="N31" s="379">
+      <c r="N31" s="385">
         <v>8.01</v>
       </c>
-      <c r="O31" s="382">
+      <c r="O31" s="386">
         <v>12.24</v>
       </c>
-      <c r="P31" s="383">
+      <c r="P31" s="381">
         <v>12.65</v>
       </c>
-      <c r="Q31" s="380">
+      <c r="Q31" s="387">
         <v>15.19</v>
       </c>
-      <c r="R31" s="386">
+      <c r="R31" s="389">
         <v>18.85</v>
       </c>
-      <c r="S31" s="387">
+      <c r="S31" s="388">
         <v>11.93</v>
       </c>
-      <c r="T31" s="388">
+      <c r="T31" s="382">
         <v>27.01</v>
       </c>
     </row>
@@ -9918,7 +9918,7 @@
       <c r="C32" t="str">
         <v>002009</v>
       </c>
-      <c r="D32" s="402" t="str">
+      <c r="D32" s="395" t="str">
         <v>净卖: -4207.08万</v>
       </c>
       <c r="E32">
@@ -9933,40 +9933,40 @@
       <c r="H32">
         <v>9.92</v>
       </c>
-      <c r="I32" s="392">
+      <c r="I32" s="398">
         <v>0.09</v>
       </c>
-      <c r="J32" s="395">
+      <c r="J32" s="400">
         <v>10.1</v>
       </c>
-      <c r="K32" s="399">
+      <c r="K32" s="401">
         <v>6.3</v>
       </c>
-      <c r="L32" s="393">
+      <c r="L32" s="402">
         <v>4.37</v>
       </c>
-      <c r="M32" s="403">
+      <c r="M32" s="399">
         <v>-1.74</v>
       </c>
-      <c r="N32" s="396">
+      <c r="N32" s="403">
         <v>2.11</v>
       </c>
-      <c r="O32" s="397">
+      <c r="O32" s="391">
         <v>2.49</v>
       </c>
-      <c r="P32" s="394">
+      <c r="P32" s="392">
         <v>4.79</v>
       </c>
-      <c r="Q32" s="391">
+      <c r="Q32" s="396">
         <v>8.13</v>
       </c>
-      <c r="R32" s="400">
+      <c r="R32" s="397">
         <v>1.83</v>
       </c>
-      <c r="S32" s="401">
+      <c r="S32" s="393">
         <v>2.63</v>
       </c>
-      <c r="T32" s="398">
+      <c r="T32" s="394">
         <v>15.55</v>
       </c>
     </row>
@@ -9980,7 +9980,7 @@
       <c r="C33" t="str">
         <v>002009</v>
       </c>
-      <c r="D33" s="408" t="str">
+      <c r="D33" s="414" t="str">
         <v>净卖: -4209.56万</v>
       </c>
       <c r="E33">
@@ -9995,40 +9995,40 @@
       <c r="H33">
         <v>2.21</v>
       </c>
-      <c r="I33" s="409">
+      <c r="I33" s="410">
         <v>7.63</v>
       </c>
-      <c r="J33" s="410">
+      <c r="J33" s="415">
         <v>3.9</v>
       </c>
       <c r="K33" s="411">
         <v>2.02</v>
       </c>
-      <c r="L33" s="416">
+      <c r="L33" s="407">
         <v>-3.95</v>
       </c>
-      <c r="M33" s="413">
+      <c r="M33" s="416">
         <v>-0.18</v>
       </c>
       <c r="N33" s="404">
         <v>0.18</v>
       </c>
-      <c r="O33" s="406">
+      <c r="O33" s="405">
         <v>2.43</v>
       </c>
       <c r="P33" s="412">
         <v>5.7</v>
       </c>
-      <c r="Q33" s="407">
+      <c r="Q33" s="406">
         <v>-0.46</v>
       </c>
-      <c r="R33" s="405">
+      <c r="R33" s="413">
         <v>0.32</v>
       </c>
-      <c r="S33" s="414">
+      <c r="S33" s="408">
         <v>-1.52</v>
       </c>
-      <c r="T33" s="415">
+      <c r="T33" s="409">
         <v>12.95</v>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       <c r="C34" t="str">
         <v>002969</v>
       </c>
-      <c r="D34" s="420" t="str">
+      <c r="D34" s="419" t="str">
         <v>净卖: -2752.13万</v>
       </c>
       <c r="E34">
@@ -10057,40 +10057,40 @@
       <c r="H34">
         <v>0.55</v>
       </c>
-      <c r="I34" s="417">
+      <c r="I34" s="427">
         <v>7.62</v>
       </c>
-      <c r="J34" s="422">
+      <c r="J34" s="418">
         <v>18.38</v>
       </c>
-      <c r="K34" s="426">
+      <c r="K34" s="421">
         <v>30.24</v>
       </c>
-      <c r="L34" s="423">
+      <c r="L34" s="422">
         <v>37.86</v>
       </c>
-      <c r="M34" s="427">
+      <c r="M34" s="428">
         <v>51.69</v>
       </c>
-      <c r="N34" s="424">
+      <c r="N34" s="423">
         <v>36.53</v>
       </c>
-      <c r="O34" s="418">
+      <c r="O34" s="424">
         <v>22.86</v>
       </c>
-      <c r="P34" s="419">
+      <c r="P34" s="420">
         <v>35.11</v>
       </c>
-      <c r="Q34" s="428">
+      <c r="Q34" s="429">
         <v>48.63</v>
       </c>
-      <c r="R34" s="425">
+      <c r="R34" s="417">
         <v>52.47</v>
       </c>
-      <c r="S34" s="421">
+      <c r="S34" s="425">
         <v>67.71</v>
       </c>
-      <c r="T34" s="429">
+      <c r="T34" s="426">
         <v>77.3</v>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       <c r="C35" t="str">
         <v>600683</v>
       </c>
-      <c r="D35" s="442" t="str">
+      <c r="D35" s="435" t="str">
         <v>净买: 819.30万</v>
       </c>
       <c r="E35">
@@ -10119,34 +10119,34 @@
       <c r="H35">
         <v>10.1</v>
       </c>
-      <c r="I35" s="432">
+      <c r="I35" s="440">
         <v>0</v>
       </c>
-      <c r="J35" s="440">
+      <c r="J35" s="441">
         <v>10.09</v>
       </c>
-      <c r="K35" s="433">
+      <c r="K35" s="442">
         <v>21.1</v>
       </c>
-      <c r="L35" s="436">
+      <c r="L35" s="430">
         <v>11.01</v>
       </c>
-      <c r="M35" s="430">
+      <c r="M35" s="436">
         <v>22.2</v>
       </c>
-      <c r="N35" s="434">
+      <c r="N35" s="437">
         <v>22.57</v>
       </c>
-      <c r="O35" s="435">
+      <c r="O35" s="431">
         <v>32.29</v>
       </c>
-      <c r="P35" s="431">
+      <c r="P35" s="432">
         <v>27.16</v>
       </c>
-      <c r="Q35" s="441">
+      <c r="Q35" s="433">
         <v>23.12</v>
       </c>
-      <c r="R35" s="437">
+      <c r="R35" s="434">
         <v>30.46</v>
       </c>
       <c r="S35" s="438">
@@ -10166,7 +10166,7 @@
       <c r="C36" t="str">
         <v>002056</v>
       </c>
-      <c r="D36" s="453" t="str">
+      <c r="D36" s="450" t="str">
         <v>净卖: -2838.92万</v>
       </c>
       <c r="E36">
@@ -10181,40 +10181,40 @@
       <c r="H36">
         <v>1.28</v>
       </c>
-      <c r="I36" s="446">
+      <c r="I36" s="451">
         <v>8.62</v>
       </c>
-      <c r="J36" s="447">
+      <c r="J36" s="449">
         <v>-0.42</v>
       </c>
-      <c r="K36" s="443">
+      <c r="K36" s="452">
         <v>-4.25</v>
       </c>
-      <c r="L36" s="444">
+      <c r="L36" s="443">
         <v>-5.84</v>
       </c>
-      <c r="M36" s="450">
+      <c r="M36" s="453">
         <v>-8.66</v>
       </c>
-      <c r="N36" s="451">
+      <c r="N36" s="444">
         <v>-6.43</v>
       </c>
-      <c r="O36" s="452">
+      <c r="O36" s="454">
         <v>-9.21</v>
       </c>
-      <c r="P36" s="448">
+      <c r="P36" s="455">
         <v>-9.21</v>
       </c>
-      <c r="Q36" s="449">
+      <c r="Q36" s="445">
         <v>-7.78</v>
       </c>
-      <c r="R36" s="454">
+      <c r="R36" s="446">
         <v>-9.46</v>
       </c>
-      <c r="S36" s="445">
+      <c r="S36" s="447">
         <v>-9.92</v>
       </c>
-      <c r="T36" s="455">
+      <c r="T36" s="448">
         <v>-18.5</v>
       </c>
     </row>
@@ -10277,40 +10277,40 @@
       <c r="F38" t="str"/>
       <c r="G38" t="str"/>
       <c r="H38" t="str"/>
-      <c r="I38" s="457">
+      <c r="I38" s="458">
         <v>31.43</v>
       </c>
-      <c r="J38" s="461">
+      <c r="J38" s="459">
         <v>62.86</v>
       </c>
-      <c r="K38" s="458">
+      <c r="K38" s="460">
         <v>54.29</v>
       </c>
-      <c r="L38" s="465">
+      <c r="L38" s="464">
         <v>54.29</v>
       </c>
-      <c r="M38" s="466">
+      <c r="M38" s="465">
         <v>42.86</v>
       </c>
-      <c r="N38" s="462">
+      <c r="N38" s="461">
         <v>42.86</v>
       </c>
-      <c r="O38" s="463">
+      <c r="O38" s="466">
         <v>48.57</v>
       </c>
-      <c r="P38" s="467">
+      <c r="P38" s="462">
         <v>37.14</v>
       </c>
-      <c r="Q38" s="464">
+      <c r="Q38" s="463">
         <v>31.43</v>
       </c>
-      <c r="R38" s="456">
+      <c r="R38" s="467">
         <v>34.29</v>
       </c>
-      <c r="S38" s="459">
+      <c r="S38" s="456">
         <v>31.43</v>
       </c>
-      <c r="T38" s="460">
+      <c r="T38" s="457">
         <v>48.57</v>
       </c>
     </row>
@@ -10325,40 +10325,40 @@
       <c r="F39" t="str"/>
       <c r="G39" t="str"/>
       <c r="H39" t="str"/>
-      <c r="I39" s="471">
+      <c r="I39" s="470">
         <v>0.72</v>
       </c>
-      <c r="J39" s="472">
+      <c r="J39" s="478">
         <v>1.7</v>
       </c>
-      <c r="K39" s="474">
+      <c r="K39" s="479">
         <v>1.83</v>
       </c>
-      <c r="L39" s="476">
+      <c r="L39" s="474">
         <v>1.8</v>
       </c>
-      <c r="M39" s="477">
+      <c r="M39" s="475">
         <v>1.64</v>
       </c>
-      <c r="N39" s="473">
+      <c r="N39" s="476">
         <v>0.36</v>
       </c>
-      <c r="O39" s="469">
+      <c r="O39" s="468">
         <v>0.46</v>
       </c>
-      <c r="P39" s="475">
+      <c r="P39" s="471">
         <v>-2.04</v>
       </c>
-      <c r="Q39" s="470">
+      <c r="Q39" s="469">
         <v>-3.24</v>
       </c>
-      <c r="R39" s="478">
+      <c r="R39" s="472">
         <v>-2.68</v>
       </c>
-      <c r="S39" s="479">
+      <c r="S39" s="477">
         <v>-2.27</v>
       </c>
-      <c r="T39" s="468">
+      <c r="T39" s="473">
         <v>10.81</v>
       </c>
     </row>

--- a/youzi/正经哥/index.xlsx
+++ b/youzi/正经哥/index.xlsx
@@ -45,25 +45,913 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF36AC51"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0ABB1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,25 +963,307 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF36AC51"/>
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,25 +1275,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,6 +1377,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -153,49 +1437,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,37 +1467,739 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -261,19 +2211,265 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,19 +2481,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBF8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,18 +2673,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -339,13 +2691,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -357,631 +2709,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
+        <fgColor rgb="FF48B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -993,37 +2727,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4654"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1035,1807 +2877,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7FBF8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2847,67 +2895,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4654"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8073,40 +8073,40 @@
       <c r="H2">
         <v>10.06</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="8">
         <v>0</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="12">
         <v>10</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="5">
         <v>21.03</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="2">
         <v>30</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="13">
         <v>18.79</v>
       </c>
       <c r="N2" s="9">
         <v>10</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="1">
         <v>11.72</v>
       </c>
-      <c r="P2" s="13">
+      <c r="P2" s="6">
         <v>10.17</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="10">
         <v>2.07</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="7">
         <v>-4.66</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="3">
         <v>-8.45</v>
       </c>
-      <c r="T2" s="3">
+      <c r="T2" s="4">
         <v>-18.1</v>
       </c>
     </row>
@@ -8120,7 +8120,7 @@
       <c r="C3" t="str">
         <v>002300</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="15" t="str">
         <v>净买: 2299.17万</v>
       </c>
       <c r="E3">
@@ -8135,40 +8135,40 @@
       <c r="H3">
         <v>9.95</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="23">
         <v>0</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="16">
         <v>10.06</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="20">
         <v>21.12</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="26">
         <v>9.77</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="21">
         <v>-1.15</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="14">
         <v>-8.76</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="17">
         <v>-11.35</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="18">
         <v>-12.36</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="19">
         <v>-13.22</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="22">
         <v>-21.84</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="24">
         <v>-23.99</v>
       </c>
-      <c r="T3" s="16">
+      <c r="T3" s="25">
         <v>36.06</v>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       <c r="C4" t="str">
         <v>002300</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="29" t="str">
         <v>净卖: -2576.68万</v>
       </c>
       <c r="E4">
@@ -8197,40 +8197,40 @@
       <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="36">
         <v>9.34</v>
       </c>
       <c r="J4" s="37">
         <v>-0.91</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="30">
         <v>-10.77</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="33">
         <v>-17.64</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="31">
         <v>-19.97</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="27">
         <v>-20.88</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="38">
         <v>-21.66</v>
       </c>
       <c r="P4" s="34">
         <v>-29.44</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="39">
         <v>-31.39</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="32">
         <v>-28.92</v>
       </c>
       <c r="S4" s="35">
         <v>-27.63</v>
       </c>
-      <c r="T4" s="36">
+      <c r="T4" s="28">
         <v>22.83</v>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       <c r="C5" t="str">
         <v>002688</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="50" t="str">
         <v>净买: 5775.20万</v>
       </c>
       <c r="E5">
@@ -8259,40 +8259,40 @@
       <c r="H5">
         <v>9.93</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="51">
         <v>0</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="45">
         <v>9.95</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="42">
         <v>20.98</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="47">
         <v>30.17</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="52">
         <v>17.15</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="43">
         <v>8.58</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="48">
         <v>10.57</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="44">
         <v>-0.46</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="40">
         <v>-5.36</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="41">
         <v>-5.05</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="46">
         <v>-4.29</v>
       </c>
-      <c r="T5" s="47">
+      <c r="T5" s="49">
         <v>-10.11</v>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="65" t="str">
         <v>净卖: -7396.08万</v>
       </c>
       <c r="E6">
@@ -8321,40 +8321,40 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="56">
         <v>7.59</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="62">
         <v>-3.16</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="57">
         <v>-10.25</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="58">
         <v>-8.61</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="59">
         <v>-17.72</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="60">
         <v>-21.77</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="55">
         <v>-21.52</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="63">
         <v>-20.89</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="61">
         <v>-16.71</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="53">
         <v>-20.76</v>
       </c>
       <c r="S6" s="64">
         <v>-17.09</v>
       </c>
-      <c r="T6" s="65">
+      <c r="T6" s="54">
         <v>-25.7</v>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       <c r="C7" t="str">
         <v>600697</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="78" t="str">
         <v>净卖: -2819.93万</v>
       </c>
       <c r="E7">
@@ -8383,16 +8383,16 @@
       <c r="H7">
         <v>-9.28</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="70">
         <v>3.2</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="66">
         <v>6.95</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="71">
         <v>17.66</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="72">
         <v>13.12</v>
       </c>
       <c r="M7" s="74">
@@ -8401,22 +8401,22 @@
       <c r="N7" s="67">
         <v>0</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="75">
         <v>4.3</v>
       </c>
-      <c r="P7" s="68">
+      <c r="P7" s="76">
         <v>-1.72</v>
       </c>
-      <c r="Q7" s="77">
+      <c r="Q7" s="68">
         <v>-5.31</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="69">
         <v>-5.23</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="73">
         <v>-7.97</v>
       </c>
-      <c r="T7" s="70">
+      <c r="T7" s="77">
         <v>-8.2</v>
       </c>
     </row>
@@ -8430,7 +8430,7 @@
       <c r="C8" t="str">
         <v>600828</v>
       </c>
-      <c r="D8" s="84" t="str">
+      <c r="D8" s="83" t="str">
         <v>净买: 1425.83万</v>
       </c>
       <c r="E8">
@@ -8445,40 +8445,40 @@
       <c r="H8">
         <v>10.11</v>
       </c>
-      <c r="I8" s="85">
+      <c r="I8" s="90">
         <v>0</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="81">
         <v>10.02</v>
       </c>
-      <c r="K8" s="90">
+      <c r="K8" s="91">
         <v>7.31</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="87">
         <v>5.01</v>
       </c>
-      <c r="M8" s="91">
+      <c r="M8" s="88">
         <v>10.65</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="84">
         <v>5.43</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="85">
         <v>-5.01</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="86">
         <v>-10.02</v>
       </c>
-      <c r="Q8" s="81">
+      <c r="Q8" s="89">
         <v>-12.73</v>
       </c>
-      <c r="R8" s="80">
+      <c r="R8" s="79">
         <v>-11.69</v>
       </c>
-      <c r="S8" s="88">
+      <c r="S8" s="80">
         <v>-10.65</v>
       </c>
-      <c r="T8" s="83">
+      <c r="T8" s="82">
         <v>10.23</v>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       <c r="C9" t="str">
         <v>600828</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="98" t="str">
         <v>净卖: -1514.63万</v>
       </c>
       <c r="E9">
@@ -8507,40 +8507,40 @@
       <c r="H9">
         <v>-0.21</v>
       </c>
-      <c r="I9" s="98">
+      <c r="I9" s="99">
         <v>10.25</v>
       </c>
-      <c r="J9" s="96">
+      <c r="J9" s="92">
         <v>7.53</v>
       </c>
-      <c r="K9" s="99">
+      <c r="K9" s="101">
         <v>5.23</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="93">
         <v>10.88</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="94">
         <v>5.65</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="95">
         <v>-4.81</v>
       </c>
-      <c r="O9" s="104">
+      <c r="O9" s="96">
         <v>-9.83</v>
       </c>
-      <c r="P9" s="92">
+      <c r="P9" s="102">
         <v>-12.55</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="97">
         <v>-11.51</v>
       </c>
-      <c r="R9" s="94">
+      <c r="R9" s="100">
         <v>-10.46</v>
       </c>
-      <c r="S9" s="95">
+      <c r="S9" s="103">
         <v>-12.34</v>
       </c>
-      <c r="T9" s="100">
+      <c r="T9" s="104">
         <v>10.46</v>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       <c r="C10" t="str">
         <v>002909</v>
       </c>
-      <c r="D10" s="109" t="str">
+      <c r="D10" s="116" t="str">
         <v>净卖: -879.53万</v>
       </c>
       <c r="E10">
@@ -8569,40 +8569,40 @@
       <c r="H10">
         <v>-1.91</v>
       </c>
-      <c r="I10" s="115">
+      <c r="I10" s="117">
         <v>-8.28</v>
       </c>
-      <c r="J10" s="116">
+      <c r="J10" s="109">
         <v>-16.44</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="114">
         <v>-21.07</v>
       </c>
-      <c r="L10" s="117">
+      <c r="L10" s="115">
         <v>-21.8</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="111">
         <v>-23.39</v>
       </c>
-      <c r="N10" s="112">
+      <c r="N10" s="105">
         <v>-23.02</v>
       </c>
-      <c r="O10" s="107">
+      <c r="O10" s="112">
         <v>-22.66</v>
       </c>
-      <c r="P10" s="111">
+      <c r="P10" s="106">
         <v>-23.87</v>
       </c>
-      <c r="Q10" s="113">
+      <c r="Q10" s="107">
         <v>-23.26</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="113">
         <v>-24.12</v>
       </c>
-      <c r="S10" s="108">
+      <c r="S10" s="110">
         <v>-23.87</v>
       </c>
-      <c r="T10" s="105">
+      <c r="T10" s="108">
         <v>-22.41</v>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
       <c r="C11" t="str">
         <v>603639</v>
       </c>
-      <c r="D11" s="118" t="str">
+      <c r="D11" s="124" t="str">
         <v>净买: 1633.37万</v>
       </c>
       <c r="E11">
@@ -8631,37 +8631,37 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="124">
+      <c r="I11" s="121">
         <v>0</v>
       </c>
-      <c r="J11" s="125">
+      <c r="J11" s="118">
         <v>-6.63</v>
       </c>
-      <c r="K11" s="126">
+      <c r="K11" s="125">
         <v>-12.9</v>
       </c>
-      <c r="L11" s="128">
+      <c r="L11" s="122">
         <v>-12.16</v>
       </c>
-      <c r="M11" s="119">
+      <c r="M11" s="123">
         <v>-13.76</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="126">
         <v>-9.83</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="128">
         <v>-10.63</v>
       </c>
       <c r="P11" s="129">
         <v>-9.46</v>
       </c>
-      <c r="Q11" s="123">
+      <c r="Q11" s="127">
         <v>-10.44</v>
       </c>
-      <c r="R11" s="127">
+      <c r="R11" s="119">
         <v>-10.01</v>
       </c>
-      <c r="S11" s="122">
+      <c r="S11" s="120">
         <v>-8.17</v>
       </c>
       <c r="T11" s="130">
@@ -8678,7 +8678,7 @@
       <c r="C12" t="str">
         <v>002235</v>
       </c>
-      <c r="D12" s="140" t="str">
+      <c r="D12" s="134" t="str">
         <v>净买: 1768.35万</v>
       </c>
       <c r="E12">
@@ -8693,40 +8693,40 @@
       <c r="H12">
         <v>10.05</v>
       </c>
-      <c r="I12" s="138">
+      <c r="I12" s="135">
         <v>0</v>
       </c>
-      <c r="J12" s="134">
+      <c r="J12" s="131">
         <v>3.19</v>
       </c>
-      <c r="K12" s="143">
+      <c r="K12" s="141">
         <v>6.23</v>
       </c>
-      <c r="L12" s="131">
+      <c r="L12" s="139">
         <v>16.81</v>
       </c>
-      <c r="M12" s="141">
+      <c r="M12" s="136">
         <v>18.99</v>
       </c>
-      <c r="N12" s="135">
+      <c r="N12" s="132">
         <v>30.87</v>
       </c>
-      <c r="O12" s="139">
+      <c r="O12" s="137">
         <v>43.91</v>
       </c>
-      <c r="P12" s="132">
+      <c r="P12" s="133">
         <v>42.17</v>
       </c>
-      <c r="Q12" s="136">
+      <c r="Q12" s="142">
         <v>36.52</v>
       </c>
-      <c r="R12" s="137">
+      <c r="R12" s="140">
         <v>43.48</v>
       </c>
-      <c r="S12" s="133">
+      <c r="S12" s="138">
         <v>44.93</v>
       </c>
-      <c r="T12" s="142">
+      <c r="T12" s="143">
         <v>37.1</v>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       <c r="C13" t="str">
         <v>603776</v>
       </c>
-      <c r="D13" s="144" t="str">
+      <c r="D13" s="156" t="str">
         <v>净买: 1894.22万</v>
       </c>
       <c r="E13">
@@ -8758,37 +8758,37 @@
       <c r="I13" s="147">
         <v>0</v>
       </c>
-      <c r="J13" s="155">
+      <c r="J13" s="151">
         <v>-9.72</v>
       </c>
-      <c r="K13" s="145">
+      <c r="K13" s="152">
         <v>-10.95</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="154">
         <v>-8.45</v>
       </c>
-      <c r="M13" s="151">
+      <c r="M13" s="144">
         <v>-7.04</v>
       </c>
-      <c r="N13" s="146">
+      <c r="N13" s="145">
         <v>-11.27</v>
       </c>
-      <c r="O13" s="152">
+      <c r="O13" s="146">
         <v>-2.41</v>
       </c>
-      <c r="P13" s="148">
+      <c r="P13" s="155">
         <v>2.36</v>
       </c>
-      <c r="Q13" s="153">
+      <c r="Q13" s="148">
         <v>-2.64</v>
       </c>
-      <c r="R13" s="156">
+      <c r="R13" s="149">
         <v>-2.32</v>
       </c>
-      <c r="S13" s="154">
+      <c r="S13" s="150">
         <v>-2.23</v>
       </c>
-      <c r="T13" s="149">
+      <c r="T13" s="153">
         <v>-8.86</v>
       </c>
     </row>
@@ -8802,7 +8802,7 @@
       <c r="C14" t="str">
         <v>603776</v>
       </c>
-      <c r="D14" s="160" t="str">
+      <c r="D14" s="157" t="str">
         <v>净卖: -2197.25万</v>
       </c>
       <c r="E14">
@@ -8817,13 +8817,13 @@
       <c r="H14">
         <v>-2.32</v>
       </c>
-      <c r="I14" s="157">
+      <c r="I14" s="166">
         <v>-7.58</v>
       </c>
-      <c r="J14" s="161">
+      <c r="J14" s="162">
         <v>-8.84</v>
       </c>
-      <c r="K14" s="162">
+      <c r="K14" s="163">
         <v>-6.28</v>
       </c>
       <c r="L14" s="158">
@@ -8835,22 +8835,22 @@
       <c r="N14" s="167">
         <v>-0.09</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="168">
         <v>4.79</v>
       </c>
-      <c r="P14" s="164">
+      <c r="P14" s="161">
         <v>-0.33</v>
       </c>
-      <c r="Q14" s="165">
+      <c r="Q14" s="160">
         <v>0</v>
       </c>
-      <c r="R14" s="168">
+      <c r="R14" s="169">
         <v>0.09</v>
       </c>
-      <c r="S14" s="169">
+      <c r="S14" s="164">
         <v>0</v>
       </c>
-      <c r="T14" s="166">
+      <c r="T14" s="165">
         <v>-6.7</v>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       <c r="C15" t="str">
         <v>001360</v>
       </c>
-      <c r="D15" s="177" t="str">
+      <c r="D15" s="178" t="str">
         <v>净买: 1803.24万</v>
       </c>
       <c r="E15">
@@ -8879,40 +8879,40 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="179">
         <v>0</v>
       </c>
-      <c r="J15" s="172">
+      <c r="J15" s="171">
         <v>10.01</v>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="172">
         <v>-0.95</v>
       </c>
-      <c r="L15" s="182">
+      <c r="L15" s="173">
         <v>-10.85</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="180">
         <v>-13.18</v>
       </c>
-      <c r="N15" s="170">
+      <c r="N15" s="174">
         <v>-14.29</v>
       </c>
-      <c r="O15" s="179">
+      <c r="O15" s="181">
         <v>-15.25</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="175">
         <v>-14.56</v>
       </c>
       <c r="Q15" s="176">
         <v>-16.52</v>
       </c>
-      <c r="R15" s="181">
+      <c r="R15" s="182">
         <v>-16.36</v>
       </c>
-      <c r="S15" s="173">
+      <c r="S15" s="170">
         <v>-16.15</v>
       </c>
-      <c r="T15" s="174">
+      <c r="T15" s="177">
         <v>15.83</v>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       <c r="C16" t="str">
         <v>601669</v>
       </c>
-      <c r="D16" s="192" t="str">
+      <c r="D16" s="187" t="str">
         <v>净买: 9396.35万</v>
       </c>
       <c r="E16">
@@ -8941,40 +8941,40 @@
       <c r="H16">
         <v>10.08</v>
       </c>
-      <c r="I16" s="184">
+      <c r="I16" s="188">
         <v>0</v>
       </c>
-      <c r="J16" s="193">
+      <c r="J16" s="189">
         <v>10.04</v>
       </c>
-      <c r="K16" s="185">
+      <c r="K16" s="184">
         <v>6.65</v>
       </c>
-      <c r="L16" s="194">
+      <c r="L16" s="190">
         <v>3.84</v>
       </c>
-      <c r="M16" s="186">
+      <c r="M16" s="191">
         <v>5.76</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="192">
         <v>0.44</v>
       </c>
-      <c r="O16" s="189">
+      <c r="O16" s="185">
         <v>0.89</v>
       </c>
-      <c r="P16" s="190">
+      <c r="P16" s="195">
         <v>-3.69</v>
       </c>
-      <c r="Q16" s="191">
+      <c r="Q16" s="193">
         <v>-4.58</v>
       </c>
-      <c r="R16" s="195">
+      <c r="R16" s="186">
         <v>-5.17</v>
       </c>
-      <c r="S16" s="187">
+      <c r="S16" s="194">
         <v>-6.5</v>
       </c>
-      <c r="T16" s="188">
+      <c r="T16" s="183">
         <v>-15.66</v>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
       <c r="C17" t="str">
         <v>001360</v>
       </c>
-      <c r="D17" s="197" t="str">
+      <c r="D17" s="206" t="str">
         <v>净卖: -1800.16万</v>
       </c>
       <c r="E17">
@@ -9006,28 +9006,28 @@
       <c r="I17" s="198">
         <v>-10.05</v>
       </c>
-      <c r="J17" s="204">
+      <c r="J17" s="196">
         <v>-19.04</v>
       </c>
       <c r="K17" s="199">
         <v>-21.15</v>
       </c>
-      <c r="L17" s="205">
+      <c r="L17" s="207">
         <v>-22.16</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="200">
         <v>-23.03</v>
       </c>
-      <c r="N17" s="206">
+      <c r="N17" s="204">
         <v>-22.4</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="201">
         <v>-24.18</v>
       </c>
-      <c r="P17" s="200">
+      <c r="P17" s="197">
         <v>-24.04</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="208">
         <v>-23.85</v>
       </c>
       <c r="R17" s="202">
@@ -9036,7 +9036,7 @@
       <c r="S17" s="203">
         <v>-24.47</v>
       </c>
-      <c r="T17" s="201">
+      <c r="T17" s="205">
         <v>5.19</v>
       </c>
     </row>
@@ -9050,7 +9050,7 @@
       <c r="C18" t="str">
         <v>001360</v>
       </c>
-      <c r="D18" s="216" t="str">
+      <c r="D18" s="211" t="str">
         <v>净卖: -1799.99万</v>
       </c>
       <c r="E18">
@@ -9065,40 +9065,40 @@
       <c r="H18">
         <v>-9.14</v>
       </c>
-      <c r="I18" s="217">
+      <c r="I18" s="214">
         <v>-0.94</v>
       </c>
-      <c r="J18" s="210">
+      <c r="J18" s="215">
         <v>-3.53</v>
       </c>
-      <c r="K18" s="218">
+      <c r="K18" s="217">
         <v>-4.76</v>
       </c>
-      <c r="L18" s="214">
+      <c r="L18" s="218">
         <v>-5.82</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="219">
         <v>-5.06</v>
       </c>
-      <c r="N18" s="219">
+      <c r="N18" s="209">
         <v>-7.24</v>
       </c>
-      <c r="O18" s="220">
+      <c r="O18" s="216">
         <v>-7.06</v>
       </c>
-      <c r="P18" s="215">
+      <c r="P18" s="210">
         <v>-6.82</v>
       </c>
-      <c r="Q18" s="221">
+      <c r="Q18" s="212">
         <v>-7.35</v>
       </c>
-      <c r="R18" s="213">
+      <c r="R18" s="220">
         <v>-7.59</v>
       </c>
-      <c r="S18" s="209">
+      <c r="S18" s="221">
         <v>-6.59</v>
       </c>
-      <c r="T18" s="211">
+      <c r="T18" s="213">
         <v>28.71</v>
       </c>
     </row>
@@ -9112,7 +9112,7 @@
       <c r="C19" t="str">
         <v>300620</v>
       </c>
-      <c r="D19" s="228" t="str">
+      <c r="D19" s="223" t="str">
         <v>净买: 1215.21万</v>
       </c>
       <c r="E19">
@@ -9127,40 +9127,40 @@
       <c r="H19">
         <v>19.99</v>
       </c>
-      <c r="I19" s="229">
+      <c r="I19" s="232">
         <v>0</v>
       </c>
-      <c r="J19" s="230">
+      <c r="J19" s="222">
         <v>20.01</v>
       </c>
-      <c r="K19" s="222">
+      <c r="K19" s="229">
         <v>21.14</v>
       </c>
-      <c r="L19" s="233">
+      <c r="L19" s="230">
         <v>24.09</v>
       </c>
-      <c r="M19" s="223">
+      <c r="M19" s="224">
         <v>46.79</v>
       </c>
-      <c r="N19" s="224">
+      <c r="N19" s="225">
         <v>50.73</v>
       </c>
-      <c r="O19" s="226">
+      <c r="O19" s="233">
         <v>40.57</v>
       </c>
-      <c r="P19" s="231">
+      <c r="P19" s="226">
         <v>31.96</v>
       </c>
       <c r="Q19" s="234">
         <v>34.41</v>
       </c>
-      <c r="R19" s="225">
+      <c r="R19" s="227">
         <v>39.6</v>
       </c>
-      <c r="S19" s="232">
+      <c r="S19" s="228">
         <v>34.69</v>
       </c>
-      <c r="T19" s="227">
+      <c r="T19" s="231">
         <v>281.1</v>
       </c>
     </row>
@@ -9174,7 +9174,7 @@
       <c r="C20" t="str">
         <v>002177</v>
       </c>
-      <c r="D20" s="245" t="str">
+      <c r="D20" s="238" t="str">
         <v>净卖: -3762.63万</v>
       </c>
       <c r="E20">
@@ -9189,40 +9189,40 @@
       <c r="H20">
         <v>3.85</v>
       </c>
-      <c r="I20" s="247">
+      <c r="I20" s="235">
         <v>5.93</v>
       </c>
       <c r="J20" s="242">
         <v>1.38</v>
       </c>
-      <c r="K20" s="237">
+      <c r="K20" s="241">
         <v>-1.17</v>
       </c>
-      <c r="L20" s="238">
+      <c r="L20" s="239">
         <v>-10.91</v>
       </c>
-      <c r="M20" s="239">
+      <c r="M20" s="240">
         <v>-11.76</v>
       </c>
       <c r="N20" s="243">
         <v>-12.39</v>
       </c>
-      <c r="O20" s="246">
+      <c r="O20" s="244">
         <v>-9.96</v>
       </c>
-      <c r="P20" s="240">
+      <c r="P20" s="245">
         <v>-15.15</v>
       </c>
-      <c r="Q20" s="235">
+      <c r="Q20" s="236">
         <v>-17.9</v>
       </c>
-      <c r="R20" s="244">
+      <c r="R20" s="246">
         <v>-19.39</v>
       </c>
-      <c r="S20" s="236">
+      <c r="S20" s="247">
         <v>-18.11</v>
       </c>
-      <c r="T20" s="241">
+      <c r="T20" s="237">
         <v>-16.53</v>
       </c>
     </row>
@@ -9251,40 +9251,40 @@
       <c r="H21">
         <v>20</v>
       </c>
-      <c r="I21" s="256">
+      <c r="I21" s="248">
         <v>-14.18</v>
       </c>
-      <c r="J21" s="257">
+      <c r="J21" s="251">
         <v>-19.79</v>
       </c>
-      <c r="K21" s="248">
+      <c r="K21" s="252">
         <v>-18.67</v>
       </c>
-      <c r="L21" s="249">
+      <c r="L21" s="253">
         <v>-21.09</v>
       </c>
-      <c r="M21" s="251">
+      <c r="M21" s="257">
         <v>-22.21</v>
       </c>
-      <c r="N21" s="252">
+      <c r="N21" s="254">
         <v>-18.54</v>
       </c>
       <c r="O21" s="258">
         <v>-22.58</v>
       </c>
-      <c r="P21" s="253">
+      <c r="P21" s="255">
         <v>-27.04</v>
       </c>
-      <c r="Q21" s="254">
+      <c r="Q21" s="256">
         <v>-25.09</v>
       </c>
-      <c r="R21" s="259">
+      <c r="R21" s="249">
         <v>-21.88</v>
       </c>
-      <c r="S21" s="260">
+      <c r="S21" s="259">
         <v>-25.85</v>
       </c>
-      <c r="T21" s="255">
+      <c r="T21" s="260">
         <v>19.65</v>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       <c r="C22" t="str">
         <v>002547</v>
       </c>
-      <c r="D22" s="262" t="str">
+      <c r="D22" s="268" t="str">
         <v>净买: 4862.70万</v>
       </c>
       <c r="E22">
@@ -9313,40 +9313,40 @@
       <c r="H22">
         <v>10.1</v>
       </c>
-      <c r="I22" s="268">
+      <c r="I22" s="269">
         <v>0</v>
       </c>
-      <c r="J22" s="269">
+      <c r="J22" s="263">
         <v>7.01</v>
       </c>
       <c r="K22" s="264">
         <v>0.36</v>
       </c>
-      <c r="L22" s="270">
+      <c r="L22" s="272">
         <v>4.68</v>
       </c>
-      <c r="M22" s="271">
+      <c r="M22" s="265">
         <v>15.11</v>
       </c>
-      <c r="N22" s="272">
+      <c r="N22" s="273">
         <v>21.76</v>
       </c>
-      <c r="O22" s="265">
+      <c r="O22" s="266">
         <v>22.66</v>
       </c>
-      <c r="P22" s="273">
+      <c r="P22" s="267">
         <v>17.81</v>
       </c>
-      <c r="Q22" s="266">
+      <c r="Q22" s="261">
         <v>9.17</v>
       </c>
-      <c r="R22" s="267">
+      <c r="R22" s="270">
         <v>12.59</v>
       </c>
-      <c r="S22" s="261">
+      <c r="S22" s="271">
         <v>7.01</v>
       </c>
-      <c r="T22" s="263">
+      <c r="T22" s="262">
         <v>-38.13</v>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       <c r="C23" t="str">
         <v>002547</v>
       </c>
-      <c r="D23" s="283" t="str">
+      <c r="D23" s="277" t="str">
         <v>净卖: -5175.09万</v>
       </c>
       <c r="E23">
@@ -9375,40 +9375,40 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23" s="276">
+      <c r="I23" s="281">
         <v>7.01</v>
       </c>
-      <c r="J23" s="284">
+      <c r="J23" s="282">
         <v>0.36</v>
       </c>
-      <c r="K23" s="277">
+      <c r="K23" s="274">
         <v>4.68</v>
       </c>
       <c r="L23" s="278">
         <v>15.11</v>
       </c>
-      <c r="M23" s="285">
+      <c r="M23" s="284">
         <v>21.76</v>
       </c>
-      <c r="N23" s="286">
+      <c r="N23" s="283">
         <v>22.66</v>
       </c>
       <c r="O23" s="279">
         <v>17.81</v>
       </c>
-      <c r="P23" s="280">
+      <c r="P23" s="285">
         <v>9.17</v>
       </c>
-      <c r="Q23" s="274">
+      <c r="Q23" s="275">
         <v>12.59</v>
       </c>
-      <c r="R23" s="275">
+      <c r="R23" s="276">
         <v>7.01</v>
       </c>
-      <c r="S23" s="281">
+      <c r="S23" s="286">
         <v>8.09</v>
       </c>
-      <c r="T23" s="282">
+      <c r="T23" s="280">
         <v>-38.13</v>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       <c r="C24" t="str">
         <v>920020</v>
       </c>
-      <c r="D24" s="294" t="str">
+      <c r="D24" s="298" t="str">
         <v>净卖: -668.61万</v>
       </c>
       <c r="E24">
@@ -9437,40 +9437,40 @@
       <c r="H24">
         <v>-9.66</v>
       </c>
-      <c r="I24" s="289">
+      <c r="I24" s="296">
         <v>14.02</v>
       </c>
-      <c r="J24" s="291">
+      <c r="J24" s="289">
         <v>2.92</v>
       </c>
-      <c r="K24" s="295">
+      <c r="K24" s="293">
         <v>1.38</v>
       </c>
-      <c r="L24" s="292">
+      <c r="L24" s="299">
         <v>0.51</v>
       </c>
       <c r="M24" s="290">
         <v>-0.82</v>
       </c>
-      <c r="N24" s="296">
+      <c r="N24" s="287">
         <v>-0.87</v>
       </c>
-      <c r="O24" s="293">
+      <c r="O24" s="291">
         <v>0.87</v>
       </c>
-      <c r="P24" s="297">
+      <c r="P24" s="288">
         <v>-2.4</v>
       </c>
-      <c r="Q24" s="298">
+      <c r="Q24" s="294">
         <v>-5.17</v>
       </c>
-      <c r="R24" s="299">
+      <c r="R24" s="295">
         <v>-4.76</v>
       </c>
-      <c r="S24" s="287">
+      <c r="S24" s="297">
         <v>-4.35</v>
       </c>
-      <c r="T24" s="288">
+      <c r="T24" s="292">
         <v>-18.47</v>
       </c>
     </row>
@@ -9484,7 +9484,7 @@
       <c r="C25" t="str">
         <v>605178</v>
       </c>
-      <c r="D25" s="305" t="str">
+      <c r="D25" s="300" t="str">
         <v>净买: 3874.18万</v>
       </c>
       <c r="E25">
@@ -9499,40 +9499,40 @@
       <c r="H25">
         <v>10</v>
       </c>
-      <c r="I25" s="309">
+      <c r="I25" s="311">
         <v>0</v>
       </c>
-      <c r="J25" s="310">
+      <c r="J25" s="301">
         <v>10</v>
       </c>
-      <c r="K25" s="312">
+      <c r="K25" s="302">
         <v>0.58</v>
       </c>
       <c r="L25" s="306">
         <v>4.74</v>
       </c>
-      <c r="M25" s="301">
+      <c r="M25" s="303">
         <v>13.42</v>
       </c>
-      <c r="N25" s="302">
+      <c r="N25" s="307">
         <v>19.72</v>
       </c>
-      <c r="O25" s="307">
+      <c r="O25" s="308">
         <v>26.01</v>
       </c>
-      <c r="P25" s="311">
+      <c r="P25" s="309">
         <v>16.89</v>
       </c>
-      <c r="Q25" s="308">
+      <c r="Q25" s="304">
         <v>6.52</v>
       </c>
-      <c r="R25" s="303">
+      <c r="R25" s="310">
         <v>10.9</v>
       </c>
-      <c r="S25" s="300">
+      <c r="S25" s="312">
         <v>12.81</v>
       </c>
-      <c r="T25" s="304">
+      <c r="T25" s="305">
         <v>36.81</v>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       <c r="C26" t="str">
         <v>000407</v>
       </c>
-      <c r="D26" s="322" t="str">
+      <c r="D26" s="320" t="str">
         <v>净买: 788.81万</v>
       </c>
       <c r="E26">
@@ -9561,40 +9561,40 @@
       <c r="H26">
         <v>10.1</v>
       </c>
-      <c r="I26" s="313">
+      <c r="I26" s="317">
         <v>0</v>
       </c>
-      <c r="J26" s="321">
+      <c r="J26" s="324">
         <v>10.04</v>
       </c>
-      <c r="K26" s="323">
+      <c r="K26" s="321">
         <v>20.96</v>
       </c>
-      <c r="L26" s="314">
+      <c r="L26" s="325">
         <v>32.97</v>
       </c>
-      <c r="M26" s="324">
+      <c r="M26" s="322">
         <v>46.29</v>
       </c>
-      <c r="N26" s="315">
+      <c r="N26" s="323">
         <v>31.66</v>
       </c>
-      <c r="O26" s="325">
+      <c r="O26" s="314">
         <v>30.35</v>
       </c>
-      <c r="P26" s="316">
+      <c r="P26" s="318">
         <v>17.25</v>
       </c>
-      <c r="Q26" s="317">
+      <c r="Q26" s="319">
         <v>5.46</v>
       </c>
-      <c r="R26" s="318">
+      <c r="R26" s="315">
         <v>5.9</v>
       </c>
-      <c r="S26" s="319">
+      <c r="S26" s="316">
         <v>12.45</v>
       </c>
-      <c r="T26" s="320">
+      <c r="T26" s="313">
         <v>1.31</v>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="335" t="str">
+      <c r="D27" s="327" t="str">
         <v>净买: 3123.85万</v>
       </c>
       <c r="E27">
@@ -9623,40 +9623,40 @@
       <c r="H27">
         <v>9.96</v>
       </c>
-      <c r="I27" s="331">
+      <c r="I27" s="333">
         <v>0</v>
       </c>
-      <c r="J27" s="332">
+      <c r="J27" s="328">
         <v>-9.95</v>
       </c>
-      <c r="K27" s="333">
+      <c r="K27" s="334">
         <v>-19.01</v>
       </c>
-      <c r="L27" s="327">
+      <c r="L27" s="329">
         <v>-27.04</v>
       </c>
-      <c r="M27" s="337">
+      <c r="M27" s="335">
         <v>-30.61</v>
       </c>
-      <c r="N27" s="338">
+      <c r="N27" s="337">
         <v>-28.7</v>
       </c>
-      <c r="O27" s="326">
+      <c r="O27" s="330">
         <v>-31.89</v>
       </c>
-      <c r="P27" s="328">
+      <c r="P27" s="338">
         <v>-31.63</v>
       </c>
-      <c r="Q27" s="336">
+      <c r="Q27" s="331">
         <v>-28.95</v>
       </c>
-      <c r="R27" s="334">
+      <c r="R27" s="336">
         <v>-26.53</v>
       </c>
-      <c r="S27" s="329">
+      <c r="S27" s="332">
         <v>-24.49</v>
       </c>
-      <c r="T27" s="330">
+      <c r="T27" s="326">
         <v>-24.23</v>
       </c>
     </row>
@@ -9670,7 +9670,7 @@
       <c r="C28" t="str">
         <v>300094</v>
       </c>
-      <c r="D28" s="341" t="str">
+      <c r="D28" s="345" t="str">
         <v>净卖: -3846.51万</v>
       </c>
       <c r="E28">
@@ -9685,37 +9685,37 @@
       <c r="H28">
         <v>0.37</v>
       </c>
-      <c r="I28" s="347">
+      <c r="I28" s="346">
         <v>-11.85</v>
       </c>
-      <c r="J28" s="342">
+      <c r="J28" s="339">
         <v>-12.41</v>
       </c>
       <c r="K28" s="350">
         <v>-8.33</v>
       </c>
-      <c r="L28" s="348">
+      <c r="L28" s="340">
         <v>-17.96</v>
       </c>
-      <c r="M28" s="343">
+      <c r="M28" s="347">
         <v>-23.89</v>
       </c>
-      <c r="N28" s="351">
+      <c r="N28" s="341">
         <v>-22.96</v>
       </c>
-      <c r="O28" s="344">
+      <c r="O28" s="342">
         <v>-24.26</v>
       </c>
-      <c r="P28" s="339">
+      <c r="P28" s="351">
         <v>-23.15</v>
       </c>
-      <c r="Q28" s="345">
+      <c r="Q28" s="348">
         <v>-21.48</v>
       </c>
-      <c r="R28" s="340">
+      <c r="R28" s="343">
         <v>-21.85</v>
       </c>
-      <c r="S28" s="346">
+      <c r="S28" s="344">
         <v>-27.78</v>
       </c>
       <c r="T28" s="349">
@@ -9747,37 +9747,37 @@
       <c r="H29">
         <v>-6.94</v>
       </c>
-      <c r="I29" s="360">
+      <c r="I29" s="357">
         <v>-3.35</v>
       </c>
-      <c r="J29" s="354">
+      <c r="J29" s="358">
         <v>-12.94</v>
       </c>
-      <c r="K29" s="357">
+      <c r="K29" s="354">
         <v>-17.2</v>
       </c>
-      <c r="L29" s="355">
+      <c r="L29" s="359">
         <v>-14.92</v>
       </c>
-      <c r="M29" s="363">
+      <c r="M29" s="360">
         <v>-18.72</v>
       </c>
-      <c r="N29" s="358">
+      <c r="N29" s="364">
         <v>-18.42</v>
       </c>
-      <c r="O29" s="359">
+      <c r="O29" s="361">
         <v>-15.22</v>
       </c>
-      <c r="P29" s="361">
+      <c r="P29" s="352">
         <v>-12.33</v>
       </c>
-      <c r="Q29" s="364">
+      <c r="Q29" s="355">
         <v>-9.89</v>
       </c>
-      <c r="R29" s="352">
+      <c r="R29" s="362">
         <v>-0.91</v>
       </c>
-      <c r="S29" s="362">
+      <c r="S29" s="363">
         <v>8.98</v>
       </c>
       <c r="T29" s="353">
@@ -9794,7 +9794,7 @@
       <c r="C30" t="str">
         <v>603069</v>
       </c>
-      <c r="D30" s="366" t="str">
+      <c r="D30" s="374" t="str">
         <v>净买: 2184.48万</v>
       </c>
       <c r="E30">
@@ -9809,40 +9809,40 @@
       <c r="H30">
         <v>10.02</v>
       </c>
-      <c r="I30" s="367">
+      <c r="I30" s="365">
         <v>0</v>
       </c>
-      <c r="J30" s="368">
+      <c r="J30" s="375">
         <v>1.25</v>
       </c>
-      <c r="K30" s="377">
+      <c r="K30" s="376">
         <v>-4.36</v>
       </c>
-      <c r="L30" s="374">
+      <c r="L30" s="368">
         <v>5.19</v>
       </c>
-      <c r="M30" s="372">
+      <c r="M30" s="369">
         <v>-1.42</v>
       </c>
-      <c r="N30" s="375">
+      <c r="N30" s="370">
         <v>-5.96</v>
       </c>
-      <c r="O30" s="376">
+      <c r="O30" s="373">
         <v>-5.99</v>
       </c>
-      <c r="P30" s="369">
+      <c r="P30" s="371">
         <v>-13.57</v>
       </c>
-      <c r="Q30" s="370">
+      <c r="Q30" s="377">
         <v>-13.64</v>
       </c>
-      <c r="R30" s="371">
+      <c r="R30" s="366">
         <v>-14.16</v>
       </c>
-      <c r="S30" s="373">
+      <c r="S30" s="367">
         <v>-15.27</v>
       </c>
-      <c r="T30" s="365">
+      <c r="T30" s="372">
         <v>-39.23</v>
       </c>
     </row>
@@ -9856,7 +9856,7 @@
       <c r="C31" t="str">
         <v>002009</v>
       </c>
-      <c r="D31" s="390" t="str">
+      <c r="D31" s="382" t="str">
         <v>净买: 3463.54万</v>
       </c>
       <c r="E31">
@@ -9871,40 +9871,40 @@
       <c r="H31">
         <v>10</v>
       </c>
-      <c r="I31" s="383">
+      <c r="I31" s="379">
         <v>0</v>
       </c>
-      <c r="J31" s="379">
+      <c r="J31" s="383">
         <v>10.02</v>
       </c>
-      <c r="K31" s="384">
+      <c r="K31" s="388">
         <v>21.02</v>
       </c>
-      <c r="L31" s="378">
+      <c r="L31" s="389">
         <v>16.84</v>
       </c>
-      <c r="M31" s="380">
+      <c r="M31" s="390">
         <v>14.72</v>
       </c>
-      <c r="N31" s="385">
+      <c r="N31" s="384">
         <v>8.01</v>
       </c>
-      <c r="O31" s="386">
+      <c r="O31" s="380">
         <v>12.24</v>
       </c>
-      <c r="P31" s="381">
+      <c r="P31" s="378">
         <v>12.65</v>
       </c>
-      <c r="Q31" s="387">
+      <c r="Q31" s="385">
         <v>15.19</v>
       </c>
-      <c r="R31" s="389">
+      <c r="R31" s="381">
         <v>18.85</v>
       </c>
-      <c r="S31" s="388">
+      <c r="S31" s="386">
         <v>11.93</v>
       </c>
-      <c r="T31" s="382">
+      <c r="T31" s="387">
         <v>27.01</v>
       </c>
     </row>
@@ -9918,7 +9918,7 @@
       <c r="C32" t="str">
         <v>002009</v>
       </c>
-      <c r="D32" s="395" t="str">
+      <c r="D32" s="393" t="str">
         <v>净卖: -4207.08万</v>
       </c>
       <c r="E32">
@@ -9933,25 +9933,25 @@
       <c r="H32">
         <v>9.92</v>
       </c>
-      <c r="I32" s="398">
+      <c r="I32" s="400">
         <v>0.09</v>
       </c>
-      <c r="J32" s="400">
+      <c r="J32" s="401">
         <v>10.1</v>
       </c>
-      <c r="K32" s="401">
+      <c r="K32" s="394">
         <v>6.3</v>
       </c>
       <c r="L32" s="402">
         <v>4.37</v>
       </c>
-      <c r="M32" s="399">
+      <c r="M32" s="391">
         <v>-1.74</v>
       </c>
-      <c r="N32" s="403">
+      <c r="N32" s="398">
         <v>2.11</v>
       </c>
-      <c r="O32" s="391">
+      <c r="O32" s="395">
         <v>2.49</v>
       </c>
       <c r="P32" s="392">
@@ -9960,13 +9960,13 @@
       <c r="Q32" s="396">
         <v>8.13</v>
       </c>
-      <c r="R32" s="397">
+      <c r="R32" s="403">
         <v>1.83</v>
       </c>
-      <c r="S32" s="393">
+      <c r="S32" s="397">
         <v>2.63</v>
       </c>
-      <c r="T32" s="394">
+      <c r="T32" s="399">
         <v>15.55</v>
       </c>
     </row>
@@ -9995,40 +9995,40 @@
       <c r="H33">
         <v>2.21</v>
       </c>
-      <c r="I33" s="410">
+      <c r="I33" s="408">
         <v>7.63</v>
       </c>
-      <c r="J33" s="415">
+      <c r="J33" s="404">
         <v>3.9</v>
       </c>
-      <c r="K33" s="411">
+      <c r="K33" s="409">
         <v>2.02</v>
       </c>
-      <c r="L33" s="407">
+      <c r="L33" s="410">
         <v>-3.95</v>
       </c>
-      <c r="M33" s="416">
+      <c r="M33" s="412">
         <v>-0.18</v>
       </c>
-      <c r="N33" s="404">
+      <c r="N33" s="405">
         <v>0.18</v>
       </c>
-      <c r="O33" s="405">
+      <c r="O33" s="413">
         <v>2.43</v>
       </c>
-      <c r="P33" s="412">
+      <c r="P33" s="406">
         <v>5.7</v>
       </c>
-      <c r="Q33" s="406">
+      <c r="Q33" s="407">
         <v>-0.46</v>
       </c>
-      <c r="R33" s="413">
+      <c r="R33" s="415">
         <v>0.32</v>
       </c>
-      <c r="S33" s="408">
+      <c r="S33" s="416">
         <v>-1.52</v>
       </c>
-      <c r="T33" s="409">
+      <c r="T33" s="411">
         <v>12.95</v>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       <c r="C34" t="str">
         <v>002969</v>
       </c>
-      <c r="D34" s="419" t="str">
+      <c r="D34" s="423" t="str">
         <v>净卖: -2752.13万</v>
       </c>
       <c r="E34">
@@ -10057,40 +10057,40 @@
       <c r="H34">
         <v>0.55</v>
       </c>
-      <c r="I34" s="427">
+      <c r="I34" s="429">
         <v>7.62</v>
       </c>
-      <c r="J34" s="418">
+      <c r="J34" s="424">
         <v>18.38</v>
       </c>
-      <c r="K34" s="421">
+      <c r="K34" s="417">
         <v>30.24</v>
       </c>
-      <c r="L34" s="422">
+      <c r="L34" s="425">
         <v>37.86</v>
       </c>
-      <c r="M34" s="428">
+      <c r="M34" s="426">
         <v>51.69</v>
       </c>
-      <c r="N34" s="423">
+      <c r="N34" s="427">
         <v>36.53</v>
       </c>
-      <c r="O34" s="424">
+      <c r="O34" s="421">
         <v>22.86</v>
       </c>
-      <c r="P34" s="420">
+      <c r="P34" s="418">
         <v>35.11</v>
       </c>
-      <c r="Q34" s="429">
+      <c r="Q34" s="428">
         <v>48.63</v>
       </c>
-      <c r="R34" s="417">
+      <c r="R34" s="419">
         <v>52.47</v>
       </c>
-      <c r="S34" s="425">
+      <c r="S34" s="420">
         <v>67.71</v>
       </c>
-      <c r="T34" s="426">
+      <c r="T34" s="422">
         <v>77.3</v>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       <c r="C35" t="str">
         <v>600683</v>
       </c>
-      <c r="D35" s="435" t="str">
+      <c r="D35" s="439" t="str">
         <v>净买: 819.30万</v>
       </c>
       <c r="E35">
@@ -10122,37 +10122,37 @@
       <c r="I35" s="440">
         <v>0</v>
       </c>
-      <c r="J35" s="441">
+      <c r="J35" s="431">
         <v>10.09</v>
       </c>
-      <c r="K35" s="442">
+      <c r="K35" s="433">
         <v>21.1</v>
       </c>
-      <c r="L35" s="430">
+      <c r="L35" s="436">
         <v>11.01</v>
       </c>
-      <c r="M35" s="436">
+      <c r="M35" s="437">
         <v>22.2</v>
       </c>
-      <c r="N35" s="437">
+      <c r="N35" s="438">
         <v>22.57</v>
       </c>
-      <c r="O35" s="431">
+      <c r="O35" s="441">
         <v>32.29</v>
       </c>
-      <c r="P35" s="432">
+      <c r="P35" s="434">
         <v>27.16</v>
       </c>
-      <c r="Q35" s="433">
+      <c r="Q35" s="442">
         <v>23.12</v>
       </c>
-      <c r="R35" s="434">
+      <c r="R35" s="430">
         <v>30.46</v>
       </c>
-      <c r="S35" s="438">
+      <c r="S35" s="432">
         <v>37.06</v>
       </c>
-      <c r="T35" s="439">
+      <c r="T35" s="435">
         <v>120</v>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
       <c r="C36" t="str">
         <v>002056</v>
       </c>
-      <c r="D36" s="450" t="str">
+      <c r="D36" s="445" t="str">
         <v>净卖: -2838.92万</v>
       </c>
       <c r="E36">
@@ -10184,37 +10184,37 @@
       <c r="I36" s="451">
         <v>8.62</v>
       </c>
-      <c r="J36" s="449">
+      <c r="J36" s="452">
         <v>-0.42</v>
       </c>
-      <c r="K36" s="452">
+      <c r="K36" s="446">
         <v>-4.25</v>
       </c>
-      <c r="L36" s="443">
+      <c r="L36" s="447">
         <v>-5.84</v>
       </c>
       <c r="M36" s="453">
         <v>-8.66</v>
       </c>
-      <c r="N36" s="444">
+      <c r="N36" s="454">
         <v>-6.43</v>
       </c>
-      <c r="O36" s="454">
+      <c r="O36" s="448">
         <v>-9.21</v>
       </c>
-      <c r="P36" s="455">
+      <c r="P36" s="449">
         <v>-9.21</v>
       </c>
-      <c r="Q36" s="445">
+      <c r="Q36" s="450">
         <v>-7.78</v>
       </c>
-      <c r="R36" s="446">
+      <c r="R36" s="443">
         <v>-9.46</v>
       </c>
-      <c r="S36" s="447">
+      <c r="S36" s="444">
         <v>-9.92</v>
       </c>
-      <c r="T36" s="448">
+      <c r="T36" s="455">
         <v>-18.5</v>
       </c>
     </row>
@@ -10277,40 +10277,40 @@
       <c r="F38" t="str"/>
       <c r="G38" t="str"/>
       <c r="H38" t="str"/>
-      <c r="I38" s="458">
+      <c r="I38" s="464">
         <v>31.43</v>
       </c>
-      <c r="J38" s="459">
+      <c r="J38" s="457">
         <v>62.86</v>
       </c>
-      <c r="K38" s="460">
+      <c r="K38" s="462">
         <v>54.29</v>
       </c>
-      <c r="L38" s="464">
+      <c r="L38" s="463">
         <v>54.29</v>
       </c>
-      <c r="M38" s="465">
+      <c r="M38" s="458">
         <v>42.86</v>
       </c>
-      <c r="N38" s="461">
+      <c r="N38" s="459">
         <v>42.86</v>
       </c>
-      <c r="O38" s="466">
+      <c r="O38" s="467">
         <v>48.57</v>
       </c>
-      <c r="P38" s="462">
+      <c r="P38" s="460">
         <v>37.14</v>
       </c>
-      <c r="Q38" s="463">
+      <c r="Q38" s="456">
         <v>31.43</v>
       </c>
-      <c r="R38" s="467">
+      <c r="R38" s="461">
         <v>34.29</v>
       </c>
-      <c r="S38" s="456">
+      <c r="S38" s="465">
         <v>31.43</v>
       </c>
-      <c r="T38" s="457">
+      <c r="T38" s="466">
         <v>48.57</v>
       </c>
     </row>
@@ -10325,40 +10325,40 @@
       <c r="F39" t="str"/>
       <c r="G39" t="str"/>
       <c r="H39" t="str"/>
-      <c r="I39" s="470">
+      <c r="I39" s="469">
         <v>0.72</v>
       </c>
       <c r="J39" s="478">
         <v>1.7</v>
       </c>
-      <c r="K39" s="479">
+      <c r="K39" s="470">
         <v>1.83</v>
       </c>
-      <c r="L39" s="474">
+      <c r="L39" s="479">
         <v>1.8</v>
       </c>
-      <c r="M39" s="475">
+      <c r="M39" s="468">
         <v>1.64</v>
       </c>
-      <c r="N39" s="476">
+      <c r="N39" s="475">
         <v>0.36</v>
       </c>
-      <c r="O39" s="468">
+      <c r="O39" s="476">
         <v>0.46</v>
       </c>
       <c r="P39" s="471">
         <v>-2.04</v>
       </c>
-      <c r="Q39" s="469">
+      <c r="Q39" s="472">
         <v>-3.24</v>
       </c>
-      <c r="R39" s="472">
+      <c r="R39" s="473">
         <v>-2.68</v>
       </c>
-      <c r="S39" s="477">
+      <c r="S39" s="474">
         <v>-2.27</v>
       </c>
-      <c r="T39" s="473">
+      <c r="T39" s="477">
         <v>10.81</v>
       </c>
     </row>

--- a/youzi/正经哥/index.xlsx
+++ b/youzi/正经哥/index.xlsx
@@ -45,7 +45,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF36AC51"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,25 +117,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF36AC51"/>
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,13 +171,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,19 +261,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,37 +291,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,31 +345,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFEBF6ED"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -231,25 +375,1789 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -261,37 +2169,343 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBF8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -303,31 +2517,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -339,85 +2679,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -429,595 +2763,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4654"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1029,1885 +2907,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7FBF8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4654"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8058,7 +8058,7 @@
       <c r="C2" t="str">
         <v>000665</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="8" t="str">
         <v>净卖: -2301.68万</v>
       </c>
       <c r="E2">
@@ -8073,41 +8073,41 @@
       <c r="H2">
         <v>10.06</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="3">
         <v>10</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="1">
         <v>21.03</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="10">
         <v>30</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="6">
         <v>18.79</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="4">
         <v>10</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="5">
         <v>11.72</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="11">
         <v>10.17</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="2">
         <v>2.07</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="12">
         <v>-4.66</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="13">
         <v>-8.45</v>
       </c>
-      <c r="T2" s="4">
-        <v>-18.1</v>
+      <c r="T2" s="7">
+        <v>-17.93</v>
       </c>
     </row>
     <row r="3">
@@ -8120,7 +8120,7 @@
       <c r="C3" t="str">
         <v>002300</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="25" t="str">
         <v>净买: 2299.17万</v>
       </c>
       <c r="E3">
@@ -8135,41 +8135,41 @@
       <c r="H3">
         <v>9.95</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="22">
         <v>0</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="20">
         <v>10.06</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="26">
         <v>21.12</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="14">
         <v>9.77</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="15">
         <v>-1.15</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="16">
         <v>-8.76</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="23">
         <v>-11.35</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="21">
         <v>-12.36</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="17">
         <v>-13.22</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="18">
         <v>-21.84</v>
       </c>
       <c r="S3" s="24">
         <v>-23.99</v>
       </c>
-      <c r="T3" s="25">
-        <v>36.06</v>
+      <c r="T3" s="19">
+        <v>49.71</v>
       </c>
     </row>
     <row r="4">
@@ -8182,7 +8182,7 @@
       <c r="C4" t="str">
         <v>002300</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="37" t="str">
         <v>净卖: -2576.68万</v>
       </c>
       <c r="E4">
@@ -8197,41 +8197,41 @@
       <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="28">
         <v>9.34</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="31">
         <v>-0.91</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="38">
         <v>-10.77</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="29">
         <v>-17.64</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="39">
         <v>-19.97</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="32">
         <v>-20.88</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="30">
         <v>-21.66</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="33">
         <v>-29.44</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="34">
         <v>-31.39</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="35">
         <v>-28.92</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="36">
         <v>-27.63</v>
       </c>
-      <c r="T4" s="28">
-        <v>22.83</v>
+      <c r="T4" s="27">
+        <v>35.15</v>
       </c>
     </row>
     <row r="5">
@@ -8244,7 +8244,7 @@
       <c r="C5" t="str">
         <v>002688</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="41" t="str">
         <v>净买: 5775.20万</v>
       </c>
       <c r="E5">
@@ -8262,38 +8262,38 @@
       <c r="I5" s="51">
         <v>0</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="47">
         <v>9.95</v>
       </c>
       <c r="K5" s="42">
         <v>20.98</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="48">
         <v>30.17</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="49">
         <v>17.15</v>
       </c>
       <c r="N5" s="43">
         <v>8.58</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="46">
         <v>10.57</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="52">
         <v>-0.46</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="50">
         <v>-5.36</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="40">
         <v>-5.05</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="44">
         <v>-4.29</v>
       </c>
-      <c r="T5" s="49">
-        <v>-10.11</v>
+      <c r="T5" s="45">
+        <v>-10.57</v>
       </c>
     </row>
     <row r="6">
@@ -8306,7 +8306,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="65" t="str">
+      <c r="D6" s="53" t="str">
         <v>净卖: -7396.08万</v>
       </c>
       <c r="E6">
@@ -8321,41 +8321,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="57">
         <v>7.59</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="64">
         <v>-3.16</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="58">
         <v>-10.25</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="59">
         <v>-8.61</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="60">
         <v>-17.72</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="54">
         <v>-21.77</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="65">
         <v>-21.52</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="55">
         <v>-20.89</v>
       </c>
-      <c r="Q6" s="61">
+      <c r="Q6" s="56">
         <v>-16.71</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="62">
         <v>-20.76</v>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="63">
         <v>-17.09</v>
       </c>
-      <c r="T6" s="54">
-        <v>-25.7</v>
+      <c r="T6" s="61">
+        <v>-26.08</v>
       </c>
     </row>
     <row r="7">
@@ -8368,7 +8368,7 @@
       <c r="C7" t="str">
         <v>600697</v>
       </c>
-      <c r="D7" s="78" t="str">
+      <c r="D7" s="75" t="str">
         <v>净卖: -2819.93万</v>
       </c>
       <c r="E7">
@@ -8383,41 +8383,41 @@
       <c r="H7">
         <v>-9.28</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="71">
         <v>3.2</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="73">
         <v>6.95</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="76">
         <v>17.66</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="74">
         <v>13.12</v>
       </c>
-      <c r="M7" s="74">
+      <c r="M7" s="77">
         <v>1.95</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="78">
         <v>0</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="68">
         <v>4.3</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="69">
         <v>-1.72</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="66">
         <v>-5.31</v>
       </c>
-      <c r="R7" s="69">
+      <c r="R7" s="70">
         <v>-5.23</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="67">
         <v>-7.97</v>
       </c>
-      <c r="T7" s="77">
-        <v>-8.2</v>
+      <c r="T7" s="72">
+        <v>-7.5</v>
       </c>
     </row>
     <row r="8">
@@ -8430,7 +8430,7 @@
       <c r="C8" t="str">
         <v>600828</v>
       </c>
-      <c r="D8" s="83" t="str">
+      <c r="D8" s="87" t="str">
         <v>净买: 1425.83万</v>
       </c>
       <c r="E8">
@@ -8445,19 +8445,19 @@
       <c r="H8">
         <v>10.11</v>
       </c>
-      <c r="I8" s="90">
+      <c r="I8" s="79">
         <v>0</v>
       </c>
       <c r="J8" s="81">
         <v>10.02</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="82">
         <v>7.31</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="88">
         <v>5.01</v>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="83">
         <v>10.65</v>
       </c>
       <c r="N8" s="84">
@@ -8466,20 +8466,20 @@
       <c r="O8" s="85">
         <v>-5.01</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="89">
         <v>-10.02</v>
       </c>
-      <c r="Q8" s="89">
+      <c r="Q8" s="80">
         <v>-12.73</v>
       </c>
-      <c r="R8" s="79">
+      <c r="R8" s="90">
         <v>-11.69</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="86">
         <v>-10.65</v>
       </c>
-      <c r="T8" s="82">
-        <v>10.23</v>
+      <c r="T8" s="91">
+        <v>8.77</v>
       </c>
     </row>
     <row r="9">
@@ -8492,7 +8492,7 @@
       <c r="C9" t="str">
         <v>600828</v>
       </c>
-      <c r="D9" s="98" t="str">
+      <c r="D9" s="94" t="str">
         <v>净卖: -1514.63万</v>
       </c>
       <c r="E9">
@@ -8507,41 +8507,41 @@
       <c r="H9">
         <v>-0.21</v>
       </c>
-      <c r="I9" s="99">
+      <c r="I9" s="102">
         <v>10.25</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="99">
         <v>7.53</v>
       </c>
-      <c r="K9" s="101">
+      <c r="K9" s="100">
         <v>5.23</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="104">
         <v>10.88</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="103">
         <v>5.65</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="92">
         <v>-4.81</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="95">
         <v>-9.83</v>
       </c>
-      <c r="P9" s="102">
+      <c r="P9" s="96">
         <v>-12.55</v>
       </c>
-      <c r="Q9" s="97">
+      <c r="Q9" s="101">
         <v>-11.51</v>
       </c>
-      <c r="R9" s="100">
+      <c r="R9" s="97">
         <v>-10.46</v>
       </c>
-      <c r="S9" s="103">
+      <c r="S9" s="93">
         <v>-12.34</v>
       </c>
-      <c r="T9" s="104">
-        <v>10.46</v>
+      <c r="T9" s="98">
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -8554,7 +8554,7 @@
       <c r="C10" t="str">
         <v>002909</v>
       </c>
-      <c r="D10" s="116" t="str">
+      <c r="D10" s="105" t="str">
         <v>净卖: -879.53万</v>
       </c>
       <c r="E10">
@@ -8569,41 +8569,41 @@
       <c r="H10">
         <v>-1.91</v>
       </c>
-      <c r="I10" s="117">
+      <c r="I10" s="109">
         <v>-8.28</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="115">
         <v>-16.44</v>
       </c>
-      <c r="K10" s="114">
+      <c r="K10" s="110">
         <v>-21.07</v>
       </c>
-      <c r="L10" s="115">
+      <c r="L10" s="112">
         <v>-21.8</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="116">
         <v>-23.39</v>
       </c>
-      <c r="N10" s="105">
+      <c r="N10" s="113">
         <v>-23.02</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="106">
         <v>-22.66</v>
       </c>
-      <c r="P10" s="106">
+      <c r="P10" s="107">
         <v>-23.87</v>
       </c>
-      <c r="Q10" s="107">
+      <c r="Q10" s="108">
         <v>-23.26</v>
       </c>
-      <c r="R10" s="113">
+      <c r="R10" s="117">
         <v>-24.12</v>
       </c>
-      <c r="S10" s="110">
+      <c r="S10" s="111">
         <v>-23.87</v>
       </c>
-      <c r="T10" s="108">
-        <v>-22.41</v>
+      <c r="T10" s="114">
+        <v>-20.1</v>
       </c>
     </row>
     <row r="11">
@@ -8616,7 +8616,7 @@
       <c r="C11" t="str">
         <v>603639</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="119" t="str">
         <v>净买: 1633.37万</v>
       </c>
       <c r="E11">
@@ -8631,41 +8631,41 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="121">
+      <c r="I11" s="123">
         <v>0</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="127">
         <v>-6.63</v>
       </c>
-      <c r="K11" s="125">
+      <c r="K11" s="124">
         <v>-12.9</v>
       </c>
-      <c r="L11" s="122">
+      <c r="L11" s="129">
         <v>-12.16</v>
       </c>
-      <c r="M11" s="123">
+      <c r="M11" s="125">
         <v>-13.76</v>
       </c>
-      <c r="N11" s="126">
+      <c r="N11" s="120">
         <v>-9.83</v>
       </c>
       <c r="O11" s="128">
         <v>-10.63</v>
       </c>
-      <c r="P11" s="129">
+      <c r="P11" s="130">
         <v>-9.46</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="121">
         <v>-10.44</v>
       </c>
-      <c r="R11" s="119">
+      <c r="R11" s="122">
         <v>-10.01</v>
       </c>
-      <c r="S11" s="120">
+      <c r="S11" s="126">
         <v>-8.17</v>
       </c>
-      <c r="T11" s="130">
-        <v>-18.92</v>
+      <c r="T11" s="118">
+        <v>-19.41</v>
       </c>
     </row>
     <row r="12">
@@ -8696,38 +8696,38 @@
       <c r="I12" s="135">
         <v>0</v>
       </c>
-      <c r="J12" s="131">
+      <c r="J12" s="143">
         <v>3.19</v>
       </c>
-      <c r="K12" s="141">
+      <c r="K12" s="139">
         <v>6.23</v>
       </c>
-      <c r="L12" s="139">
+      <c r="L12" s="131">
         <v>16.81</v>
       </c>
-      <c r="M12" s="136">
+      <c r="M12" s="140">
         <v>18.99</v>
       </c>
-      <c r="N12" s="132">
+      <c r="N12" s="141">
         <v>30.87</v>
       </c>
-      <c r="O12" s="137">
+      <c r="O12" s="136">
         <v>43.91</v>
       </c>
-      <c r="P12" s="133">
+      <c r="P12" s="142">
         <v>42.17</v>
       </c>
-      <c r="Q12" s="142">
+      <c r="Q12" s="132">
         <v>36.52</v>
       </c>
-      <c r="R12" s="140">
+      <c r="R12" s="137">
         <v>43.48</v>
       </c>
-      <c r="S12" s="138">
+      <c r="S12" s="133">
         <v>44.93</v>
       </c>
-      <c r="T12" s="143">
-        <v>37.1</v>
+      <c r="T12" s="138">
+        <v>40.14</v>
       </c>
     </row>
     <row r="13">
@@ -8740,7 +8740,7 @@
       <c r="C13" t="str">
         <v>603776</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="148" t="str">
         <v>净买: 1894.22万</v>
       </c>
       <c r="E13">
@@ -8755,41 +8755,41 @@
       <c r="H13">
         <v>10</v>
       </c>
-      <c r="I13" s="147">
+      <c r="I13" s="153">
         <v>0</v>
       </c>
-      <c r="J13" s="151">
+      <c r="J13" s="149">
         <v>-9.72</v>
       </c>
-      <c r="K13" s="152">
+      <c r="K13" s="154">
         <v>-10.95</v>
       </c>
-      <c r="L13" s="154">
+      <c r="L13" s="150">
         <v>-8.45</v>
       </c>
-      <c r="M13" s="144">
+      <c r="M13" s="155">
         <v>-7.04</v>
       </c>
-      <c r="N13" s="145">
+      <c r="N13" s="156">
         <v>-11.27</v>
       </c>
-      <c r="O13" s="146">
+      <c r="O13" s="151">
         <v>-2.41</v>
       </c>
-      <c r="P13" s="155">
+      <c r="P13" s="152">
         <v>2.36</v>
       </c>
-      <c r="Q13" s="148">
+      <c r="Q13" s="144">
         <v>-2.64</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="145">
         <v>-2.32</v>
       </c>
-      <c r="S13" s="150">
+      <c r="S13" s="146">
         <v>-2.23</v>
       </c>
-      <c r="T13" s="153">
-        <v>-8.86</v>
+      <c r="T13" s="147">
+        <v>-7.81</v>
       </c>
     </row>
     <row r="14">
@@ -8802,7 +8802,7 @@
       <c r="C14" t="str">
         <v>603776</v>
       </c>
-      <c r="D14" s="157" t="str">
+      <c r="D14" s="160" t="str">
         <v>净卖: -2197.25万</v>
       </c>
       <c r="E14">
@@ -8817,41 +8817,41 @@
       <c r="H14">
         <v>-2.32</v>
       </c>
-      <c r="I14" s="166">
+      <c r="I14" s="165">
         <v>-7.58</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="157">
         <v>-8.84</v>
       </c>
-      <c r="K14" s="163">
+      <c r="K14" s="161">
         <v>-6.28</v>
       </c>
-      <c r="L14" s="158">
+      <c r="L14" s="166">
         <v>-4.84</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="158">
         <v>-9.16</v>
       </c>
       <c r="N14" s="167">
         <v>-0.09</v>
       </c>
-      <c r="O14" s="168">
+      <c r="O14" s="162">
         <v>4.79</v>
       </c>
-      <c r="P14" s="161">
+      <c r="P14" s="168">
         <v>-0.33</v>
       </c>
-      <c r="Q14" s="160">
+      <c r="Q14" s="169">
         <v>0</v>
       </c>
-      <c r="R14" s="169">
+      <c r="R14" s="159">
         <v>0.09</v>
       </c>
-      <c r="S14" s="164">
+      <c r="S14" s="163">
         <v>0</v>
       </c>
-      <c r="T14" s="165">
-        <v>-6.7</v>
+      <c r="T14" s="164">
+        <v>-5.63</v>
       </c>
     </row>
     <row r="15">
@@ -8864,7 +8864,7 @@
       <c r="C15" t="str">
         <v>001360</v>
       </c>
-      <c r="D15" s="178" t="str">
+      <c r="D15" s="172" t="str">
         <v>净买: 1803.24万</v>
       </c>
       <c r="E15">
@@ -8879,41 +8879,41 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="179">
+      <c r="I15" s="173">
         <v>0</v>
       </c>
-      <c r="J15" s="171">
+      <c r="J15" s="175">
         <v>10.01</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="179">
         <v>-0.95</v>
       </c>
-      <c r="L15" s="173">
+      <c r="L15" s="176">
         <v>-10.85</v>
       </c>
-      <c r="M15" s="180">
+      <c r="M15" s="182">
         <v>-13.18</v>
       </c>
-      <c r="N15" s="174">
+      <c r="N15" s="177">
         <v>-14.29</v>
       </c>
-      <c r="O15" s="181">
+      <c r="O15" s="180">
         <v>-15.25</v>
       </c>
-      <c r="P15" s="175">
+      <c r="P15" s="181">
         <v>-14.56</v>
       </c>
-      <c r="Q15" s="176">
+      <c r="Q15" s="170">
         <v>-16.52</v>
       </c>
-      <c r="R15" s="182">
+      <c r="R15" s="174">
         <v>-16.36</v>
       </c>
-      <c r="S15" s="170">
+      <c r="S15" s="178">
         <v>-16.15</v>
       </c>
-      <c r="T15" s="177">
-        <v>15.83</v>
+      <c r="T15" s="171">
+        <v>17.26</v>
       </c>
     </row>
     <row r="16">
@@ -8926,7 +8926,7 @@
       <c r="C16" t="str">
         <v>601669</v>
       </c>
-      <c r="D16" s="187" t="str">
+      <c r="D16" s="192" t="str">
         <v>净买: 9396.35万</v>
       </c>
       <c r="E16">
@@ -8941,41 +8941,41 @@
       <c r="H16">
         <v>10.08</v>
       </c>
-      <c r="I16" s="188">
+      <c r="I16" s="189">
         <v>0</v>
       </c>
-      <c r="J16" s="189">
+      <c r="J16" s="187">
         <v>10.04</v>
       </c>
-      <c r="K16" s="184">
+      <c r="K16" s="193">
         <v>6.65</v>
       </c>
       <c r="L16" s="190">
         <v>3.84</v>
       </c>
-      <c r="M16" s="191">
+      <c r="M16" s="194">
         <v>5.76</v>
       </c>
-      <c r="N16" s="192">
+      <c r="N16" s="195">
         <v>0.44</v>
       </c>
-      <c r="O16" s="185">
+      <c r="O16" s="183">
         <v>0.89</v>
       </c>
-      <c r="P16" s="195">
+      <c r="P16" s="184">
         <v>-3.69</v>
       </c>
-      <c r="Q16" s="193">
+      <c r="Q16" s="185">
         <v>-4.58</v>
       </c>
-      <c r="R16" s="186">
+      <c r="R16" s="188">
         <v>-5.17</v>
       </c>
-      <c r="S16" s="194">
+      <c r="S16" s="191">
         <v>-6.5</v>
       </c>
-      <c r="T16" s="183">
-        <v>-15.66</v>
+      <c r="T16" s="186">
+        <v>-14.33</v>
       </c>
     </row>
     <row r="17">
@@ -8988,7 +8988,7 @@
       <c r="C17" t="str">
         <v>001360</v>
       </c>
-      <c r="D17" s="206" t="str">
+      <c r="D17" s="197" t="str">
         <v>净卖: -1800.16万</v>
       </c>
       <c r="E17">
@@ -9003,41 +9003,41 @@
       <c r="H17">
         <v>0.1</v>
       </c>
-      <c r="I17" s="198">
+      <c r="I17" s="202">
         <v>-10.05</v>
       </c>
-      <c r="J17" s="196">
+      <c r="J17" s="198">
         <v>-19.04</v>
       </c>
-      <c r="K17" s="199">
+      <c r="K17" s="203">
         <v>-21.15</v>
       </c>
-      <c r="L17" s="207">
+      <c r="L17" s="204">
         <v>-22.16</v>
       </c>
-      <c r="M17" s="200">
+      <c r="M17" s="199">
         <v>-23.03</v>
       </c>
-      <c r="N17" s="204">
+      <c r="N17" s="207">
         <v>-22.4</v>
       </c>
-      <c r="O17" s="201">
+      <c r="O17" s="200">
         <v>-24.18</v>
       </c>
-      <c r="P17" s="197">
+      <c r="P17" s="208">
         <v>-24.04</v>
       </c>
-      <c r="Q17" s="208">
+      <c r="Q17" s="201">
         <v>-23.85</v>
       </c>
-      <c r="R17" s="202">
+      <c r="R17" s="205">
         <v>-24.28</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="206">
         <v>-24.47</v>
       </c>
-      <c r="T17" s="205">
-        <v>5.19</v>
+      <c r="T17" s="196">
+        <v>6.49</v>
       </c>
     </row>
     <row r="18">
@@ -9065,31 +9065,31 @@
       <c r="H18">
         <v>-9.14</v>
       </c>
-      <c r="I18" s="214">
+      <c r="I18" s="216">
         <v>-0.94</v>
       </c>
-      <c r="J18" s="215">
+      <c r="J18" s="212">
         <v>-3.53</v>
       </c>
-      <c r="K18" s="217">
+      <c r="K18" s="213">
         <v>-4.76</v>
       </c>
-      <c r="L18" s="218">
+      <c r="L18" s="209">
         <v>-5.82</v>
       </c>
-      <c r="M18" s="219">
+      <c r="M18" s="217">
         <v>-5.06</v>
       </c>
-      <c r="N18" s="209">
+      <c r="N18" s="218">
         <v>-7.24</v>
       </c>
-      <c r="O18" s="216">
+      <c r="O18" s="214">
         <v>-7.06</v>
       </c>
-      <c r="P18" s="210">
+      <c r="P18" s="219">
         <v>-6.82</v>
       </c>
-      <c r="Q18" s="212">
+      <c r="Q18" s="210">
         <v>-7.35</v>
       </c>
       <c r="R18" s="220">
@@ -9098,8 +9098,8 @@
       <c r="S18" s="221">
         <v>-6.59</v>
       </c>
-      <c r="T18" s="213">
-        <v>28.71</v>
+      <c r="T18" s="215">
+        <v>30.29</v>
       </c>
     </row>
     <row r="19">
@@ -9112,7 +9112,7 @@
       <c r="C19" t="str">
         <v>300620</v>
       </c>
-      <c r="D19" s="223" t="str">
+      <c r="D19" s="233" t="str">
         <v>净买: 1215.21万</v>
       </c>
       <c r="E19">
@@ -9127,41 +9127,41 @@
       <c r="H19">
         <v>19.99</v>
       </c>
-      <c r="I19" s="232">
+      <c r="I19" s="230">
         <v>0</v>
       </c>
-      <c r="J19" s="222">
+      <c r="J19" s="226">
         <v>20.01</v>
       </c>
-      <c r="K19" s="229">
+      <c r="K19" s="227">
         <v>21.14</v>
       </c>
-      <c r="L19" s="230">
+      <c r="L19" s="231">
         <v>24.09</v>
       </c>
-      <c r="M19" s="224">
+      <c r="M19" s="228">
         <v>46.79</v>
       </c>
-      <c r="N19" s="225">
+      <c r="N19" s="234">
         <v>50.73</v>
       </c>
-      <c r="O19" s="233">
+      <c r="O19" s="229">
         <v>40.57</v>
       </c>
-      <c r="P19" s="226">
+      <c r="P19" s="232">
         <v>31.96</v>
       </c>
-      <c r="Q19" s="234">
+      <c r="Q19" s="222">
         <v>34.41</v>
       </c>
-      <c r="R19" s="227">
+      <c r="R19" s="223">
         <v>39.6</v>
       </c>
-      <c r="S19" s="228">
+      <c r="S19" s="225">
         <v>34.69</v>
       </c>
-      <c r="T19" s="231">
-        <v>281.1</v>
+      <c r="T19" s="224">
+        <v>279.72</v>
       </c>
     </row>
     <row r="20">
@@ -9174,7 +9174,7 @@
       <c r="C20" t="str">
         <v>002177</v>
       </c>
-      <c r="D20" s="238" t="str">
+      <c r="D20" s="243" t="str">
         <v>净卖: -3762.63万</v>
       </c>
       <c r="E20">
@@ -9192,38 +9192,38 @@
       <c r="I20" s="235">
         <v>5.93</v>
       </c>
-      <c r="J20" s="242">
+      <c r="J20" s="244">
         <v>1.38</v>
       </c>
-      <c r="K20" s="241">
+      <c r="K20" s="236">
         <v>-1.17</v>
       </c>
-      <c r="L20" s="239">
+      <c r="L20" s="247">
         <v>-10.91</v>
       </c>
-      <c r="M20" s="240">
+      <c r="M20" s="237">
         <v>-11.76</v>
       </c>
-      <c r="N20" s="243">
+      <c r="N20" s="238">
         <v>-12.39</v>
       </c>
-      <c r="O20" s="244">
+      <c r="O20" s="239">
         <v>-9.96</v>
       </c>
-      <c r="P20" s="245">
+      <c r="P20" s="240">
         <v>-15.15</v>
       </c>
-      <c r="Q20" s="236">
+      <c r="Q20" s="245">
         <v>-17.9</v>
       </c>
       <c r="R20" s="246">
         <v>-19.39</v>
       </c>
-      <c r="S20" s="247">
+      <c r="S20" s="241">
         <v>-18.11</v>
       </c>
-      <c r="T20" s="237">
-        <v>-16.53</v>
+      <c r="T20" s="242">
+        <v>-16.21</v>
       </c>
     </row>
     <row r="21">
@@ -9236,7 +9236,7 @@
       <c r="C21" t="str">
         <v>301517</v>
       </c>
-      <c r="D21" s="250" t="str">
+      <c r="D21" s="257" t="str">
         <v>净买: 1391.15万</v>
       </c>
       <c r="E21">
@@ -9251,41 +9251,41 @@
       <c r="H21">
         <v>20</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="249">
         <v>-14.18</v>
       </c>
-      <c r="J21" s="251">
+      <c r="J21" s="255">
         <v>-19.79</v>
       </c>
-      <c r="K21" s="252">
+      <c r="K21" s="250">
         <v>-18.67</v>
       </c>
-      <c r="L21" s="253">
+      <c r="L21" s="256">
         <v>-21.09</v>
       </c>
-      <c r="M21" s="257">
+      <c r="M21" s="251">
         <v>-22.21</v>
       </c>
-      <c r="N21" s="254">
+      <c r="N21" s="258">
         <v>-18.54</v>
       </c>
-      <c r="O21" s="258">
+      <c r="O21" s="260">
         <v>-22.58</v>
       </c>
-      <c r="P21" s="255">
+      <c r="P21" s="259">
         <v>-27.04</v>
       </c>
-      <c r="Q21" s="256">
+      <c r="Q21" s="252">
         <v>-25.09</v>
       </c>
-      <c r="R21" s="249">
+      <c r="R21" s="253">
         <v>-21.88</v>
       </c>
-      <c r="S21" s="259">
+      <c r="S21" s="254">
         <v>-25.85</v>
       </c>
-      <c r="T21" s="260">
-        <v>19.65</v>
+      <c r="T21" s="248">
+        <v>21.25</v>
       </c>
     </row>
     <row r="22">
@@ -9298,7 +9298,7 @@
       <c r="C22" t="str">
         <v>002547</v>
       </c>
-      <c r="D22" s="268" t="str">
+      <c r="D22" s="269" t="str">
         <v>净买: 4862.70万</v>
       </c>
       <c r="E22">
@@ -9313,41 +9313,41 @@
       <c r="H22">
         <v>10.1</v>
       </c>
-      <c r="I22" s="269">
+      <c r="I22" s="261">
         <v>0</v>
       </c>
-      <c r="J22" s="263">
+      <c r="J22" s="262">
         <v>7.01</v>
       </c>
       <c r="K22" s="264">
         <v>0.36</v>
       </c>
-      <c r="L22" s="272">
+      <c r="L22" s="265">
         <v>4.68</v>
       </c>
-      <c r="M22" s="265">
+      <c r="M22" s="266">
         <v>15.11</v>
       </c>
-      <c r="N22" s="273">
+      <c r="N22" s="270">
         <v>21.76</v>
       </c>
-      <c r="O22" s="266">
+      <c r="O22" s="267">
         <v>22.66</v>
       </c>
-      <c r="P22" s="267">
+      <c r="P22" s="271">
         <v>17.81</v>
       </c>
-      <c r="Q22" s="261">
+      <c r="Q22" s="272">
         <v>9.17</v>
       </c>
-      <c r="R22" s="270">
+      <c r="R22" s="263">
         <v>12.59</v>
       </c>
-      <c r="S22" s="271">
+      <c r="S22" s="273">
         <v>7.01</v>
       </c>
-      <c r="T22" s="262">
-        <v>-38.13</v>
+      <c r="T22" s="268">
+        <v>-37.59</v>
       </c>
     </row>
     <row r="23">
@@ -9360,7 +9360,7 @@
       <c r="C23" t="str">
         <v>002547</v>
       </c>
-      <c r="D23" s="277" t="str">
+      <c r="D23" s="286" t="str">
         <v>净卖: -5175.09万</v>
       </c>
       <c r="E23">
@@ -9375,41 +9375,41 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23" s="281">
+      <c r="I23" s="274">
         <v>7.01</v>
       </c>
-      <c r="J23" s="282">
+      <c r="J23" s="275">
         <v>0.36</v>
       </c>
-      <c r="K23" s="274">
+      <c r="K23" s="278">
         <v>4.68</v>
       </c>
-      <c r="L23" s="278">
+      <c r="L23" s="282">
         <v>15.11</v>
       </c>
-      <c r="M23" s="284">
+      <c r="M23" s="279">
         <v>21.76</v>
       </c>
-      <c r="N23" s="283">
+      <c r="N23" s="285">
         <v>22.66</v>
       </c>
-      <c r="O23" s="279">
+      <c r="O23" s="283">
         <v>17.81</v>
       </c>
-      <c r="P23" s="285">
+      <c r="P23" s="276">
         <v>9.17</v>
       </c>
-      <c r="Q23" s="275">
+      <c r="Q23" s="277">
         <v>12.59</v>
       </c>
-      <c r="R23" s="276">
+      <c r="R23" s="280">
         <v>7.01</v>
       </c>
-      <c r="S23" s="286">
+      <c r="S23" s="281">
         <v>8.09</v>
       </c>
-      <c r="T23" s="280">
-        <v>-38.13</v>
+      <c r="T23" s="284">
+        <v>-37.59</v>
       </c>
     </row>
     <row r="24">
@@ -9422,7 +9422,7 @@
       <c r="C24" t="str">
         <v>920020</v>
       </c>
-      <c r="D24" s="298" t="str">
+      <c r="D24" s="293" t="str">
         <v>净卖: -668.61万</v>
       </c>
       <c r="E24">
@@ -9437,41 +9437,41 @@
       <c r="H24">
         <v>-9.66</v>
       </c>
-      <c r="I24" s="296">
+      <c r="I24" s="297">
         <v>14.02</v>
       </c>
-      <c r="J24" s="289">
+      <c r="J24" s="298">
         <v>2.92</v>
       </c>
-      <c r="K24" s="293">
+      <c r="K24" s="299">
         <v>1.38</v>
       </c>
-      <c r="L24" s="299">
+      <c r="L24" s="287">
         <v>0.51</v>
       </c>
-      <c r="M24" s="290">
+      <c r="M24" s="295">
         <v>-0.82</v>
       </c>
-      <c r="N24" s="287">
+      <c r="N24" s="289">
         <v>-0.87</v>
       </c>
-      <c r="O24" s="291">
+      <c r="O24" s="288">
         <v>0.87</v>
       </c>
-      <c r="P24" s="288">
+      <c r="P24" s="290">
         <v>-2.4</v>
       </c>
-      <c r="Q24" s="294">
+      <c r="Q24" s="291">
         <v>-5.17</v>
       </c>
-      <c r="R24" s="295">
+      <c r="R24" s="296">
         <v>-4.76</v>
       </c>
-      <c r="S24" s="297">
+      <c r="S24" s="294">
         <v>-4.35</v>
       </c>
       <c r="T24" s="292">
-        <v>-18.47</v>
+        <v>-17.49</v>
       </c>
     </row>
     <row r="25">
@@ -9484,7 +9484,7 @@
       <c r="C25" t="str">
         <v>605178</v>
       </c>
-      <c r="D25" s="300" t="str">
+      <c r="D25" s="308" t="str">
         <v>净买: 3874.18万</v>
       </c>
       <c r="E25">
@@ -9499,41 +9499,41 @@
       <c r="H25">
         <v>10</v>
       </c>
-      <c r="I25" s="311">
+      <c r="I25" s="309">
         <v>0</v>
       </c>
-      <c r="J25" s="301">
+      <c r="J25" s="305">
         <v>10</v>
       </c>
-      <c r="K25" s="302">
+      <c r="K25" s="310">
         <v>0.58</v>
       </c>
       <c r="L25" s="306">
         <v>4.74</v>
       </c>
-      <c r="M25" s="303">
+      <c r="M25" s="311">
         <v>13.42</v>
       </c>
-      <c r="N25" s="307">
+      <c r="N25" s="301">
         <v>19.72</v>
       </c>
-      <c r="O25" s="308">
+      <c r="O25" s="302">
         <v>26.01</v>
       </c>
-      <c r="P25" s="309">
+      <c r="P25" s="303">
         <v>16.89</v>
       </c>
-      <c r="Q25" s="304">
+      <c r="Q25" s="312">
         <v>6.52</v>
       </c>
-      <c r="R25" s="310">
+      <c r="R25" s="304">
         <v>10.9</v>
       </c>
-      <c r="S25" s="312">
+      <c r="S25" s="307">
         <v>12.81</v>
       </c>
-      <c r="T25" s="305">
-        <v>36.81</v>
+      <c r="T25" s="300">
+        <v>23.14</v>
       </c>
     </row>
     <row r="26">
@@ -9546,7 +9546,7 @@
       <c r="C26" t="str">
         <v>000407</v>
       </c>
-      <c r="D26" s="320" t="str">
+      <c r="D26" s="313" t="str">
         <v>净买: 788.81万</v>
       </c>
       <c r="E26">
@@ -9561,41 +9561,41 @@
       <c r="H26">
         <v>10.1</v>
       </c>
-      <c r="I26" s="317">
+      <c r="I26" s="314">
         <v>0</v>
       </c>
-      <c r="J26" s="324">
+      <c r="J26" s="315">
         <v>10.04</v>
       </c>
-      <c r="K26" s="321">
+      <c r="K26" s="316">
         <v>20.96</v>
       </c>
-      <c r="L26" s="325">
+      <c r="L26" s="322">
         <v>32.97</v>
       </c>
-      <c r="M26" s="322">
+      <c r="M26" s="317">
         <v>46.29</v>
       </c>
-      <c r="N26" s="323">
+      <c r="N26" s="319">
         <v>31.66</v>
       </c>
-      <c r="O26" s="314">
+      <c r="O26" s="320">
         <v>30.35</v>
       </c>
-      <c r="P26" s="318">
+      <c r="P26" s="321">
         <v>17.25</v>
       </c>
-      <c r="Q26" s="319">
+      <c r="Q26" s="323">
         <v>5.46</v>
       </c>
-      <c r="R26" s="315">
+      <c r="R26" s="318">
         <v>5.9</v>
       </c>
-      <c r="S26" s="316">
+      <c r="S26" s="324">
         <v>12.45</v>
       </c>
-      <c r="T26" s="313">
-        <v>1.31</v>
+      <c r="T26" s="325">
+        <v>2.84</v>
       </c>
     </row>
     <row r="27">
@@ -9608,7 +9608,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="327" t="str">
+      <c r="D27" s="334" t="str">
         <v>净买: 3123.85万</v>
       </c>
       <c r="E27">
@@ -9623,41 +9623,41 @@
       <c r="H27">
         <v>9.96</v>
       </c>
-      <c r="I27" s="333">
+      <c r="I27" s="326">
         <v>0</v>
       </c>
-      <c r="J27" s="328">
+      <c r="J27" s="327">
         <v>-9.95</v>
       </c>
-      <c r="K27" s="334">
+      <c r="K27" s="328">
         <v>-19.01</v>
       </c>
-      <c r="L27" s="329">
+      <c r="L27" s="337">
         <v>-27.04</v>
       </c>
-      <c r="M27" s="335">
+      <c r="M27" s="332">
         <v>-30.61</v>
       </c>
-      <c r="N27" s="337">
+      <c r="N27" s="329">
         <v>-28.7</v>
       </c>
-      <c r="O27" s="330">
+      <c r="O27" s="333">
         <v>-31.89</v>
       </c>
-      <c r="P27" s="338">
+      <c r="P27" s="335">
         <v>-31.63</v>
       </c>
-      <c r="Q27" s="331">
+      <c r="Q27" s="336">
         <v>-28.95</v>
       </c>
-      <c r="R27" s="336">
+      <c r="R27" s="338">
         <v>-26.53</v>
       </c>
-      <c r="S27" s="332">
+      <c r="S27" s="330">
         <v>-24.49</v>
       </c>
-      <c r="T27" s="326">
-        <v>-24.23</v>
+      <c r="T27" s="331">
+        <v>-23.21</v>
       </c>
     </row>
     <row r="28">
@@ -9670,7 +9670,7 @@
       <c r="C28" t="str">
         <v>300094</v>
       </c>
-      <c r="D28" s="345" t="str">
+      <c r="D28" s="343" t="str">
         <v>净卖: -3846.51万</v>
       </c>
       <c r="E28">
@@ -9685,41 +9685,41 @@
       <c r="H28">
         <v>0.37</v>
       </c>
-      <c r="I28" s="346">
+      <c r="I28" s="351">
         <v>-11.85</v>
       </c>
-      <c r="J28" s="339">
+      <c r="J28" s="346">
         <v>-12.41</v>
       </c>
-      <c r="K28" s="350">
+      <c r="K28" s="339">
         <v>-8.33</v>
       </c>
       <c r="L28" s="340">
         <v>-17.96</v>
       </c>
-      <c r="M28" s="347">
+      <c r="M28" s="341">
         <v>-23.89</v>
       </c>
-      <c r="N28" s="341">
+      <c r="N28" s="347">
         <v>-22.96</v>
       </c>
-      <c r="O28" s="342">
+      <c r="O28" s="348">
         <v>-24.26</v>
       </c>
-      <c r="P28" s="351">
+      <c r="P28" s="344">
         <v>-23.15</v>
       </c>
-      <c r="Q28" s="348">
+      <c r="Q28" s="349">
         <v>-21.48</v>
       </c>
-      <c r="R28" s="343">
+      <c r="R28" s="350">
         <v>-21.85</v>
       </c>
-      <c r="S28" s="344">
+      <c r="S28" s="345">
         <v>-27.78</v>
       </c>
-      <c r="T28" s="349">
-        <v>-42.22</v>
+      <c r="T28" s="342">
+        <v>-41.85</v>
       </c>
     </row>
     <row r="29">
@@ -9732,7 +9732,7 @@
       <c r="C29" t="str">
         <v>002682</v>
       </c>
-      <c r="D29" s="356" t="str">
+      <c r="D29" s="364" t="str">
         <v>净卖: -2565.97万</v>
       </c>
       <c r="E29">
@@ -9747,41 +9747,41 @@
       <c r="H29">
         <v>-6.94</v>
       </c>
-      <c r="I29" s="357">
+      <c r="I29" s="352">
         <v>-3.35</v>
       </c>
-      <c r="J29" s="358">
+      <c r="J29" s="361">
         <v>-12.94</v>
       </c>
-      <c r="K29" s="354">
+      <c r="K29" s="357">
         <v>-17.2</v>
       </c>
-      <c r="L29" s="359">
+      <c r="L29" s="358">
         <v>-14.92</v>
       </c>
-      <c r="M29" s="360">
+      <c r="M29" s="353">
         <v>-18.72</v>
       </c>
-      <c r="N29" s="364">
+      <c r="N29" s="354">
         <v>-18.42</v>
       </c>
-      <c r="O29" s="361">
+      <c r="O29" s="362">
         <v>-15.22</v>
       </c>
-      <c r="P29" s="352">
+      <c r="P29" s="360">
         <v>-12.33</v>
       </c>
-      <c r="Q29" s="355">
+      <c r="Q29" s="359">
         <v>-9.89</v>
       </c>
-      <c r="R29" s="362">
+      <c r="R29" s="355">
         <v>-0.91</v>
       </c>
-      <c r="S29" s="363">
+      <c r="S29" s="356">
         <v>8.98</v>
       </c>
-      <c r="T29" s="353">
-        <v>-9.59</v>
+      <c r="T29" s="363">
+        <v>-8.37</v>
       </c>
     </row>
     <row r="30">
@@ -9794,7 +9794,7 @@
       <c r="C30" t="str">
         <v>603069</v>
       </c>
-      <c r="D30" s="374" t="str">
+      <c r="D30" s="370" t="str">
         <v>净买: 2184.48万</v>
       </c>
       <c r="E30">
@@ -9809,41 +9809,41 @@
       <c r="H30">
         <v>10.02</v>
       </c>
-      <c r="I30" s="365">
+      <c r="I30" s="367">
         <v>0</v>
       </c>
-      <c r="J30" s="375">
+      <c r="J30" s="371">
         <v>1.25</v>
       </c>
-      <c r="K30" s="376">
+      <c r="K30" s="372">
         <v>-4.36</v>
       </c>
       <c r="L30" s="368">
         <v>5.19</v>
       </c>
-      <c r="M30" s="369">
+      <c r="M30" s="377">
         <v>-1.42</v>
       </c>
-      <c r="N30" s="370">
+      <c r="N30" s="365">
         <v>-5.96</v>
       </c>
-      <c r="O30" s="373">
+      <c r="O30" s="366">
         <v>-5.99</v>
       </c>
-      <c r="P30" s="371">
+      <c r="P30" s="374">
         <v>-13.57</v>
       </c>
-      <c r="Q30" s="377">
+      <c r="Q30" s="375">
         <v>-13.64</v>
       </c>
-      <c r="R30" s="366">
+      <c r="R30" s="376">
         <v>-14.16</v>
       </c>
-      <c r="S30" s="367">
+      <c r="S30" s="373">
         <v>-15.27</v>
       </c>
-      <c r="T30" s="372">
-        <v>-39.23</v>
+      <c r="T30" s="369">
+        <v>-38.47</v>
       </c>
     </row>
     <row r="31">
@@ -9856,7 +9856,7 @@
       <c r="C31" t="str">
         <v>002009</v>
       </c>
-      <c r="D31" s="382" t="str">
+      <c r="D31" s="389" t="str">
         <v>净买: 3463.54万</v>
       </c>
       <c r="E31">
@@ -9871,41 +9871,41 @@
       <c r="H31">
         <v>10</v>
       </c>
-      <c r="I31" s="379">
+      <c r="I31" s="378">
         <v>0</v>
       </c>
-      <c r="J31" s="383">
+      <c r="J31" s="384">
         <v>10.02</v>
       </c>
-      <c r="K31" s="388">
+      <c r="K31" s="385">
         <v>21.02</v>
       </c>
-      <c r="L31" s="389">
+      <c r="L31" s="386">
         <v>16.84</v>
       </c>
-      <c r="M31" s="390">
+      <c r="M31" s="380">
         <v>14.72</v>
       </c>
-      <c r="N31" s="384">
+      <c r="N31" s="381">
         <v>8.01</v>
       </c>
-      <c r="O31" s="380">
+      <c r="O31" s="382">
         <v>12.24</v>
       </c>
-      <c r="P31" s="378">
+      <c r="P31" s="387">
         <v>12.65</v>
       </c>
-      <c r="Q31" s="385">
+      <c r="Q31" s="388">
         <v>15.19</v>
       </c>
-      <c r="R31" s="381">
+      <c r="R31" s="383">
         <v>18.85</v>
       </c>
-      <c r="S31" s="386">
+      <c r="S31" s="379">
         <v>11.93</v>
       </c>
-      <c r="T31" s="387">
-        <v>27.01</v>
+      <c r="T31" s="390">
+        <v>28.1</v>
       </c>
     </row>
     <row r="32">
@@ -9918,7 +9918,7 @@
       <c r="C32" t="str">
         <v>002009</v>
       </c>
-      <c r="D32" s="393" t="str">
+      <c r="D32" s="395" t="str">
         <v>净卖: -4207.08万</v>
       </c>
       <c r="E32">
@@ -9933,41 +9933,41 @@
       <c r="H32">
         <v>9.92</v>
       </c>
-      <c r="I32" s="400">
+      <c r="I32" s="396">
         <v>0.09</v>
       </c>
-      <c r="J32" s="401">
+      <c r="J32" s="397">
         <v>10.1</v>
       </c>
-      <c r="K32" s="394">
+      <c r="K32" s="398">
         <v>6.3</v>
       </c>
-      <c r="L32" s="402">
+      <c r="L32" s="393">
         <v>4.37</v>
       </c>
-      <c r="M32" s="391">
+      <c r="M32" s="399">
         <v>-1.74</v>
       </c>
-      <c r="N32" s="398">
+      <c r="N32" s="400">
         <v>2.11</v>
       </c>
-      <c r="O32" s="395">
+      <c r="O32" s="402">
         <v>2.49</v>
       </c>
-      <c r="P32" s="392">
+      <c r="P32" s="403">
         <v>4.79</v>
       </c>
-      <c r="Q32" s="396">
+      <c r="Q32" s="391">
         <v>8.13</v>
       </c>
-      <c r="R32" s="403">
+      <c r="R32" s="401">
         <v>1.83</v>
       </c>
-      <c r="S32" s="397">
+      <c r="S32" s="392">
         <v>2.63</v>
       </c>
-      <c r="T32" s="399">
-        <v>15.55</v>
+      <c r="T32" s="394">
+        <v>16.54</v>
       </c>
     </row>
     <row r="33">
@@ -9980,7 +9980,7 @@
       <c r="C33" t="str">
         <v>002009</v>
       </c>
-      <c r="D33" s="414" t="str">
+      <c r="D33" s="407" t="str">
         <v>净卖: -4209.56万</v>
       </c>
       <c r="E33">
@@ -9995,41 +9995,41 @@
       <c r="H33">
         <v>2.21</v>
       </c>
-      <c r="I33" s="408">
+      <c r="I33" s="410">
         <v>7.63</v>
       </c>
-      <c r="J33" s="404">
+      <c r="J33" s="414">
         <v>3.9</v>
       </c>
-      <c r="K33" s="409">
+      <c r="K33" s="415">
         <v>2.02</v>
       </c>
-      <c r="L33" s="410">
+      <c r="L33" s="416">
         <v>-3.95</v>
       </c>
-      <c r="M33" s="412">
+      <c r="M33" s="404">
         <v>-0.18</v>
       </c>
       <c r="N33" s="405">
         <v>0.18</v>
       </c>
-      <c r="O33" s="413">
+      <c r="O33" s="411">
         <v>2.43</v>
       </c>
-      <c r="P33" s="406">
+      <c r="P33" s="412">
         <v>5.7</v>
       </c>
-      <c r="Q33" s="407">
+      <c r="Q33" s="413">
         <v>-0.46</v>
       </c>
-      <c r="R33" s="415">
+      <c r="R33" s="408">
         <v>0.32</v>
       </c>
-      <c r="S33" s="416">
+      <c r="S33" s="406">
         <v>-1.52</v>
       </c>
-      <c r="T33" s="411">
-        <v>12.95</v>
+      <c r="T33" s="409">
+        <v>13.92</v>
       </c>
     </row>
     <row r="34">
@@ -10042,7 +10042,7 @@
       <c r="C34" t="str">
         <v>002969</v>
       </c>
-      <c r="D34" s="423" t="str">
+      <c r="D34" s="422" t="str">
         <v>净卖: -2752.13万</v>
       </c>
       <c r="E34">
@@ -10057,41 +10057,41 @@
       <c r="H34">
         <v>0.55</v>
       </c>
-      <c r="I34" s="429">
+      <c r="I34" s="423">
         <v>7.62</v>
       </c>
-      <c r="J34" s="424">
+      <c r="J34" s="417">
         <v>18.38</v>
       </c>
-      <c r="K34" s="417">
+      <c r="K34" s="419">
         <v>30.24</v>
       </c>
-      <c r="L34" s="425">
+      <c r="L34" s="424">
         <v>37.86</v>
       </c>
-      <c r="M34" s="426">
+      <c r="M34" s="425">
         <v>51.69</v>
       </c>
-      <c r="N34" s="427">
+      <c r="N34" s="426">
         <v>36.53</v>
       </c>
-      <c r="O34" s="421">
+      <c r="O34" s="420">
         <v>22.86</v>
       </c>
-      <c r="P34" s="418">
+      <c r="P34" s="421">
         <v>35.11</v>
       </c>
-      <c r="Q34" s="428">
+      <c r="Q34" s="418">
         <v>48.63</v>
       </c>
-      <c r="R34" s="419">
+      <c r="R34" s="429">
         <v>52.47</v>
       </c>
-      <c r="S34" s="420">
+      <c r="S34" s="427">
         <v>67.71</v>
       </c>
-      <c r="T34" s="422">
-        <v>77.3</v>
+      <c r="T34" s="428">
+        <v>77.53</v>
       </c>
     </row>
     <row r="35">
@@ -10104,7 +10104,7 @@
       <c r="C35" t="str">
         <v>600683</v>
       </c>
-      <c r="D35" s="439" t="str">
+      <c r="D35" s="440" t="str">
         <v>净买: 819.30万</v>
       </c>
       <c r="E35">
@@ -10119,41 +10119,41 @@
       <c r="H35">
         <v>10.1</v>
       </c>
-      <c r="I35" s="440">
+      <c r="I35" s="433">
         <v>0</v>
       </c>
-      <c r="J35" s="431">
+      <c r="J35" s="430">
         <v>10.09</v>
       </c>
-      <c r="K35" s="433">
+      <c r="K35" s="441">
         <v>21.1</v>
       </c>
-      <c r="L35" s="436">
+      <c r="L35" s="434">
         <v>11.01</v>
       </c>
-      <c r="M35" s="437">
+      <c r="M35" s="435">
         <v>22.2</v>
       </c>
-      <c r="N35" s="438">
+      <c r="N35" s="442">
         <v>22.57</v>
       </c>
-      <c r="O35" s="441">
+      <c r="O35" s="436">
         <v>32.29</v>
       </c>
-      <c r="P35" s="434">
+      <c r="P35" s="439">
         <v>27.16</v>
       </c>
-      <c r="Q35" s="442">
+      <c r="Q35" s="431">
         <v>23.12</v>
       </c>
-      <c r="R35" s="430">
+      <c r="R35" s="432">
         <v>30.46</v>
       </c>
-      <c r="S35" s="432">
+      <c r="S35" s="437">
         <v>37.06</v>
       </c>
-      <c r="T35" s="435">
-        <v>120</v>
+      <c r="T35" s="438">
+        <v>121.1</v>
       </c>
     </row>
     <row r="36">
@@ -10166,7 +10166,7 @@
       <c r="C36" t="str">
         <v>002056</v>
       </c>
-      <c r="D36" s="445" t="str">
+      <c r="D36" s="454" t="str">
         <v>净卖: -2838.92万</v>
       </c>
       <c r="E36">
@@ -10181,41 +10181,41 @@
       <c r="H36">
         <v>1.28</v>
       </c>
-      <c r="I36" s="451">
+      <c r="I36" s="445">
         <v>8.62</v>
       </c>
-      <c r="J36" s="452">
+      <c r="J36" s="449">
         <v>-0.42</v>
       </c>
       <c r="K36" s="446">
         <v>-4.25</v>
       </c>
-      <c r="L36" s="447">
+      <c r="L36" s="450">
         <v>-5.84</v>
       </c>
-      <c r="M36" s="453">
+      <c r="M36" s="452">
         <v>-8.66</v>
       </c>
-      <c r="N36" s="454">
+      <c r="N36" s="455">
         <v>-6.43</v>
       </c>
-      <c r="O36" s="448">
+      <c r="O36" s="447">
         <v>-9.21</v>
       </c>
-      <c r="P36" s="449">
+      <c r="P36" s="448">
         <v>-9.21</v>
       </c>
-      <c r="Q36" s="450">
+      <c r="Q36" s="453">
         <v>-7.78</v>
       </c>
-      <c r="R36" s="443">
+      <c r="R36" s="451">
         <v>-9.46</v>
       </c>
-      <c r="S36" s="444">
+      <c r="S36" s="443">
         <v>-9.92</v>
       </c>
-      <c r="T36" s="455">
-        <v>-18.5</v>
+      <c r="T36" s="444">
+        <v>-17.44</v>
       </c>
     </row>
     <row r="37">
@@ -10277,37 +10277,37 @@
       <c r="F38" t="str"/>
       <c r="G38" t="str"/>
       <c r="H38" t="str"/>
-      <c r="I38" s="464">
+      <c r="I38" s="460">
         <v>31.43</v>
       </c>
-      <c r="J38" s="457">
+      <c r="J38" s="458">
         <v>62.86</v>
       </c>
-      <c r="K38" s="462">
+      <c r="K38" s="459">
         <v>54.29</v>
       </c>
-      <c r="L38" s="463">
+      <c r="L38" s="461">
         <v>54.29</v>
       </c>
-      <c r="M38" s="458">
+      <c r="M38" s="462">
         <v>42.86</v>
       </c>
-      <c r="N38" s="459">
+      <c r="N38" s="463">
         <v>42.86</v>
       </c>
-      <c r="O38" s="467">
+      <c r="O38" s="464">
         <v>48.57</v>
       </c>
-      <c r="P38" s="460">
+      <c r="P38" s="467">
         <v>37.14</v>
       </c>
-      <c r="Q38" s="456">
+      <c r="Q38" s="457">
         <v>31.43</v>
       </c>
-      <c r="R38" s="461">
+      <c r="R38" s="465">
         <v>34.29</v>
       </c>
-      <c r="S38" s="465">
+      <c r="S38" s="456">
         <v>31.43</v>
       </c>
       <c r="T38" s="466">
@@ -10325,22 +10325,22 @@
       <c r="F39" t="str"/>
       <c r="G39" t="str"/>
       <c r="H39" t="str"/>
-      <c r="I39" s="469">
+      <c r="I39" s="473">
         <v>0.72</v>
       </c>
-      <c r="J39" s="478">
+      <c r="J39" s="474">
         <v>1.7</v>
       </c>
-      <c r="K39" s="470">
+      <c r="K39" s="468">
         <v>1.83</v>
       </c>
-      <c r="L39" s="479">
+      <c r="L39" s="470">
         <v>1.8</v>
       </c>
-      <c r="M39" s="468">
+      <c r="M39" s="475">
         <v>1.64</v>
       </c>
-      <c r="N39" s="475">
+      <c r="N39" s="469">
         <v>0.36</v>
       </c>
       <c r="O39" s="476">
@@ -10352,14 +10352,14 @@
       <c r="Q39" s="472">
         <v>-3.24</v>
       </c>
-      <c r="R39" s="473">
+      <c r="R39" s="478">
         <v>-2.68</v>
       </c>
-      <c r="S39" s="474">
+      <c r="S39" s="479">
         <v>-2.27</v>
       </c>
       <c r="T39" s="477">
-        <v>10.81</v>
+        <v>11.81</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/正经哥/index.xlsx
+++ b/youzi/正经哥/index.xlsx
@@ -39,6 +39,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF36AC51"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -69,7 +135,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,25 +237,679 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF36AC51"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,49 +921,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,7 +945,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF9FD7AC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,25 +957,1189 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,31 +2157,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1A702F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -267,13 +2175,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,55 +2253,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -345,139 +2289,445 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBF8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEBF6ED"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -489,793 +2739,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1293,1471 +2769,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7FBF8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2775,67 +2841,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2847,67 +2883,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDF4957"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D4"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8058,7 +8058,7 @@
       <c r="C2" t="str">
         <v>000665</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="10" t="str">
         <v>净卖: -2301.68万</v>
       </c>
       <c r="E2">
@@ -8073,41 +8073,41 @@
       <c r="H2">
         <v>10.06</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="1">
         <v>0</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>10</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="11">
         <v>21.03</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="3">
         <v>30</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="9">
         <v>18.79</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="12">
         <v>10</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="7">
         <v>11.72</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="8">
         <v>10.17</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="13">
         <v>2.07</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="4">
         <v>-4.66</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="5">
         <v>-8.45</v>
       </c>
-      <c r="T2" s="7">
-        <v>-17.93</v>
+      <c r="T2" s="6">
+        <v>-18.97</v>
       </c>
     </row>
     <row r="3">
@@ -8135,41 +8135,41 @@
       <c r="H3">
         <v>9.95</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="20">
         <v>0</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="15">
         <v>10.06</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="16">
         <v>21.12</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="23">
         <v>9.77</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="21">
         <v>-1.15</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="17">
         <v>-8.76</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="18">
         <v>-11.35</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="26">
         <v>-12.36</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="22">
         <v>-13.22</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="24">
         <v>-21.84</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="19">
         <v>-23.99</v>
       </c>
-      <c r="T3" s="19">
-        <v>49.71</v>
+      <c r="T3" s="14">
+        <v>48.56</v>
       </c>
     </row>
     <row r="4">
@@ -8182,7 +8182,7 @@
       <c r="C4" t="str">
         <v>002300</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="33" t="str">
         <v>净卖: -2576.68万</v>
       </c>
       <c r="E4">
@@ -8197,41 +8197,41 @@
       <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="27">
         <v>9.34</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="28">
         <v>-0.91</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="31">
         <v>-10.77</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="36">
         <v>-17.64</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="37">
         <v>-19.97</v>
       </c>
       <c r="N4" s="32">
         <v>-20.88</v>
       </c>
-      <c r="O4" s="30">
+      <c r="O4" s="29">
         <v>-21.66</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="34">
         <v>-29.44</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="38">
         <v>-31.39</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="39">
         <v>-28.92</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="35">
         <v>-27.63</v>
       </c>
-      <c r="T4" s="27">
-        <v>35.15</v>
+      <c r="T4" s="30">
+        <v>34.11</v>
       </c>
     </row>
     <row r="5">
@@ -8244,7 +8244,7 @@
       <c r="C5" t="str">
         <v>002688</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="49" t="str">
         <v>净买: 5775.20万</v>
       </c>
       <c r="E5">
@@ -8259,41 +8259,41 @@
       <c r="H5">
         <v>9.93</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="52">
         <v>0</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="42">
         <v>9.95</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="50">
         <v>20.98</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="43">
         <v>30.17</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="40">
         <v>17.15</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="48">
         <v>8.58</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="51">
         <v>10.57</v>
       </c>
-      <c r="P5" s="52">
+      <c r="P5" s="41">
         <v>-0.46</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="44">
         <v>-5.36</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="45">
         <v>-5.05</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="46">
         <v>-4.29</v>
       </c>
-      <c r="T5" s="45">
-        <v>-10.57</v>
+      <c r="T5" s="47">
+        <v>-11.49</v>
       </c>
     </row>
     <row r="6">
@@ -8306,7 +8306,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="60" t="str">
         <v>净卖: -7396.08万</v>
       </c>
       <c r="E6">
@@ -8321,41 +8321,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="54">
         <v>7.59</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="55">
         <v>-3.16</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="65">
         <v>-10.25</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="58">
         <v>-8.61</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="59">
         <v>-17.72</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="56">
         <v>-21.77</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="61">
         <v>-21.52</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="57">
         <v>-20.89</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="62">
         <v>-16.71</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="63">
         <v>-20.76</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="53">
         <v>-17.09</v>
       </c>
-      <c r="T6" s="61">
-        <v>-26.08</v>
+      <c r="T6" s="64">
+        <v>-26.84</v>
       </c>
     </row>
     <row r="7">
@@ -8368,7 +8368,7 @@
       <c r="C7" t="str">
         <v>600697</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="76" t="str">
         <v>净卖: -2819.93万</v>
       </c>
       <c r="E7">
@@ -8383,41 +8383,41 @@
       <c r="H7">
         <v>-9.28</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="66">
         <v>3.2</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="72">
         <v>6.95</v>
       </c>
-      <c r="K7" s="76">
+      <c r="K7" s="69">
         <v>17.66</v>
       </c>
-      <c r="L7" s="74">
+      <c r="L7" s="70">
         <v>13.12</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="73">
         <v>1.95</v>
       </c>
-      <c r="N7" s="78">
+      <c r="N7" s="71">
         <v>0</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="67">
         <v>4.3</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="77">
         <v>-1.72</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="74">
         <v>-5.31</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="68">
         <v>-5.23</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="78">
         <v>-7.97</v>
       </c>
-      <c r="T7" s="72">
-        <v>-7.5</v>
+      <c r="T7" s="75">
+        <v>-8.36</v>
       </c>
     </row>
     <row r="8">
@@ -8430,7 +8430,7 @@
       <c r="C8" t="str">
         <v>600828</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="90" t="str">
         <v>净买: 1425.83万</v>
       </c>
       <c r="E8">
@@ -8445,41 +8445,41 @@
       <c r="H8">
         <v>10.11</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="84">
         <v>0</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="91">
         <v>10.02</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="88">
         <v>7.31</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="79">
         <v>5.01</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="80">
         <v>10.65</v>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="86">
         <v>5.43</v>
       </c>
       <c r="O8" s="85">
         <v>-5.01</v>
       </c>
-      <c r="P8" s="89">
+      <c r="P8" s="81">
         <v>-10.02</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="89">
         <v>-12.73</v>
       </c>
-      <c r="R8" s="90">
+      <c r="R8" s="87">
         <v>-11.69</v>
       </c>
-      <c r="S8" s="86">
+      <c r="S8" s="82">
         <v>-10.65</v>
       </c>
-      <c r="T8" s="91">
-        <v>8.77</v>
+      <c r="T8" s="83">
+        <v>8.56</v>
       </c>
     </row>
     <row r="9">
@@ -8492,7 +8492,7 @@
       <c r="C9" t="str">
         <v>600828</v>
       </c>
-      <c r="D9" s="94" t="str">
+      <c r="D9" s="100" t="str">
         <v>净卖: -1514.63万</v>
       </c>
       <c r="E9">
@@ -8507,41 +8507,41 @@
       <c r="H9">
         <v>-0.21</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="101">
         <v>10.25</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="95">
         <v>7.53</v>
       </c>
-      <c r="K9" s="100">
+      <c r="K9" s="102">
         <v>5.23</v>
       </c>
-      <c r="L9" s="104">
+      <c r="L9" s="103">
         <v>10.88</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="96">
         <v>5.65</v>
       </c>
-      <c r="N9" s="92">
+      <c r="N9" s="97">
         <v>-4.81</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="92">
         <v>-9.83</v>
       </c>
-      <c r="P9" s="96">
+      <c r="P9" s="104">
         <v>-12.55</v>
       </c>
-      <c r="Q9" s="101">
+      <c r="Q9" s="93">
         <v>-11.51</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="99">
         <v>-10.46</v>
       </c>
-      <c r="S9" s="93">
+      <c r="S9" s="98">
         <v>-12.34</v>
       </c>
-      <c r="T9" s="98">
-        <v>9</v>
+      <c r="T9" s="94">
+        <v>8.79</v>
       </c>
     </row>
     <row r="10">
@@ -8554,7 +8554,7 @@
       <c r="C10" t="str">
         <v>002909</v>
       </c>
-      <c r="D10" s="105" t="str">
+      <c r="D10" s="112" t="str">
         <v>净卖: -879.53万</v>
       </c>
       <c r="E10">
@@ -8569,41 +8569,41 @@
       <c r="H10">
         <v>-1.91</v>
       </c>
-      <c r="I10" s="109">
+      <c r="I10" s="110">
         <v>-8.28</v>
       </c>
-      <c r="J10" s="115">
+      <c r="J10" s="113">
         <v>-16.44</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="105">
         <v>-21.07</v>
       </c>
-      <c r="L10" s="112">
+      <c r="L10" s="106">
         <v>-21.8</v>
       </c>
-      <c r="M10" s="116">
+      <c r="M10" s="107">
         <v>-23.39</v>
       </c>
-      <c r="N10" s="113">
+      <c r="N10" s="111">
         <v>-23.02</v>
       </c>
-      <c r="O10" s="106">
+      <c r="O10" s="108">
         <v>-22.66</v>
       </c>
-      <c r="P10" s="107">
+      <c r="P10" s="115">
         <v>-23.87</v>
       </c>
-      <c r="Q10" s="108">
+      <c r="Q10" s="109">
         <v>-23.26</v>
       </c>
-      <c r="R10" s="117">
+      <c r="R10" s="114">
         <v>-24.12</v>
       </c>
-      <c r="S10" s="111">
+      <c r="S10" s="116">
         <v>-23.87</v>
       </c>
-      <c r="T10" s="114">
-        <v>-20.1</v>
+      <c r="T10" s="117">
+        <v>-21.44</v>
       </c>
     </row>
     <row r="11">
@@ -8616,7 +8616,7 @@
       <c r="C11" t="str">
         <v>603639</v>
       </c>
-      <c r="D11" s="119" t="str">
+      <c r="D11" s="130" t="str">
         <v>净买: 1633.37万</v>
       </c>
       <c r="E11">
@@ -8631,41 +8631,41 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="123">
+      <c r="I11" s="126">
         <v>0</v>
       </c>
-      <c r="J11" s="127">
+      <c r="J11" s="121">
         <v>-6.63</v>
       </c>
-      <c r="K11" s="124">
+      <c r="K11" s="118">
         <v>-12.9</v>
       </c>
-      <c r="L11" s="129">
+      <c r="L11" s="127">
         <v>-12.16</v>
       </c>
-      <c r="M11" s="125">
+      <c r="M11" s="122">
         <v>-13.76</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="123">
         <v>-9.83</v>
       </c>
-      <c r="O11" s="128">
+      <c r="O11" s="129">
         <v>-10.63</v>
       </c>
-      <c r="P11" s="130">
+      <c r="P11" s="119">
         <v>-9.46</v>
       </c>
-      <c r="Q11" s="121">
+      <c r="Q11" s="124">
         <v>-10.44</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="128">
         <v>-10.01</v>
       </c>
-      <c r="S11" s="126">
+      <c r="S11" s="120">
         <v>-8.17</v>
       </c>
-      <c r="T11" s="118">
-        <v>-19.41</v>
+      <c r="T11" s="125">
+        <v>-19.1</v>
       </c>
     </row>
     <row r="12">
@@ -8678,7 +8678,7 @@
       <c r="C12" t="str">
         <v>002235</v>
       </c>
-      <c r="D12" s="134" t="str">
+      <c r="D12" s="142" t="str">
         <v>净买: 1768.35万</v>
       </c>
       <c r="E12">
@@ -8693,41 +8693,41 @@
       <c r="H12">
         <v>10.05</v>
       </c>
-      <c r="I12" s="135">
+      <c r="I12" s="143">
         <v>0</v>
       </c>
-      <c r="J12" s="143">
+      <c r="J12" s="138">
         <v>3.19</v>
       </c>
-      <c r="K12" s="139">
+      <c r="K12" s="131">
         <v>6.23</v>
       </c>
-      <c r="L12" s="131">
+      <c r="L12" s="139">
         <v>16.81</v>
       </c>
-      <c r="M12" s="140">
+      <c r="M12" s="141">
         <v>18.99</v>
       </c>
-      <c r="N12" s="141">
+      <c r="N12" s="132">
         <v>30.87</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="135">
         <v>43.91</v>
       </c>
-      <c r="P12" s="142">
+      <c r="P12" s="133">
         <v>42.17</v>
       </c>
-      <c r="Q12" s="132">
+      <c r="Q12" s="134">
         <v>36.52</v>
       </c>
-      <c r="R12" s="137">
+      <c r="R12" s="140">
         <v>43.48</v>
       </c>
-      <c r="S12" s="133">
+      <c r="S12" s="136">
         <v>44.93</v>
       </c>
-      <c r="T12" s="138">
-        <v>40.14</v>
+      <c r="T12" s="137">
+        <v>36.96</v>
       </c>
     </row>
     <row r="13">
@@ -8740,7 +8740,7 @@
       <c r="C13" t="str">
         <v>603776</v>
       </c>
-      <c r="D13" s="148" t="str">
+      <c r="D13" s="153" t="str">
         <v>净买: 1894.22万</v>
       </c>
       <c r="E13">
@@ -8755,28 +8755,28 @@
       <c r="H13">
         <v>10</v>
       </c>
-      <c r="I13" s="153">
+      <c r="I13" s="150">
         <v>0</v>
       </c>
-      <c r="J13" s="149">
+      <c r="J13" s="154">
         <v>-9.72</v>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="146">
         <v>-10.95</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="147">
         <v>-8.45</v>
       </c>
-      <c r="M13" s="155">
+      <c r="M13" s="148">
         <v>-7.04</v>
       </c>
-      <c r="N13" s="156">
+      <c r="N13" s="151">
         <v>-11.27</v>
       </c>
-      <c r="O13" s="151">
+      <c r="O13" s="155">
         <v>-2.41</v>
       </c>
-      <c r="P13" s="152">
+      <c r="P13" s="156">
         <v>2.36</v>
       </c>
       <c r="Q13" s="144">
@@ -8785,11 +8785,11 @@
       <c r="R13" s="145">
         <v>-2.32</v>
       </c>
-      <c r="S13" s="146">
+      <c r="S13" s="152">
         <v>-2.23</v>
       </c>
-      <c r="T13" s="147">
-        <v>-7.81</v>
+      <c r="T13" s="149">
+        <v>-7.45</v>
       </c>
     </row>
     <row r="14">
@@ -8802,7 +8802,7 @@
       <c r="C14" t="str">
         <v>603776</v>
       </c>
-      <c r="D14" s="160" t="str">
+      <c r="D14" s="168" t="str">
         <v>净卖: -2197.25万</v>
       </c>
       <c r="E14">
@@ -8817,41 +8817,41 @@
       <c r="H14">
         <v>-2.32</v>
       </c>
-      <c r="I14" s="165">
+      <c r="I14" s="158">
         <v>-7.58</v>
       </c>
-      <c r="J14" s="157">
+      <c r="J14" s="169">
         <v>-8.84</v>
       </c>
       <c r="K14" s="161">
         <v>-6.28</v>
       </c>
-      <c r="L14" s="166">
+      <c r="L14" s="162">
         <v>-4.84</v>
       </c>
-      <c r="M14" s="158">
+      <c r="M14" s="163">
         <v>-9.16</v>
       </c>
-      <c r="N14" s="167">
+      <c r="N14" s="159">
         <v>-0.09</v>
       </c>
-      <c r="O14" s="162">
+      <c r="O14" s="164">
         <v>4.79</v>
       </c>
-      <c r="P14" s="168">
+      <c r="P14" s="165">
         <v>-0.33</v>
       </c>
-      <c r="Q14" s="169">
+      <c r="Q14" s="166">
         <v>0</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="157">
         <v>0.09</v>
       </c>
-      <c r="S14" s="163">
+      <c r="S14" s="167">
         <v>0</v>
       </c>
-      <c r="T14" s="164">
-        <v>-5.63</v>
+      <c r="T14" s="160">
+        <v>-5.26</v>
       </c>
     </row>
     <row r="15">
@@ -8864,7 +8864,7 @@
       <c r="C15" t="str">
         <v>001360</v>
       </c>
-      <c r="D15" s="172" t="str">
+      <c r="D15" s="181" t="str">
         <v>净买: 1803.24万</v>
       </c>
       <c r="E15">
@@ -8879,41 +8879,41 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="172">
         <v>0</v>
       </c>
-      <c r="J15" s="175">
+      <c r="J15" s="176">
         <v>10.01</v>
       </c>
-      <c r="K15" s="179">
+      <c r="K15" s="177">
         <v>-0.95</v>
       </c>
-      <c r="L15" s="176">
+      <c r="L15" s="182">
         <v>-10.85</v>
       </c>
-      <c r="M15" s="182">
+      <c r="M15" s="170">
         <v>-13.18</v>
       </c>
-      <c r="N15" s="177">
+      <c r="N15" s="171">
         <v>-14.29</v>
       </c>
-      <c r="O15" s="180">
+      <c r="O15" s="173">
         <v>-15.25</v>
       </c>
-      <c r="P15" s="181">
+      <c r="P15" s="174">
         <v>-14.56</v>
       </c>
-      <c r="Q15" s="170">
+      <c r="Q15" s="179">
         <v>-16.52</v>
       </c>
-      <c r="R15" s="174">
+      <c r="R15" s="175">
         <v>-16.36</v>
       </c>
       <c r="S15" s="178">
         <v>-16.15</v>
       </c>
-      <c r="T15" s="171">
-        <v>17.26</v>
+      <c r="T15" s="180">
+        <v>15.56</v>
       </c>
     </row>
     <row r="16">
@@ -8926,7 +8926,7 @@
       <c r="C16" t="str">
         <v>601669</v>
       </c>
-      <c r="D16" s="192" t="str">
+      <c r="D16" s="185" t="str">
         <v>净买: 9396.35万</v>
       </c>
       <c r="E16">
@@ -8941,41 +8941,41 @@
       <c r="H16">
         <v>10.08</v>
       </c>
-      <c r="I16" s="189">
+      <c r="I16" s="190">
         <v>0</v>
       </c>
-      <c r="J16" s="187">
+      <c r="J16" s="194">
         <v>10.04</v>
       </c>
-      <c r="K16" s="193">
+      <c r="K16" s="192">
         <v>6.65</v>
       </c>
-      <c r="L16" s="190">
+      <c r="L16" s="195">
         <v>3.84</v>
       </c>
-      <c r="M16" s="194">
+      <c r="M16" s="186">
         <v>5.76</v>
       </c>
-      <c r="N16" s="195">
+      <c r="N16" s="183">
         <v>0.44</v>
       </c>
-      <c r="O16" s="183">
+      <c r="O16" s="191">
         <v>0.89</v>
       </c>
-      <c r="P16" s="184">
+      <c r="P16" s="193">
         <v>-3.69</v>
       </c>
-      <c r="Q16" s="185">
+      <c r="Q16" s="187">
         <v>-4.58</v>
       </c>
       <c r="R16" s="188">
         <v>-5.17</v>
       </c>
-      <c r="S16" s="191">
+      <c r="S16" s="184">
         <v>-6.5</v>
       </c>
-      <c r="T16" s="186">
-        <v>-14.33</v>
+      <c r="T16" s="189">
+        <v>-12.41</v>
       </c>
     </row>
     <row r="17">
@@ -8988,7 +8988,7 @@
       <c r="C17" t="str">
         <v>001360</v>
       </c>
-      <c r="D17" s="197" t="str">
+      <c r="D17" s="196" t="str">
         <v>净卖: -1800.16万</v>
       </c>
       <c r="E17">
@@ -9003,41 +9003,41 @@
       <c r="H17">
         <v>0.1</v>
       </c>
-      <c r="I17" s="202">
+      <c r="I17" s="201">
         <v>-10.05</v>
       </c>
-      <c r="J17" s="198">
+      <c r="J17" s="202">
         <v>-19.04</v>
       </c>
       <c r="K17" s="203">
         <v>-21.15</v>
       </c>
-      <c r="L17" s="204">
+      <c r="L17" s="197">
         <v>-22.16</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="206">
         <v>-23.03</v>
       </c>
       <c r="N17" s="207">
         <v>-22.4</v>
       </c>
-      <c r="O17" s="200">
+      <c r="O17" s="208">
         <v>-24.18</v>
       </c>
-      <c r="P17" s="208">
+      <c r="P17" s="204">
         <v>-24.04</v>
       </c>
-      <c r="Q17" s="201">
+      <c r="Q17" s="198">
         <v>-23.85</v>
       </c>
-      <c r="R17" s="205">
+      <c r="R17" s="199">
         <v>-24.28</v>
       </c>
-      <c r="S17" s="206">
+      <c r="S17" s="205">
         <v>-24.47</v>
       </c>
-      <c r="T17" s="196">
-        <v>6.49</v>
+      <c r="T17" s="200">
+        <v>4.95</v>
       </c>
     </row>
     <row r="18">
@@ -9050,7 +9050,7 @@
       <c r="C18" t="str">
         <v>001360</v>
       </c>
-      <c r="D18" s="211" t="str">
+      <c r="D18" s="213" t="str">
         <v>净卖: -1799.99万</v>
       </c>
       <c r="E18">
@@ -9065,41 +9065,41 @@
       <c r="H18">
         <v>-9.14</v>
       </c>
-      <c r="I18" s="216">
+      <c r="I18" s="218">
         <v>-0.94</v>
       </c>
-      <c r="J18" s="212">
+      <c r="J18" s="210">
         <v>-3.53</v>
       </c>
-      <c r="K18" s="213">
+      <c r="K18" s="221">
         <v>-4.76</v>
       </c>
-      <c r="L18" s="209">
+      <c r="L18" s="214">
         <v>-5.82</v>
       </c>
-      <c r="M18" s="217">
+      <c r="M18" s="211">
         <v>-5.06</v>
       </c>
-      <c r="N18" s="218">
+      <c r="N18" s="215">
         <v>-7.24</v>
       </c>
-      <c r="O18" s="214">
+      <c r="O18" s="216">
         <v>-7.06</v>
       </c>
       <c r="P18" s="219">
         <v>-6.82</v>
       </c>
-      <c r="Q18" s="210">
+      <c r="Q18" s="220">
         <v>-7.35</v>
       </c>
-      <c r="R18" s="220">
+      <c r="R18" s="217">
         <v>-7.59</v>
       </c>
-      <c r="S18" s="221">
+      <c r="S18" s="209">
         <v>-6.59</v>
       </c>
-      <c r="T18" s="215">
-        <v>30.29</v>
+      <c r="T18" s="212">
+        <v>28.41</v>
       </c>
     </row>
     <row r="19">
@@ -9112,7 +9112,7 @@
       <c r="C19" t="str">
         <v>300620</v>
       </c>
-      <c r="D19" s="233" t="str">
+      <c r="D19" s="231" t="str">
         <v>净买: 1215.21万</v>
       </c>
       <c r="E19">
@@ -9127,41 +9127,41 @@
       <c r="H19">
         <v>19.99</v>
       </c>
-      <c r="I19" s="230">
+      <c r="I19" s="223">
         <v>0</v>
       </c>
-      <c r="J19" s="226">
+      <c r="J19" s="232">
         <v>20.01</v>
       </c>
-      <c r="K19" s="227">
+      <c r="K19" s="233">
         <v>21.14</v>
       </c>
-      <c r="L19" s="231">
+      <c r="L19" s="225">
         <v>24.09</v>
       </c>
-      <c r="M19" s="228">
+      <c r="M19" s="226">
         <v>46.79</v>
       </c>
-      <c r="N19" s="234">
+      <c r="N19" s="227">
         <v>50.73</v>
       </c>
-      <c r="O19" s="229">
+      <c r="O19" s="224">
         <v>40.57</v>
       </c>
-      <c r="P19" s="232">
+      <c r="P19" s="228">
         <v>31.96</v>
       </c>
-      <c r="Q19" s="222">
+      <c r="Q19" s="229">
         <v>34.41</v>
       </c>
-      <c r="R19" s="223">
+      <c r="R19" s="234">
         <v>39.6</v>
       </c>
-      <c r="S19" s="225">
+      <c r="S19" s="230">
         <v>34.69</v>
       </c>
-      <c r="T19" s="224">
-        <v>279.72</v>
+      <c r="T19" s="222">
+        <v>288.65</v>
       </c>
     </row>
     <row r="20">
@@ -9174,7 +9174,7 @@
       <c r="C20" t="str">
         <v>002177</v>
       </c>
-      <c r="D20" s="243" t="str">
+      <c r="D20" s="245" t="str">
         <v>净卖: -3762.63万</v>
       </c>
       <c r="E20">
@@ -9189,41 +9189,41 @@
       <c r="H20">
         <v>3.85</v>
       </c>
-      <c r="I20" s="235">
+      <c r="I20" s="241">
         <v>5.93</v>
       </c>
-      <c r="J20" s="244">
+      <c r="J20" s="242">
         <v>1.38</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="238">
         <v>-1.17</v>
       </c>
-      <c r="L20" s="247">
+      <c r="L20" s="246">
         <v>-10.91</v>
       </c>
-      <c r="M20" s="237">
+      <c r="M20" s="243">
         <v>-11.76</v>
       </c>
-      <c r="N20" s="238">
+      <c r="N20" s="247">
         <v>-12.39</v>
       </c>
-      <c r="O20" s="239">
+      <c r="O20" s="235">
         <v>-9.96</v>
       </c>
-      <c r="P20" s="240">
+      <c r="P20" s="244">
         <v>-15.15</v>
       </c>
-      <c r="Q20" s="245">
+      <c r="Q20" s="239">
         <v>-17.9</v>
       </c>
-      <c r="R20" s="246">
+      <c r="R20" s="236">
         <v>-19.39</v>
       </c>
-      <c r="S20" s="241">
+      <c r="S20" s="237">
         <v>-18.11</v>
       </c>
-      <c r="T20" s="242">
-        <v>-16.21</v>
+      <c r="T20" s="240">
+        <v>-19.39</v>
       </c>
     </row>
     <row r="21">
@@ -9236,7 +9236,7 @@
       <c r="C21" t="str">
         <v>301517</v>
       </c>
-      <c r="D21" s="257" t="str">
+      <c r="D21" s="250" t="str">
         <v>净买: 1391.15万</v>
       </c>
       <c r="E21">
@@ -9251,41 +9251,41 @@
       <c r="H21">
         <v>20</v>
       </c>
-      <c r="I21" s="249">
+      <c r="I21" s="256">
         <v>-14.18</v>
       </c>
-      <c r="J21" s="255">
+      <c r="J21" s="251">
         <v>-19.79</v>
       </c>
-      <c r="K21" s="250">
+      <c r="K21" s="259">
         <v>-18.67</v>
       </c>
-      <c r="L21" s="256">
+      <c r="L21" s="254">
         <v>-21.09</v>
       </c>
-      <c r="M21" s="251">
+      <c r="M21" s="255">
         <v>-22.21</v>
       </c>
-      <c r="N21" s="258">
+      <c r="N21" s="252">
         <v>-18.54</v>
       </c>
-      <c r="O21" s="260">
+      <c r="O21" s="257">
         <v>-22.58</v>
       </c>
-      <c r="P21" s="259">
+      <c r="P21" s="260">
         <v>-27.04</v>
       </c>
-      <c r="Q21" s="252">
+      <c r="Q21" s="248">
         <v>-25.09</v>
       </c>
-      <c r="R21" s="253">
+      <c r="R21" s="258">
         <v>-21.88</v>
       </c>
-      <c r="S21" s="254">
+      <c r="S21" s="253">
         <v>-25.85</v>
       </c>
-      <c r="T21" s="248">
-        <v>21.25</v>
+      <c r="T21" s="249">
+        <v>20.72</v>
       </c>
     </row>
     <row r="22">
@@ -9298,7 +9298,7 @@
       <c r="C22" t="str">
         <v>002547</v>
       </c>
-      <c r="D22" s="269" t="str">
+      <c r="D22" s="271" t="str">
         <v>净买: 4862.70万</v>
       </c>
       <c r="E22">
@@ -9313,41 +9313,41 @@
       <c r="H22">
         <v>10.1</v>
       </c>
-      <c r="I22" s="261">
+      <c r="I22" s="263">
         <v>0</v>
       </c>
-      <c r="J22" s="262">
+      <c r="J22" s="265">
         <v>7.01</v>
       </c>
-      <c r="K22" s="264">
+      <c r="K22" s="268">
         <v>0.36</v>
       </c>
-      <c r="L22" s="265">
+      <c r="L22" s="272">
         <v>4.68</v>
       </c>
       <c r="M22" s="266">
         <v>15.11</v>
       </c>
-      <c r="N22" s="270">
+      <c r="N22" s="273">
         <v>21.76</v>
       </c>
-      <c r="O22" s="267">
+      <c r="O22" s="269">
         <v>22.66</v>
       </c>
-      <c r="P22" s="271">
+      <c r="P22" s="264">
         <v>17.81</v>
       </c>
-      <c r="Q22" s="272">
+      <c r="Q22" s="267">
         <v>9.17</v>
       </c>
-      <c r="R22" s="263">
+      <c r="R22" s="261">
         <v>12.59</v>
       </c>
-      <c r="S22" s="273">
+      <c r="S22" s="262">
         <v>7.01</v>
       </c>
-      <c r="T22" s="268">
-        <v>-37.59</v>
+      <c r="T22" s="270">
+        <v>-39.03</v>
       </c>
     </row>
     <row r="23">
@@ -9360,7 +9360,7 @@
       <c r="C23" t="str">
         <v>002547</v>
       </c>
-      <c r="D23" s="286" t="str">
+      <c r="D23" s="285" t="str">
         <v>净卖: -5175.09万</v>
       </c>
       <c r="E23">
@@ -9378,38 +9378,38 @@
       <c r="I23" s="274">
         <v>7.01</v>
       </c>
-      <c r="J23" s="275">
+      <c r="J23" s="286">
         <v>0.36</v>
       </c>
-      <c r="K23" s="278">
+      <c r="K23" s="275">
         <v>4.68</v>
       </c>
       <c r="L23" s="282">
         <v>15.11</v>
       </c>
-      <c r="M23" s="279">
+      <c r="M23" s="277">
         <v>21.76</v>
       </c>
-      <c r="N23" s="285">
+      <c r="N23" s="278">
         <v>22.66</v>
       </c>
-      <c r="O23" s="283">
+      <c r="O23" s="279">
         <v>17.81</v>
       </c>
       <c r="P23" s="276">
         <v>9.17</v>
       </c>
-      <c r="Q23" s="277">
+      <c r="Q23" s="280">
         <v>12.59</v>
       </c>
-      <c r="R23" s="280">
+      <c r="R23" s="283">
         <v>7.01</v>
       </c>
-      <c r="S23" s="281">
+      <c r="S23" s="284">
         <v>8.09</v>
       </c>
-      <c r="T23" s="284">
-        <v>-37.59</v>
+      <c r="T23" s="281">
+        <v>-39.03</v>
       </c>
     </row>
     <row r="24">
@@ -9422,7 +9422,7 @@
       <c r="C24" t="str">
         <v>920020</v>
       </c>
-      <c r="D24" s="293" t="str">
+      <c r="D24" s="291" t="str">
         <v>净卖: -668.61万</v>
       </c>
       <c r="E24">
@@ -9437,41 +9437,41 @@
       <c r="H24">
         <v>-9.66</v>
       </c>
-      <c r="I24" s="297">
+      <c r="I24" s="296">
         <v>14.02</v>
       </c>
-      <c r="J24" s="298">
+      <c r="J24" s="297">
         <v>2.92</v>
       </c>
-      <c r="K24" s="299">
+      <c r="K24" s="298">
         <v>1.38</v>
       </c>
-      <c r="L24" s="287">
+      <c r="L24" s="293">
         <v>0.51</v>
       </c>
-      <c r="M24" s="295">
+      <c r="M24" s="294">
         <v>-0.82</v>
       </c>
-      <c r="N24" s="289">
+      <c r="N24" s="292">
         <v>-0.87</v>
       </c>
-      <c r="O24" s="288">
+      <c r="O24" s="289">
         <v>0.87</v>
       </c>
-      <c r="P24" s="290">
+      <c r="P24" s="299">
         <v>-2.4</v>
       </c>
-      <c r="Q24" s="291">
+      <c r="Q24" s="290">
         <v>-5.17</v>
       </c>
-      <c r="R24" s="296">
+      <c r="R24" s="295">
         <v>-4.76</v>
       </c>
-      <c r="S24" s="294">
+      <c r="S24" s="287">
         <v>-4.35</v>
       </c>
-      <c r="T24" s="292">
-        <v>-17.49</v>
+      <c r="T24" s="288">
+        <v>-18.26</v>
       </c>
     </row>
     <row r="25">
@@ -9484,7 +9484,7 @@
       <c r="C25" t="str">
         <v>605178</v>
       </c>
-      <c r="D25" s="308" t="str">
+      <c r="D25" s="305" t="str">
         <v>净买: 3874.18万</v>
       </c>
       <c r="E25">
@@ -9499,41 +9499,41 @@
       <c r="H25">
         <v>10</v>
       </c>
-      <c r="I25" s="309">
+      <c r="I25" s="301">
         <v>0</v>
       </c>
-      <c r="J25" s="305">
+      <c r="J25" s="302">
         <v>10</v>
       </c>
-      <c r="K25" s="310">
+      <c r="K25" s="308">
         <v>0.58</v>
       </c>
-      <c r="L25" s="306">
+      <c r="L25" s="311">
         <v>4.74</v>
       </c>
-      <c r="M25" s="311">
+      <c r="M25" s="312">
         <v>13.42</v>
       </c>
-      <c r="N25" s="301">
+      <c r="N25" s="303">
         <v>19.72</v>
       </c>
-      <c r="O25" s="302">
+      <c r="O25" s="306">
         <v>26.01</v>
       </c>
-      <c r="P25" s="303">
+      <c r="P25" s="307">
         <v>16.89</v>
       </c>
-      <c r="Q25" s="312">
+      <c r="Q25" s="309">
         <v>6.52</v>
       </c>
-      <c r="R25" s="304">
+      <c r="R25" s="300">
         <v>10.9</v>
       </c>
-      <c r="S25" s="307">
+      <c r="S25" s="304">
         <v>12.81</v>
       </c>
-      <c r="T25" s="300">
-        <v>23.14</v>
+      <c r="T25" s="310">
+        <v>10.82</v>
       </c>
     </row>
     <row r="26">
@@ -9546,7 +9546,7 @@
       <c r="C26" t="str">
         <v>000407</v>
       </c>
-      <c r="D26" s="313" t="str">
+      <c r="D26" s="316" t="str">
         <v>净买: 788.81万</v>
       </c>
       <c r="E26">
@@ -9561,40 +9561,40 @@
       <c r="H26">
         <v>10.1</v>
       </c>
-      <c r="I26" s="314">
+      <c r="I26" s="317">
         <v>0</v>
       </c>
-      <c r="J26" s="315">
+      <c r="J26" s="324">
         <v>10.04</v>
       </c>
-      <c r="K26" s="316">
+      <c r="K26" s="318">
         <v>20.96</v>
       </c>
-      <c r="L26" s="322">
+      <c r="L26" s="319">
         <v>32.97</v>
       </c>
-      <c r="M26" s="317">
+      <c r="M26" s="325">
         <v>46.29</v>
       </c>
-      <c r="N26" s="319">
+      <c r="N26" s="320">
         <v>31.66</v>
       </c>
-      <c r="O26" s="320">
+      <c r="O26" s="321">
         <v>30.35</v>
       </c>
-      <c r="P26" s="321">
+      <c r="P26" s="322">
         <v>17.25</v>
       </c>
-      <c r="Q26" s="323">
+      <c r="Q26" s="313">
         <v>5.46</v>
       </c>
-      <c r="R26" s="318">
+      <c r="R26" s="315">
         <v>5.9</v>
       </c>
-      <c r="S26" s="324">
+      <c r="S26" s="314">
         <v>12.45</v>
       </c>
-      <c r="T26" s="325">
+      <c r="T26" s="323">
         <v>2.84</v>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="334" t="str">
+      <c r="D27" s="332" t="str">
         <v>净买: 3123.85万</v>
       </c>
       <c r="E27">
@@ -9623,41 +9623,41 @@
       <c r="H27">
         <v>9.96</v>
       </c>
-      <c r="I27" s="326">
+      <c r="I27" s="333">
         <v>0</v>
       </c>
-      <c r="J27" s="327">
+      <c r="J27" s="334">
         <v>-9.95</v>
       </c>
       <c r="K27" s="328">
         <v>-19.01</v>
       </c>
-      <c r="L27" s="337">
+      <c r="L27" s="330">
         <v>-27.04</v>
       </c>
-      <c r="M27" s="332">
+      <c r="M27" s="335">
         <v>-30.61</v>
       </c>
-      <c r="N27" s="329">
+      <c r="N27" s="331">
         <v>-28.7</v>
       </c>
-      <c r="O27" s="333">
+      <c r="O27" s="336">
         <v>-31.89</v>
       </c>
-      <c r="P27" s="335">
+      <c r="P27" s="326">
         <v>-31.63</v>
       </c>
-      <c r="Q27" s="336">
+      <c r="Q27" s="337">
         <v>-28.95</v>
       </c>
       <c r="R27" s="338">
         <v>-26.53</v>
       </c>
-      <c r="S27" s="330">
+      <c r="S27" s="329">
         <v>-24.49</v>
       </c>
-      <c r="T27" s="331">
-        <v>-23.21</v>
+      <c r="T27" s="327">
+        <v>-24.23</v>
       </c>
     </row>
     <row r="28">
@@ -9670,7 +9670,7 @@
       <c r="C28" t="str">
         <v>300094</v>
       </c>
-      <c r="D28" s="343" t="str">
+      <c r="D28" s="351" t="str">
         <v>净卖: -3846.51万</v>
       </c>
       <c r="E28">
@@ -9685,19 +9685,19 @@
       <c r="H28">
         <v>0.37</v>
       </c>
-      <c r="I28" s="351">
+      <c r="I28" s="345">
         <v>-11.85</v>
       </c>
-      <c r="J28" s="346">
+      <c r="J28" s="339">
         <v>-12.41</v>
       </c>
-      <c r="K28" s="339">
+      <c r="K28" s="340">
         <v>-8.33</v>
       </c>
-      <c r="L28" s="340">
+      <c r="L28" s="346">
         <v>-17.96</v>
       </c>
-      <c r="M28" s="341">
+      <c r="M28" s="342">
         <v>-23.89</v>
       </c>
       <c r="N28" s="347">
@@ -9706,20 +9706,20 @@
       <c r="O28" s="348">
         <v>-24.26</v>
       </c>
-      <c r="P28" s="344">
+      <c r="P28" s="349">
         <v>-23.15</v>
       </c>
-      <c r="Q28" s="349">
+      <c r="Q28" s="343">
         <v>-21.48</v>
       </c>
-      <c r="R28" s="350">
+      <c r="R28" s="341">
         <v>-21.85</v>
       </c>
-      <c r="S28" s="345">
+      <c r="S28" s="350">
         <v>-27.78</v>
       </c>
-      <c r="T28" s="342">
-        <v>-41.85</v>
+      <c r="T28" s="344">
+        <v>-41.48</v>
       </c>
     </row>
     <row r="29">
@@ -9732,7 +9732,7 @@
       <c r="C29" t="str">
         <v>002682</v>
       </c>
-      <c r="D29" s="364" t="str">
+      <c r="D29" s="355" t="str">
         <v>净卖: -2565.97万</v>
       </c>
       <c r="E29">
@@ -9747,41 +9747,41 @@
       <c r="H29">
         <v>-6.94</v>
       </c>
-      <c r="I29" s="352">
+      <c r="I29" s="358">
         <v>-3.35</v>
       </c>
-      <c r="J29" s="361">
+      <c r="J29" s="362">
         <v>-12.94</v>
       </c>
-      <c r="K29" s="357">
+      <c r="K29" s="363">
         <v>-17.2</v>
       </c>
-      <c r="L29" s="358">
+      <c r="L29" s="359">
         <v>-14.92</v>
       </c>
-      <c r="M29" s="353">
+      <c r="M29" s="360">
         <v>-18.72</v>
       </c>
-      <c r="N29" s="354">
+      <c r="N29" s="356">
         <v>-18.42</v>
       </c>
-      <c r="O29" s="362">
+      <c r="O29" s="364">
         <v>-15.22</v>
       </c>
-      <c r="P29" s="360">
+      <c r="P29" s="352">
         <v>-12.33</v>
       </c>
-      <c r="Q29" s="359">
+      <c r="Q29" s="357">
         <v>-9.89</v>
       </c>
-      <c r="R29" s="355">
+      <c r="R29" s="353">
         <v>-0.91</v>
       </c>
-      <c r="S29" s="356">
+      <c r="S29" s="361">
         <v>8.98</v>
       </c>
-      <c r="T29" s="363">
-        <v>-8.37</v>
+      <c r="T29" s="354">
+        <v>-9.59</v>
       </c>
     </row>
     <row r="30">
@@ -9794,7 +9794,7 @@
       <c r="C30" t="str">
         <v>603069</v>
       </c>
-      <c r="D30" s="370" t="str">
+      <c r="D30" s="369" t="str">
         <v>净买: 2184.48万</v>
       </c>
       <c r="E30">
@@ -9809,41 +9809,41 @@
       <c r="H30">
         <v>10.02</v>
       </c>
-      <c r="I30" s="367">
+      <c r="I30" s="375">
         <v>0</v>
       </c>
-      <c r="J30" s="371">
+      <c r="J30" s="370">
         <v>1.25</v>
       </c>
-      <c r="K30" s="372">
+      <c r="K30" s="376">
         <v>-4.36</v>
       </c>
-      <c r="L30" s="368">
+      <c r="L30" s="371">
         <v>5.19</v>
       </c>
-      <c r="M30" s="377">
+      <c r="M30" s="366">
         <v>-1.42</v>
       </c>
-      <c r="N30" s="365">
+      <c r="N30" s="377">
         <v>-5.96</v>
       </c>
-      <c r="O30" s="366">
+      <c r="O30" s="372">
         <v>-5.99</v>
       </c>
-      <c r="P30" s="374">
+      <c r="P30" s="373">
         <v>-13.57</v>
       </c>
-      <c r="Q30" s="375">
+      <c r="Q30" s="365">
         <v>-13.64</v>
       </c>
-      <c r="R30" s="376">
+      <c r="R30" s="367">
         <v>-14.16</v>
       </c>
-      <c r="S30" s="373">
+      <c r="S30" s="368">
         <v>-15.27</v>
       </c>
-      <c r="T30" s="369">
-        <v>-38.47</v>
+      <c r="T30" s="374">
+        <v>-40.13</v>
       </c>
     </row>
     <row r="31">
@@ -9856,7 +9856,7 @@
       <c r="C31" t="str">
         <v>002009</v>
       </c>
-      <c r="D31" s="389" t="str">
+      <c r="D31" s="385" t="str">
         <v>净买: 3463.54万</v>
       </c>
       <c r="E31">
@@ -9871,41 +9871,41 @@
       <c r="H31">
         <v>10</v>
       </c>
-      <c r="I31" s="378">
+      <c r="I31" s="382">
         <v>0</v>
       </c>
-      <c r="J31" s="384">
+      <c r="J31" s="383">
         <v>10.02</v>
       </c>
-      <c r="K31" s="385">
+      <c r="K31" s="379">
         <v>21.02</v>
       </c>
       <c r="L31" s="386">
         <v>16.84</v>
       </c>
-      <c r="M31" s="380">
+      <c r="M31" s="388">
         <v>14.72</v>
       </c>
-      <c r="N31" s="381">
+      <c r="N31" s="384">
         <v>8.01</v>
       </c>
-      <c r="O31" s="382">
+      <c r="O31" s="389">
         <v>12.24</v>
       </c>
-      <c r="P31" s="387">
+      <c r="P31" s="380">
         <v>12.65</v>
       </c>
-      <c r="Q31" s="388">
+      <c r="Q31" s="381">
         <v>15.19</v>
       </c>
-      <c r="R31" s="383">
+      <c r="R31" s="390">
         <v>18.85</v>
       </c>
-      <c r="S31" s="379">
+      <c r="S31" s="387">
         <v>11.93</v>
       </c>
-      <c r="T31" s="390">
-        <v>28.1</v>
+      <c r="T31" s="378">
+        <v>29.65</v>
       </c>
     </row>
     <row r="32">
@@ -9918,7 +9918,7 @@
       <c r="C32" t="str">
         <v>002009</v>
       </c>
-      <c r="D32" s="395" t="str">
+      <c r="D32" s="394" t="str">
         <v>净卖: -4207.08万</v>
       </c>
       <c r="E32">
@@ -9933,41 +9933,41 @@
       <c r="H32">
         <v>9.92</v>
       </c>
-      <c r="I32" s="396">
+      <c r="I32" s="397">
         <v>0.09</v>
       </c>
-      <c r="J32" s="397">
+      <c r="J32" s="401">
         <v>10.1</v>
       </c>
-      <c r="K32" s="398">
+      <c r="K32" s="391">
         <v>6.3</v>
       </c>
-      <c r="L32" s="393">
+      <c r="L32" s="398">
         <v>4.37</v>
       </c>
-      <c r="M32" s="399">
+      <c r="M32" s="392">
         <v>-1.74</v>
       </c>
-      <c r="N32" s="400">
+      <c r="N32" s="402">
         <v>2.11</v>
       </c>
-      <c r="O32" s="402">
+      <c r="O32" s="393">
         <v>2.49</v>
       </c>
-      <c r="P32" s="403">
+      <c r="P32" s="395">
         <v>4.79</v>
       </c>
-      <c r="Q32" s="391">
+      <c r="Q32" s="399">
         <v>8.13</v>
       </c>
-      <c r="R32" s="401">
+      <c r="R32" s="396">
         <v>1.83</v>
       </c>
-      <c r="S32" s="392">
+      <c r="S32" s="403">
         <v>2.63</v>
       </c>
-      <c r="T32" s="394">
-        <v>16.54</v>
+      <c r="T32" s="400">
+        <v>17.95</v>
       </c>
     </row>
     <row r="33">
@@ -9995,41 +9995,41 @@
       <c r="H33">
         <v>2.21</v>
       </c>
-      <c r="I33" s="410">
+      <c r="I33" s="408">
         <v>7.63</v>
       </c>
-      <c r="J33" s="414">
+      <c r="J33" s="409">
         <v>3.9</v>
       </c>
       <c r="K33" s="415">
         <v>2.02</v>
       </c>
-      <c r="L33" s="416">
+      <c r="L33" s="410">
         <v>-3.95</v>
       </c>
-      <c r="M33" s="404">
+      <c r="M33" s="412">
         <v>-0.18</v>
       </c>
-      <c r="N33" s="405">
+      <c r="N33" s="406">
         <v>0.18</v>
       </c>
-      <c r="O33" s="411">
+      <c r="O33" s="413">
         <v>2.43</v>
       </c>
-      <c r="P33" s="412">
+      <c r="P33" s="416">
         <v>5.7</v>
       </c>
-      <c r="Q33" s="413">
+      <c r="Q33" s="414">
         <v>-0.46</v>
       </c>
-      <c r="R33" s="408">
+      <c r="R33" s="404">
         <v>0.32</v>
       </c>
-      <c r="S33" s="406">
+      <c r="S33" s="411">
         <v>-1.52</v>
       </c>
-      <c r="T33" s="409">
-        <v>13.92</v>
+      <c r="T33" s="405">
+        <v>15.3</v>
       </c>
     </row>
     <row r="34">
@@ -10042,7 +10042,7 @@
       <c r="C34" t="str">
         <v>002969</v>
       </c>
-      <c r="D34" s="422" t="str">
+      <c r="D34" s="417" t="str">
         <v>净卖: -2752.13万</v>
       </c>
       <c r="E34">
@@ -10057,19 +10057,19 @@
       <c r="H34">
         <v>0.55</v>
       </c>
-      <c r="I34" s="423">
+      <c r="I34" s="428">
         <v>7.62</v>
       </c>
-      <c r="J34" s="417">
+      <c r="J34" s="418">
         <v>18.38</v>
       </c>
-      <c r="K34" s="419">
+      <c r="K34" s="429">
         <v>30.24</v>
       </c>
-      <c r="L34" s="424">
+      <c r="L34" s="419">
         <v>37.86</v>
       </c>
-      <c r="M34" s="425">
+      <c r="M34" s="423">
         <v>51.69</v>
       </c>
       <c r="N34" s="426">
@@ -10081,17 +10081,17 @@
       <c r="P34" s="421">
         <v>35.11</v>
       </c>
-      <c r="Q34" s="418">
+      <c r="Q34" s="424">
         <v>48.63</v>
       </c>
-      <c r="R34" s="429">
+      <c r="R34" s="422">
         <v>52.47</v>
       </c>
-      <c r="S34" s="427">
+      <c r="S34" s="425">
         <v>67.71</v>
       </c>
-      <c r="T34" s="428">
-        <v>77.53</v>
+      <c r="T34" s="427">
+        <v>71.17</v>
       </c>
     </row>
     <row r="35">
@@ -10104,7 +10104,7 @@
       <c r="C35" t="str">
         <v>600683</v>
       </c>
-      <c r="D35" s="440" t="str">
+      <c r="D35" s="438" t="str">
         <v>净买: 819.30万</v>
       </c>
       <c r="E35">
@@ -10119,41 +10119,41 @@
       <c r="H35">
         <v>10.1</v>
       </c>
-      <c r="I35" s="433">
+      <c r="I35" s="432">
         <v>0</v>
       </c>
-      <c r="J35" s="430">
+      <c r="J35" s="442">
         <v>10.09</v>
       </c>
-      <c r="K35" s="441">
+      <c r="K35" s="439">
         <v>21.1</v>
       </c>
-      <c r="L35" s="434">
+      <c r="L35" s="440">
         <v>11.01</v>
       </c>
-      <c r="M35" s="435">
+      <c r="M35" s="433">
         <v>22.2</v>
       </c>
-      <c r="N35" s="442">
+      <c r="N35" s="437">
         <v>22.57</v>
       </c>
-      <c r="O35" s="436">
+      <c r="O35" s="430">
         <v>32.29</v>
       </c>
-      <c r="P35" s="439">
+      <c r="P35" s="431">
         <v>27.16</v>
       </c>
-      <c r="Q35" s="431">
+      <c r="Q35" s="441">
         <v>23.12</v>
       </c>
-      <c r="R35" s="432">
+      <c r="R35" s="434">
         <v>30.46</v>
       </c>
-      <c r="S35" s="437">
+      <c r="S35" s="435">
         <v>37.06</v>
       </c>
-      <c r="T35" s="438">
-        <v>121.1</v>
+      <c r="T35" s="436">
+        <v>119.27</v>
       </c>
     </row>
     <row r="36">
@@ -10166,7 +10166,7 @@
       <c r="C36" t="str">
         <v>002056</v>
       </c>
-      <c r="D36" s="454" t="str">
+      <c r="D36" s="450" t="str">
         <v>净卖: -2838.92万</v>
       </c>
       <c r="E36">
@@ -10181,41 +10181,41 @@
       <c r="H36">
         <v>1.28</v>
       </c>
-      <c r="I36" s="445">
+      <c r="I36" s="451">
         <v>8.62</v>
       </c>
-      <c r="J36" s="449">
+      <c r="J36" s="444">
         <v>-0.42</v>
       </c>
-      <c r="K36" s="446">
+      <c r="K36" s="445">
         <v>-4.25</v>
       </c>
-      <c r="L36" s="450">
+      <c r="L36" s="455">
         <v>-5.84</v>
       </c>
       <c r="M36" s="452">
         <v>-8.66</v>
       </c>
-      <c r="N36" s="455">
+      <c r="N36" s="446">
         <v>-6.43</v>
       </c>
       <c r="O36" s="447">
         <v>-9.21</v>
       </c>
-      <c r="P36" s="448">
+      <c r="P36" s="443">
         <v>-9.21</v>
       </c>
       <c r="Q36" s="453">
         <v>-7.78</v>
       </c>
-      <c r="R36" s="451">
+      <c r="R36" s="448">
         <v>-9.46</v>
       </c>
-      <c r="S36" s="443">
+      <c r="S36" s="449">
         <v>-9.92</v>
       </c>
-      <c r="T36" s="444">
-        <v>-17.44</v>
+      <c r="T36" s="454">
+        <v>-16.35</v>
       </c>
     </row>
     <row r="37">
@@ -10277,40 +10277,40 @@
       <c r="F38" t="str"/>
       <c r="G38" t="str"/>
       <c r="H38" t="str"/>
-      <c r="I38" s="460">
+      <c r="I38" s="463">
         <v>31.43</v>
       </c>
-      <c r="J38" s="458">
+      <c r="J38" s="460">
         <v>62.86</v>
       </c>
-      <c r="K38" s="459">
+      <c r="K38" s="464">
         <v>54.29</v>
       </c>
-      <c r="L38" s="461">
+      <c r="L38" s="457">
         <v>54.29</v>
       </c>
-      <c r="M38" s="462">
+      <c r="M38" s="465">
         <v>42.86</v>
       </c>
-      <c r="N38" s="463">
+      <c r="N38" s="458">
         <v>42.86</v>
       </c>
-      <c r="O38" s="464">
+      <c r="O38" s="459">
         <v>48.57</v>
       </c>
-      <c r="P38" s="467">
+      <c r="P38" s="466">
         <v>37.14</v>
       </c>
-      <c r="Q38" s="457">
+      <c r="Q38" s="461">
         <v>31.43</v>
       </c>
-      <c r="R38" s="465">
+      <c r="R38" s="462">
         <v>34.29</v>
       </c>
-      <c r="S38" s="456">
+      <c r="S38" s="467">
         <v>31.43</v>
       </c>
-      <c r="T38" s="466">
+      <c r="T38" s="456">
         <v>48.57</v>
       </c>
     </row>
@@ -10325,41 +10325,41 @@
       <c r="F39" t="str"/>
       <c r="G39" t="str"/>
       <c r="H39" t="str"/>
-      <c r="I39" s="473">
+      <c r="I39" s="470">
         <v>0.72</v>
       </c>
-      <c r="J39" s="474">
+      <c r="J39" s="471">
         <v>1.7</v>
       </c>
-      <c r="K39" s="468">
+      <c r="K39" s="474">
         <v>1.83</v>
       </c>
-      <c r="L39" s="470">
+      <c r="L39" s="475">
         <v>1.8</v>
       </c>
-      <c r="M39" s="475">
+      <c r="M39" s="477">
         <v>1.64</v>
       </c>
-      <c r="N39" s="469">
+      <c r="N39" s="472">
         <v>0.36</v>
       </c>
-      <c r="O39" s="476">
+      <c r="O39" s="478">
         <v>0.46</v>
       </c>
-      <c r="P39" s="471">
+      <c r="P39" s="468">
         <v>-2.04</v>
       </c>
-      <c r="Q39" s="472">
+      <c r="Q39" s="479">
         <v>-3.24</v>
       </c>
-      <c r="R39" s="478">
+      <c r="R39" s="473">
         <v>-2.68</v>
       </c>
-      <c r="S39" s="479">
+      <c r="S39" s="476">
         <v>-2.27</v>
       </c>
-      <c r="T39" s="477">
-        <v>11.81</v>
+      <c r="T39" s="469">
+        <v>10.96</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/正经哥/index.xlsx
+++ b/youzi/正经哥/index.xlsx
@@ -39,6 +39,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -57,37 +63,577 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF36AC51"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1D7E35"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,49 +651,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,25 +807,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,7 +837,1639 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBF8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,31 +2481,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -237,43 +2493,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,43 +2529,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -345,49 +2685,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -399,613 +2733,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
+        <fgColor rgb="FFECF7EF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1017,1675 +2745,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7FBF8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2697,13 +2763,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B460"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2715,55 +2781,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2775,25 +2817,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF65C07A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
+        <fgColor rgb="FF65C07A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2805,37 +2835,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF1B7431"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2853,61 +2871,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDE4654"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2B6BC"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4654"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8058,7 +8058,7 @@
       <c r="C2" t="str">
         <v>000665</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="1" t="str">
         <v>净卖: -2301.68万</v>
       </c>
       <c r="E2">
@@ -8073,41 +8073,41 @@
       <c r="H2">
         <v>10.06</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="2">
         <v>0</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="6">
         <v>10</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="8">
         <v>21.03</v>
       </c>
       <c r="L2" s="3">
         <v>30</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="11">
         <v>18.79</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="9">
         <v>10</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="12">
         <v>11.72</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="4">
         <v>10.17</v>
       </c>
       <c r="Q2" s="13">
         <v>2.07</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="10">
         <v>-4.66</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="7">
         <v>-8.45</v>
       </c>
-      <c r="T2" s="6">
-        <v>-18.97</v>
+      <c r="T2" s="5">
+        <v>-20</v>
       </c>
     </row>
     <row r="3">
@@ -8120,7 +8120,7 @@
       <c r="C3" t="str">
         <v>002300</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="24" t="str">
         <v>净买: 2299.17万</v>
       </c>
       <c r="E3">
@@ -8135,41 +8135,41 @@
       <c r="H3">
         <v>9.95</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="21">
         <v>0</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="14">
         <v>10.06</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="15">
         <v>21.12</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="25">
         <v>9.77</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="22">
         <v>-1.15</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="16">
         <v>-8.76</v>
       </c>
       <c r="O3" s="18">
         <v>-11.35</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="17">
         <v>-12.36</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="23">
         <v>-13.22</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="19">
         <v>-21.84</v>
       </c>
-      <c r="S3" s="19">
+      <c r="S3" s="26">
         <v>-23.99</v>
       </c>
-      <c r="T3" s="14">
-        <v>48.56</v>
+      <c r="T3" s="20">
+        <v>48.28</v>
       </c>
     </row>
     <row r="4">
@@ -8182,7 +8182,7 @@
       <c r="C4" t="str">
         <v>002300</v>
       </c>
-      <c r="D4" s="33" t="str">
+      <c r="D4" s="34" t="str">
         <v>净卖: -2576.68万</v>
       </c>
       <c r="E4">
@@ -8197,41 +8197,41 @@
       <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="39">
         <v>9.34</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="37">
         <v>-0.91</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="32">
         <v>-10.77</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="27">
         <v>-17.64</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="28">
         <v>-19.97</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="35">
         <v>-20.88</v>
       </c>
       <c r="O4" s="29">
         <v>-21.66</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="30">
         <v>-29.44</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="33">
         <v>-31.39</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="31">
         <v>-28.92</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="36">
         <v>-27.63</v>
       </c>
-      <c r="T4" s="30">
-        <v>34.11</v>
+      <c r="T4" s="38">
+        <v>33.85</v>
       </c>
     </row>
     <row r="5">
@@ -8244,7 +8244,7 @@
       <c r="C5" t="str">
         <v>002688</v>
       </c>
-      <c r="D5" s="49" t="str">
+      <c r="D5" s="45" t="str">
         <v>净买: 5775.20万</v>
       </c>
       <c r="E5">
@@ -8262,38 +8262,38 @@
       <c r="I5" s="52">
         <v>0</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="47">
         <v>9.95</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="46">
         <v>20.98</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="40">
         <v>30.17</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="43">
         <v>17.15</v>
       </c>
       <c r="N5" s="48">
         <v>8.58</v>
       </c>
-      <c r="O5" s="51">
+      <c r="O5" s="41">
         <v>10.57</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="49">
         <v>-0.46</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="50">
         <v>-5.36</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="42">
         <v>-5.05</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="51">
         <v>-4.29</v>
       </c>
-      <c r="T5" s="47">
-        <v>-11.49</v>
+      <c r="T5" s="44">
+        <v>-11.03</v>
       </c>
     </row>
     <row r="6">
@@ -8306,7 +8306,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="55" t="str">
         <v>净卖: -7396.08万</v>
       </c>
       <c r="E6">
@@ -8321,41 +8321,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="58">
         <v>7.59</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="65">
         <v>-3.16</v>
       </c>
-      <c r="K6" s="65">
+      <c r="K6" s="59">
         <v>-10.25</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="56">
         <v>-8.61</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="53">
         <v>-17.72</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="62">
         <v>-21.77</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="63">
         <v>-21.52</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="64">
         <v>-20.89</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="57">
         <v>-16.71</v>
       </c>
-      <c r="R6" s="63">
+      <c r="R6" s="54">
         <v>-20.76</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="60">
         <v>-17.09</v>
       </c>
-      <c r="T6" s="64">
-        <v>-26.84</v>
+      <c r="T6" s="61">
+        <v>-26.46</v>
       </c>
     </row>
     <row r="7">
@@ -8368,7 +8368,7 @@
       <c r="C7" t="str">
         <v>600697</v>
       </c>
-      <c r="D7" s="76" t="str">
+      <c r="D7" s="69" t="str">
         <v>净卖: -2819.93万</v>
       </c>
       <c r="E7">
@@ -8383,41 +8383,41 @@
       <c r="H7">
         <v>-9.28</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="78">
         <v>3.2</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="66">
         <v>6.95</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="70">
         <v>17.66</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="71">
         <v>13.12</v>
       </c>
-      <c r="M7" s="73">
+      <c r="M7" s="72">
         <v>1.95</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="67">
         <v>0</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="73">
         <v>4.3</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="74">
         <v>-1.72</v>
       </c>
-      <c r="Q7" s="74">
+      <c r="Q7" s="68">
         <v>-5.31</v>
       </c>
-      <c r="R7" s="68">
+      <c r="R7" s="75">
         <v>-5.23</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="76">
         <v>-7.97</v>
       </c>
-      <c r="T7" s="75">
-        <v>-8.36</v>
+      <c r="T7" s="77">
+        <v>-8.44</v>
       </c>
     </row>
     <row r="8">
@@ -8430,7 +8430,7 @@
       <c r="C8" t="str">
         <v>600828</v>
       </c>
-      <c r="D8" s="90" t="str">
+      <c r="D8" s="87" t="str">
         <v>净买: 1425.83万</v>
       </c>
       <c r="E8">
@@ -8445,41 +8445,41 @@
       <c r="H8">
         <v>10.11</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="79">
         <v>0</v>
       </c>
-      <c r="J8" s="91">
+      <c r="J8" s="80">
         <v>10.02</v>
       </c>
-      <c r="K8" s="88">
+      <c r="K8" s="81">
         <v>7.31</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="88">
         <v>5.01</v>
       </c>
-      <c r="M8" s="80">
+      <c r="M8" s="82">
         <v>10.65</v>
       </c>
-      <c r="N8" s="86">
+      <c r="N8" s="83">
         <v>5.43</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="86">
         <v>-5.01</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="84">
         <v>-10.02</v>
       </c>
-      <c r="Q8" s="89">
+      <c r="Q8" s="85">
         <v>-12.73</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="89">
         <v>-11.69</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="90">
         <v>-10.65</v>
       </c>
-      <c r="T8" s="83">
-        <v>8.56</v>
+      <c r="T8" s="91">
+        <v>5.01</v>
       </c>
     </row>
     <row r="9">
@@ -8492,7 +8492,7 @@
       <c r="C9" t="str">
         <v>600828</v>
       </c>
-      <c r="D9" s="100" t="str">
+      <c r="D9" s="101" t="str">
         <v>净卖: -1514.63万</v>
       </c>
       <c r="E9">
@@ -8507,41 +8507,41 @@
       <c r="H9">
         <v>-0.21</v>
       </c>
-      <c r="I9" s="101">
+      <c r="I9" s="97">
         <v>10.25</v>
       </c>
-      <c r="J9" s="95">
+      <c r="J9" s="98">
         <v>7.53</v>
       </c>
-      <c r="K9" s="102">
+      <c r="K9" s="104">
         <v>5.23</v>
       </c>
-      <c r="L9" s="103">
+      <c r="L9" s="102">
         <v>10.88</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="92">
         <v>5.65</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="94">
         <v>-4.81</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="95">
         <v>-9.83</v>
       </c>
-      <c r="P9" s="104">
+      <c r="P9" s="103">
         <v>-12.55</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="99">
         <v>-11.51</v>
       </c>
-      <c r="R9" s="99">
+      <c r="R9" s="96">
         <v>-10.46</v>
       </c>
-      <c r="S9" s="98">
+      <c r="S9" s="93">
         <v>-12.34</v>
       </c>
-      <c r="T9" s="94">
-        <v>8.79</v>
+      <c r="T9" s="100">
+        <v>5.23</v>
       </c>
     </row>
     <row r="10">
@@ -8554,7 +8554,7 @@
       <c r="C10" t="str">
         <v>002909</v>
       </c>
-      <c r="D10" s="112" t="str">
+      <c r="D10" s="107" t="str">
         <v>净卖: -879.53万</v>
       </c>
       <c r="E10">
@@ -8569,41 +8569,41 @@
       <c r="H10">
         <v>-1.91</v>
       </c>
-      <c r="I10" s="110">
+      <c r="I10" s="108">
         <v>-8.28</v>
       </c>
-      <c r="J10" s="113">
+      <c r="J10" s="111">
         <v>-16.44</v>
       </c>
-      <c r="K10" s="105">
+      <c r="K10" s="113">
         <v>-21.07</v>
       </c>
-      <c r="L10" s="106">
+      <c r="L10" s="114">
         <v>-21.8</v>
       </c>
-      <c r="M10" s="107">
+      <c r="M10" s="109">
         <v>-23.39</v>
       </c>
-      <c r="N10" s="111">
+      <c r="N10" s="112">
         <v>-23.02</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="115">
         <v>-22.66</v>
       </c>
-      <c r="P10" s="115">
+      <c r="P10" s="116">
         <v>-23.87</v>
       </c>
-      <c r="Q10" s="109">
+      <c r="Q10" s="117">
         <v>-23.26</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="105">
         <v>-24.12</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="110">
         <v>-23.87</v>
       </c>
-      <c r="T10" s="117">
-        <v>-21.44</v>
+      <c r="T10" s="106">
+        <v>-22.17</v>
       </c>
     </row>
     <row r="11">
@@ -8616,7 +8616,7 @@
       <c r="C11" t="str">
         <v>603639</v>
       </c>
-      <c r="D11" s="130" t="str">
+      <c r="D11" s="127" t="str">
         <v>净买: 1633.37万</v>
       </c>
       <c r="E11">
@@ -8631,41 +8631,41 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="126">
+      <c r="I11" s="128">
         <v>0</v>
       </c>
-      <c r="J11" s="121">
+      <c r="J11" s="129">
         <v>-6.63</v>
       </c>
-      <c r="K11" s="118">
+      <c r="K11" s="119">
         <v>-12.9</v>
       </c>
-      <c r="L11" s="127">
+      <c r="L11" s="130">
         <v>-12.16</v>
       </c>
-      <c r="M11" s="122">
+      <c r="M11" s="120">
         <v>-13.76</v>
       </c>
       <c r="N11" s="123">
         <v>-9.83</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="124">
         <v>-10.63</v>
       </c>
-      <c r="P11" s="119">
+      <c r="P11" s="121">
         <v>-9.46</v>
       </c>
-      <c r="Q11" s="124">
+      <c r="Q11" s="122">
         <v>-10.44</v>
       </c>
-      <c r="R11" s="128">
+      <c r="R11" s="125">
         <v>-10.01</v>
       </c>
-      <c r="S11" s="120">
+      <c r="S11" s="126">
         <v>-8.17</v>
       </c>
-      <c r="T11" s="125">
-        <v>-19.1</v>
+      <c r="T11" s="118">
+        <v>-15.23</v>
       </c>
     </row>
     <row r="12">
@@ -8678,7 +8678,7 @@
       <c r="C12" t="str">
         <v>002235</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="133" t="str">
         <v>净买: 1768.35万</v>
       </c>
       <c r="E12">
@@ -8693,41 +8693,41 @@
       <c r="H12">
         <v>10.05</v>
       </c>
-      <c r="I12" s="143">
+      <c r="I12" s="139">
         <v>0</v>
       </c>
-      <c r="J12" s="138">
+      <c r="J12" s="134">
         <v>3.19</v>
       </c>
-      <c r="K12" s="131">
+      <c r="K12" s="140">
         <v>6.23</v>
       </c>
-      <c r="L12" s="139">
+      <c r="L12" s="141">
         <v>16.81</v>
       </c>
-      <c r="M12" s="141">
+      <c r="M12" s="143">
         <v>18.99</v>
       </c>
-      <c r="N12" s="132">
+      <c r="N12" s="135">
         <v>30.87</v>
       </c>
-      <c r="O12" s="135">
+      <c r="O12" s="136">
         <v>43.91</v>
       </c>
-      <c r="P12" s="133">
+      <c r="P12" s="137">
         <v>42.17</v>
       </c>
-      <c r="Q12" s="134">
+      <c r="Q12" s="142">
         <v>36.52</v>
       </c>
-      <c r="R12" s="140">
+      <c r="R12" s="131">
         <v>43.48</v>
       </c>
-      <c r="S12" s="136">
+      <c r="S12" s="132">
         <v>44.93</v>
       </c>
-      <c r="T12" s="137">
-        <v>36.96</v>
+      <c r="T12" s="138">
+        <v>36.67</v>
       </c>
     </row>
     <row r="13">
@@ -8740,7 +8740,7 @@
       <c r="C13" t="str">
         <v>603776</v>
       </c>
-      <c r="D13" s="153" t="str">
+      <c r="D13" s="148" t="str">
         <v>净买: 1894.22万</v>
       </c>
       <c r="E13">
@@ -8755,41 +8755,41 @@
       <c r="H13">
         <v>10</v>
       </c>
-      <c r="I13" s="150">
+      <c r="I13" s="149">
         <v>0</v>
       </c>
       <c r="J13" s="154">
         <v>-9.72</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="150">
         <v>-10.95</v>
       </c>
-      <c r="L13" s="147">
+      <c r="L13" s="151">
         <v>-8.45</v>
       </c>
-      <c r="M13" s="148">
+      <c r="M13" s="152">
         <v>-7.04</v>
       </c>
-      <c r="N13" s="151">
+      <c r="N13" s="145">
         <v>-11.27</v>
       </c>
-      <c r="O13" s="155">
+      <c r="O13" s="146">
         <v>-2.41</v>
       </c>
-      <c r="P13" s="156">
+      <c r="P13" s="153">
         <v>2.36</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="147">
         <v>-2.64</v>
       </c>
-      <c r="R13" s="145">
+      <c r="R13" s="144">
         <v>-2.32</v>
       </c>
-      <c r="S13" s="152">
+      <c r="S13" s="155">
         <v>-2.23</v>
       </c>
-      <c r="T13" s="149">
-        <v>-7.45</v>
+      <c r="T13" s="156">
+        <v>-5.41</v>
       </c>
     </row>
     <row r="14">
@@ -8802,7 +8802,7 @@
       <c r="C14" t="str">
         <v>603776</v>
       </c>
-      <c r="D14" s="168" t="str">
+      <c r="D14" s="167" t="str">
         <v>净卖: -2197.25万</v>
       </c>
       <c r="E14">
@@ -8817,41 +8817,41 @@
       <c r="H14">
         <v>-2.32</v>
       </c>
-      <c r="I14" s="158">
+      <c r="I14" s="163">
         <v>-7.58</v>
       </c>
-      <c r="J14" s="169">
+      <c r="J14" s="166">
         <v>-8.84</v>
       </c>
-      <c r="K14" s="161">
+      <c r="K14" s="168">
         <v>-6.28</v>
       </c>
-      <c r="L14" s="162">
+      <c r="L14" s="169">
         <v>-4.84</v>
       </c>
-      <c r="M14" s="163">
+      <c r="M14" s="164">
         <v>-9.16</v>
       </c>
-      <c r="N14" s="159">
+      <c r="N14" s="165">
         <v>-0.09</v>
       </c>
-      <c r="O14" s="164">
+      <c r="O14" s="160">
         <v>4.79</v>
       </c>
-      <c r="P14" s="165">
+      <c r="P14" s="161">
         <v>-0.33</v>
       </c>
-      <c r="Q14" s="166">
+      <c r="Q14" s="157">
         <v>0</v>
       </c>
-      <c r="R14" s="157">
+      <c r="R14" s="158">
         <v>0.09</v>
       </c>
-      <c r="S14" s="167">
+      <c r="S14" s="162">
         <v>0</v>
       </c>
-      <c r="T14" s="160">
-        <v>-5.26</v>
+      <c r="T14" s="159">
+        <v>-3.16</v>
       </c>
     </row>
     <row r="15">
@@ -8864,7 +8864,7 @@
       <c r="C15" t="str">
         <v>001360</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="173" t="str">
         <v>净买: 1803.24万</v>
       </c>
       <c r="E15">
@@ -8879,41 +8879,41 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="172">
+      <c r="I15" s="174">
         <v>0</v>
       </c>
-      <c r="J15" s="176">
+      <c r="J15" s="180">
         <v>10.01</v>
       </c>
-      <c r="K15" s="177">
+      <c r="K15" s="175">
         <v>-0.95</v>
       </c>
-      <c r="L15" s="182">
+      <c r="L15" s="171">
         <v>-10.85</v>
       </c>
-      <c r="M15" s="170">
+      <c r="M15" s="176">
         <v>-13.18</v>
       </c>
-      <c r="N15" s="171">
+      <c r="N15" s="177">
         <v>-14.29</v>
       </c>
-      <c r="O15" s="173">
+      <c r="O15" s="172">
         <v>-15.25</v>
       </c>
-      <c r="P15" s="174">
+      <c r="P15" s="182">
         <v>-14.56</v>
       </c>
-      <c r="Q15" s="179">
+      <c r="Q15" s="181">
         <v>-16.52</v>
       </c>
-      <c r="R15" s="175">
+      <c r="R15" s="178">
         <v>-16.36</v>
       </c>
-      <c r="S15" s="178">
+      <c r="S15" s="179">
         <v>-16.15</v>
       </c>
-      <c r="T15" s="180">
-        <v>15.56</v>
+      <c r="T15" s="170">
+        <v>6.46</v>
       </c>
     </row>
     <row r="16">
@@ -8926,7 +8926,7 @@
       <c r="C16" t="str">
         <v>601669</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" s="183" t="str">
         <v>净买: 9396.35万</v>
       </c>
       <c r="E16">
@@ -8944,38 +8944,38 @@
       <c r="I16" s="190">
         <v>0</v>
       </c>
-      <c r="J16" s="194">
+      <c r="J16" s="191">
         <v>10.04</v>
       </c>
-      <c r="K16" s="192">
+      <c r="K16" s="184">
         <v>6.65</v>
       </c>
-      <c r="L16" s="195">
+      <c r="L16" s="185">
         <v>3.84</v>
       </c>
-      <c r="M16" s="186">
+      <c r="M16" s="187">
         <v>5.76</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="192">
         <v>0.44</v>
       </c>
-      <c r="O16" s="191">
+      <c r="O16" s="186">
         <v>0.89</v>
       </c>
-      <c r="P16" s="193">
+      <c r="P16" s="195">
         <v>-3.69</v>
       </c>
-      <c r="Q16" s="187">
+      <c r="Q16" s="193">
         <v>-4.58</v>
       </c>
       <c r="R16" s="188">
         <v>-5.17</v>
       </c>
-      <c r="S16" s="184">
+      <c r="S16" s="189">
         <v>-6.5</v>
       </c>
-      <c r="T16" s="189">
-        <v>-12.41</v>
+      <c r="T16" s="194">
+        <v>-14.62</v>
       </c>
     </row>
     <row r="17">
@@ -8988,7 +8988,7 @@
       <c r="C17" t="str">
         <v>001360</v>
       </c>
-      <c r="D17" s="196" t="str">
+      <c r="D17" s="199" t="str">
         <v>净卖: -1800.16万</v>
       </c>
       <c r="E17">
@@ -9003,41 +9003,41 @@
       <c r="H17">
         <v>0.1</v>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="207">
         <v>-10.05</v>
       </c>
-      <c r="J17" s="202">
+      <c r="J17" s="200">
         <v>-19.04</v>
       </c>
-      <c r="K17" s="203">
+      <c r="K17" s="201">
         <v>-21.15</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="208">
         <v>-22.16</v>
       </c>
-      <c r="M17" s="206">
+      <c r="M17" s="203">
         <v>-23.03</v>
       </c>
-      <c r="N17" s="207">
+      <c r="N17" s="196">
         <v>-22.4</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="205">
         <v>-24.18</v>
       </c>
-      <c r="P17" s="204">
+      <c r="P17" s="197">
         <v>-24.04</v>
       </c>
-      <c r="Q17" s="198">
+      <c r="Q17" s="206">
         <v>-23.85</v>
       </c>
-      <c r="R17" s="199">
+      <c r="R17" s="202">
         <v>-24.28</v>
       </c>
-      <c r="S17" s="205">
+      <c r="S17" s="204">
         <v>-24.47</v>
       </c>
-      <c r="T17" s="200">
-        <v>4.95</v>
+      <c r="T17" s="198">
+        <v>-3.32</v>
       </c>
     </row>
     <row r="18">
@@ -9050,7 +9050,7 @@
       <c r="C18" t="str">
         <v>001360</v>
       </c>
-      <c r="D18" s="213" t="str">
+      <c r="D18" s="211" t="str">
         <v>净卖: -1799.99万</v>
       </c>
       <c r="E18">
@@ -9065,41 +9065,41 @@
       <c r="H18">
         <v>-9.14</v>
       </c>
-      <c r="I18" s="218">
+      <c r="I18" s="217">
         <v>-0.94</v>
       </c>
-      <c r="J18" s="210">
+      <c r="J18" s="212">
         <v>-3.53</v>
       </c>
       <c r="K18" s="221">
         <v>-4.76</v>
       </c>
-      <c r="L18" s="214">
+      <c r="L18" s="210">
         <v>-5.82</v>
       </c>
-      <c r="M18" s="211">
+      <c r="M18" s="213">
         <v>-5.06</v>
       </c>
-      <c r="N18" s="215">
+      <c r="N18" s="214">
         <v>-7.24</v>
       </c>
-      <c r="O18" s="216">
+      <c r="O18" s="218">
         <v>-7.06</v>
       </c>
       <c r="P18" s="219">
         <v>-6.82</v>
       </c>
-      <c r="Q18" s="220">
+      <c r="Q18" s="215">
         <v>-7.35</v>
       </c>
-      <c r="R18" s="217">
+      <c r="R18" s="220">
         <v>-7.59</v>
       </c>
       <c r="S18" s="209">
         <v>-6.59</v>
       </c>
-      <c r="T18" s="212">
-        <v>28.41</v>
+      <c r="T18" s="216">
+        <v>18.29</v>
       </c>
     </row>
     <row r="19">
@@ -9112,7 +9112,7 @@
       <c r="C19" t="str">
         <v>300620</v>
       </c>
-      <c r="D19" s="231" t="str">
+      <c r="D19" s="233" t="str">
         <v>净买: 1215.21万</v>
       </c>
       <c r="E19">
@@ -9130,38 +9130,38 @@
       <c r="I19" s="223">
         <v>0</v>
       </c>
-      <c r="J19" s="232">
+      <c r="J19" s="229">
         <v>20.01</v>
       </c>
-      <c r="K19" s="233">
+      <c r="K19" s="224">
         <v>21.14</v>
       </c>
-      <c r="L19" s="225">
+      <c r="L19" s="230">
         <v>24.09</v>
       </c>
-      <c r="M19" s="226">
+      <c r="M19" s="234">
         <v>46.79</v>
       </c>
-      <c r="N19" s="227">
+      <c r="N19" s="226">
         <v>50.73</v>
       </c>
-      <c r="O19" s="224">
+      <c r="O19" s="227">
         <v>40.57</v>
       </c>
-      <c r="P19" s="228">
+      <c r="P19" s="225">
         <v>31.96</v>
       </c>
-      <c r="Q19" s="229">
+      <c r="Q19" s="228">
         <v>34.41</v>
       </c>
-      <c r="R19" s="234">
+      <c r="R19" s="231">
         <v>39.6</v>
       </c>
-      <c r="S19" s="230">
+      <c r="S19" s="232">
         <v>34.69</v>
       </c>
       <c r="T19" s="222">
-        <v>288.65</v>
+        <v>259.93</v>
       </c>
     </row>
     <row r="20">
@@ -9174,7 +9174,7 @@
       <c r="C20" t="str">
         <v>002177</v>
       </c>
-      <c r="D20" s="245" t="str">
+      <c r="D20" s="238" t="str">
         <v>净卖: -3762.63万</v>
       </c>
       <c r="E20">
@@ -9189,41 +9189,41 @@
       <c r="H20">
         <v>3.85</v>
       </c>
-      <c r="I20" s="241">
+      <c r="I20" s="243">
         <v>5.93</v>
       </c>
-      <c r="J20" s="242">
+      <c r="J20" s="244">
         <v>1.38</v>
       </c>
-      <c r="K20" s="238">
+      <c r="K20" s="245">
         <v>-1.17</v>
       </c>
-      <c r="L20" s="246">
+      <c r="L20" s="235">
         <v>-10.91</v>
       </c>
-      <c r="M20" s="243">
+      <c r="M20" s="236">
         <v>-11.76</v>
       </c>
-      <c r="N20" s="247">
+      <c r="N20" s="239">
         <v>-12.39</v>
       </c>
-      <c r="O20" s="235">
+      <c r="O20" s="237">
         <v>-9.96</v>
       </c>
-      <c r="P20" s="244">
+      <c r="P20" s="246">
         <v>-15.15</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="240">
         <v>-17.9</v>
       </c>
-      <c r="R20" s="236">
+      <c r="R20" s="247">
         <v>-19.39</v>
       </c>
-      <c r="S20" s="237">
+      <c r="S20" s="241">
         <v>-18.11</v>
       </c>
-      <c r="T20" s="240">
-        <v>-19.39</v>
+      <c r="T20" s="242">
+        <v>-20.44</v>
       </c>
     </row>
     <row r="21">
@@ -9236,7 +9236,7 @@
       <c r="C21" t="str">
         <v>301517</v>
       </c>
-      <c r="D21" s="250" t="str">
+      <c r="D21" s="251" t="str">
         <v>净买: 1391.15万</v>
       </c>
       <c r="E21">
@@ -9251,41 +9251,41 @@
       <c r="H21">
         <v>20</v>
       </c>
-      <c r="I21" s="256">
+      <c r="I21" s="252">
         <v>-14.18</v>
       </c>
-      <c r="J21" s="251">
+      <c r="J21" s="259">
         <v>-19.79</v>
       </c>
-      <c r="K21" s="259">
+      <c r="K21" s="249">
         <v>-18.67</v>
       </c>
-      <c r="L21" s="254">
+      <c r="L21" s="253">
         <v>-21.09</v>
       </c>
-      <c r="M21" s="255">
+      <c r="M21" s="254">
         <v>-22.21</v>
       </c>
-      <c r="N21" s="252">
+      <c r="N21" s="255">
         <v>-18.54</v>
       </c>
-      <c r="O21" s="257">
+      <c r="O21" s="260">
         <v>-22.58</v>
       </c>
-      <c r="P21" s="260">
+      <c r="P21" s="256">
         <v>-27.04</v>
       </c>
       <c r="Q21" s="248">
         <v>-25.09</v>
       </c>
-      <c r="R21" s="258">
+      <c r="R21" s="257">
         <v>-21.88</v>
       </c>
-      <c r="S21" s="253">
+      <c r="S21" s="250">
         <v>-25.85</v>
       </c>
-      <c r="T21" s="249">
-        <v>20.72</v>
+      <c r="T21" s="258">
+        <v>13.64</v>
       </c>
     </row>
     <row r="22">
@@ -9298,7 +9298,7 @@
       <c r="C22" t="str">
         <v>002547</v>
       </c>
-      <c r="D22" s="271" t="str">
+      <c r="D22" s="269" t="str">
         <v>净买: 4862.70万</v>
       </c>
       <c r="E22">
@@ -9316,38 +9316,38 @@
       <c r="I22" s="263">
         <v>0</v>
       </c>
-      <c r="J22" s="265">
+      <c r="J22" s="273">
         <v>7.01</v>
       </c>
-      <c r="K22" s="268">
+      <c r="K22" s="264">
         <v>0.36</v>
       </c>
-      <c r="L22" s="272">
+      <c r="L22" s="270">
         <v>4.68</v>
       </c>
-      <c r="M22" s="266">
+      <c r="M22" s="271">
         <v>15.11</v>
       </c>
-      <c r="N22" s="273">
+      <c r="N22" s="265">
         <v>21.76</v>
       </c>
-      <c r="O22" s="269">
+      <c r="O22" s="266">
         <v>22.66</v>
       </c>
-      <c r="P22" s="264">
+      <c r="P22" s="272">
         <v>17.81</v>
       </c>
-      <c r="Q22" s="267">
+      <c r="Q22" s="261">
         <v>9.17</v>
       </c>
-      <c r="R22" s="261">
+      <c r="R22" s="267">
         <v>12.59</v>
       </c>
       <c r="S22" s="262">
         <v>7.01</v>
       </c>
-      <c r="T22" s="270">
-        <v>-39.03</v>
+      <c r="T22" s="268">
+        <v>-44.78</v>
       </c>
     </row>
     <row r="23">
@@ -9360,7 +9360,7 @@
       <c r="C23" t="str">
         <v>002547</v>
       </c>
-      <c r="D23" s="285" t="str">
+      <c r="D23" s="282" t="str">
         <v>净卖: -5175.09万</v>
       </c>
       <c r="E23">
@@ -9375,41 +9375,41 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23" s="274">
+      <c r="I23" s="286">
         <v>7.01</v>
       </c>
-      <c r="J23" s="286">
+      <c r="J23" s="274">
         <v>0.36</v>
       </c>
-      <c r="K23" s="275">
+      <c r="K23" s="283">
         <v>4.68</v>
       </c>
-      <c r="L23" s="282">
+      <c r="L23" s="284">
         <v>15.11</v>
       </c>
-      <c r="M23" s="277">
+      <c r="M23" s="278">
         <v>21.76</v>
       </c>
-      <c r="N23" s="278">
+      <c r="N23" s="280">
         <v>22.66</v>
       </c>
-      <c r="O23" s="279">
+      <c r="O23" s="275">
         <v>17.81</v>
       </c>
       <c r="P23" s="276">
         <v>9.17</v>
       </c>
-      <c r="Q23" s="280">
+      <c r="Q23" s="277">
         <v>12.59</v>
       </c>
-      <c r="R23" s="283">
+      <c r="R23" s="281">
         <v>7.01</v>
       </c>
-      <c r="S23" s="284">
+      <c r="S23" s="285">
         <v>8.09</v>
       </c>
-      <c r="T23" s="281">
-        <v>-39.03</v>
+      <c r="T23" s="279">
+        <v>-44.78</v>
       </c>
     </row>
     <row r="24">
@@ -9422,7 +9422,7 @@
       <c r="C24" t="str">
         <v>920020</v>
       </c>
-      <c r="D24" s="291" t="str">
+      <c r="D24" s="290" t="str">
         <v>净卖: -668.61万</v>
       </c>
       <c r="E24">
@@ -9440,38 +9440,38 @@
       <c r="I24" s="296">
         <v>14.02</v>
       </c>
-      <c r="J24" s="297">
+      <c r="J24" s="293">
         <v>2.92</v>
       </c>
-      <c r="K24" s="298">
+      <c r="K24" s="291">
         <v>1.38</v>
       </c>
-      <c r="L24" s="293">
+      <c r="L24" s="294">
         <v>0.51</v>
       </c>
-      <c r="M24" s="294">
+      <c r="M24" s="297">
         <v>-0.82</v>
       </c>
-      <c r="N24" s="292">
+      <c r="N24" s="299">
         <v>-0.87</v>
       </c>
-      <c r="O24" s="289">
+      <c r="O24" s="287">
         <v>0.87</v>
       </c>
-      <c r="P24" s="299">
+      <c r="P24" s="298">
         <v>-2.4</v>
       </c>
-      <c r="Q24" s="290">
+      <c r="Q24" s="288">
         <v>-5.17</v>
       </c>
-      <c r="R24" s="295">
+      <c r="R24" s="289">
         <v>-4.76</v>
       </c>
-      <c r="S24" s="287">
+      <c r="S24" s="292">
         <v>-4.35</v>
       </c>
-      <c r="T24" s="288">
-        <v>-18.26</v>
+      <c r="T24" s="295">
+        <v>-19.54</v>
       </c>
     </row>
     <row r="25">
@@ -9484,7 +9484,7 @@
       <c r="C25" t="str">
         <v>605178</v>
       </c>
-      <c r="D25" s="305" t="str">
+      <c r="D25" s="301" t="str">
         <v>净买: 3874.18万</v>
       </c>
       <c r="E25">
@@ -9499,10 +9499,10 @@
       <c r="H25">
         <v>10</v>
       </c>
-      <c r="I25" s="301">
+      <c r="I25" s="302">
         <v>0</v>
       </c>
-      <c r="J25" s="302">
+      <c r="J25" s="307">
         <v>10</v>
       </c>
       <c r="K25" s="308">
@@ -9511,29 +9511,29 @@
       <c r="L25" s="311">
         <v>4.74</v>
       </c>
-      <c r="M25" s="312">
+      <c r="M25" s="306">
         <v>13.42</v>
       </c>
       <c r="N25" s="303">
         <v>19.72</v>
       </c>
-      <c r="O25" s="306">
+      <c r="O25" s="304">
         <v>26.01</v>
       </c>
-      <c r="P25" s="307">
+      <c r="P25" s="305">
         <v>16.89</v>
       </c>
       <c r="Q25" s="309">
         <v>6.52</v>
       </c>
-      <c r="R25" s="300">
+      <c r="R25" s="310">
         <v>10.9</v>
       </c>
-      <c r="S25" s="304">
+      <c r="S25" s="312">
         <v>12.81</v>
       </c>
-      <c r="T25" s="310">
-        <v>10.82</v>
+      <c r="T25" s="300">
+        <v>2.39</v>
       </c>
     </row>
     <row r="26">
@@ -9546,7 +9546,7 @@
       <c r="C26" t="str">
         <v>000407</v>
       </c>
-      <c r="D26" s="316" t="str">
+      <c r="D26" s="325" t="str">
         <v>净买: 788.81万</v>
       </c>
       <c r="E26">
@@ -9561,41 +9561,41 @@
       <c r="H26">
         <v>10.1</v>
       </c>
-      <c r="I26" s="317">
+      <c r="I26" s="315">
         <v>0</v>
       </c>
-      <c r="J26" s="324">
+      <c r="J26" s="313">
         <v>10.04</v>
       </c>
-      <c r="K26" s="318">
+      <c r="K26" s="320">
         <v>20.96</v>
       </c>
-      <c r="L26" s="319">
+      <c r="L26" s="314">
         <v>32.97</v>
       </c>
-      <c r="M26" s="325">
+      <c r="M26" s="316">
         <v>46.29</v>
       </c>
-      <c r="N26" s="320">
+      <c r="N26" s="317">
         <v>31.66</v>
       </c>
       <c r="O26" s="321">
         <v>30.35</v>
       </c>
-      <c r="P26" s="322">
+      <c r="P26" s="318">
         <v>17.25</v>
       </c>
-      <c r="Q26" s="313">
+      <c r="Q26" s="319">
         <v>5.46</v>
       </c>
-      <c r="R26" s="315">
+      <c r="R26" s="322">
         <v>5.9</v>
       </c>
-      <c r="S26" s="314">
+      <c r="S26" s="323">
         <v>12.45</v>
       </c>
-      <c r="T26" s="323">
-        <v>2.84</v>
+      <c r="T26" s="324">
+        <v>2.4</v>
       </c>
     </row>
     <row r="27">
@@ -9608,7 +9608,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="332" t="str">
+      <c r="D27" s="337" t="str">
         <v>净买: 3123.85万</v>
       </c>
       <c r="E27">
@@ -9623,41 +9623,41 @@
       <c r="H27">
         <v>9.96</v>
       </c>
-      <c r="I27" s="333">
+      <c r="I27" s="338">
         <v>0</v>
       </c>
-      <c r="J27" s="334">
+      <c r="J27" s="335">
         <v>-9.95</v>
       </c>
-      <c r="K27" s="328">
+      <c r="K27" s="326">
         <v>-19.01</v>
       </c>
-      <c r="L27" s="330">
+      <c r="L27" s="333">
         <v>-27.04</v>
       </c>
-      <c r="M27" s="335">
+      <c r="M27" s="327">
         <v>-30.61</v>
       </c>
-      <c r="N27" s="331">
+      <c r="N27" s="328">
         <v>-28.7</v>
       </c>
-      <c r="O27" s="336">
+      <c r="O27" s="329">
         <v>-31.89</v>
       </c>
-      <c r="P27" s="326">
+      <c r="P27" s="334">
         <v>-31.63</v>
       </c>
-      <c r="Q27" s="337">
+      <c r="Q27" s="331">
         <v>-28.95</v>
       </c>
-      <c r="R27" s="338">
+      <c r="R27" s="330">
         <v>-26.53</v>
       </c>
-      <c r="S27" s="329">
+      <c r="S27" s="336">
         <v>-24.49</v>
       </c>
-      <c r="T27" s="327">
-        <v>-24.23</v>
+      <c r="T27" s="332">
+        <v>-27.17</v>
       </c>
     </row>
     <row r="28">
@@ -9670,7 +9670,7 @@
       <c r="C28" t="str">
         <v>300094</v>
       </c>
-      <c r="D28" s="351" t="str">
+      <c r="D28" s="340" t="str">
         <v>净卖: -3846.51万</v>
       </c>
       <c r="E28">
@@ -9685,41 +9685,41 @@
       <c r="H28">
         <v>0.37</v>
       </c>
-      <c r="I28" s="345">
+      <c r="I28" s="341">
         <v>-11.85</v>
       </c>
-      <c r="J28" s="339">
+      <c r="J28" s="342">
         <v>-12.41</v>
       </c>
-      <c r="K28" s="340">
+      <c r="K28" s="347">
         <v>-8.33</v>
       </c>
-      <c r="L28" s="346">
+      <c r="L28" s="348">
         <v>-17.96</v>
       </c>
-      <c r="M28" s="342">
+      <c r="M28" s="351">
         <v>-23.89</v>
       </c>
-      <c r="N28" s="347">
+      <c r="N28" s="349">
         <v>-22.96</v>
       </c>
-      <c r="O28" s="348">
+      <c r="O28" s="343">
         <v>-24.26</v>
       </c>
-      <c r="P28" s="349">
+      <c r="P28" s="344">
         <v>-23.15</v>
       </c>
-      <c r="Q28" s="343">
+      <c r="Q28" s="345">
         <v>-21.48</v>
       </c>
-      <c r="R28" s="341">
+      <c r="R28" s="346">
         <v>-21.85</v>
       </c>
       <c r="S28" s="350">
         <v>-27.78</v>
       </c>
-      <c r="T28" s="344">
-        <v>-41.48</v>
+      <c r="T28" s="339">
+        <v>-44.44</v>
       </c>
     </row>
     <row r="29">
@@ -9732,7 +9732,7 @@
       <c r="C29" t="str">
         <v>002682</v>
       </c>
-      <c r="D29" s="355" t="str">
+      <c r="D29" s="360" t="str">
         <v>净卖: -2565.97万</v>
       </c>
       <c r="E29">
@@ -9747,41 +9747,41 @@
       <c r="H29">
         <v>-6.94</v>
       </c>
-      <c r="I29" s="358">
+      <c r="I29" s="353">
         <v>-3.35</v>
       </c>
-      <c r="J29" s="362">
+      <c r="J29" s="361">
         <v>-12.94</v>
       </c>
-      <c r="K29" s="363">
+      <c r="K29" s="358">
         <v>-17.2</v>
       </c>
-      <c r="L29" s="359">
+      <c r="L29" s="364">
         <v>-14.92</v>
       </c>
-      <c r="M29" s="360">
+      <c r="M29" s="354">
         <v>-18.72</v>
       </c>
-      <c r="N29" s="356">
+      <c r="N29" s="355">
         <v>-18.42</v>
       </c>
-      <c r="O29" s="364">
+      <c r="O29" s="352">
         <v>-15.22</v>
       </c>
-      <c r="P29" s="352">
+      <c r="P29" s="356">
         <v>-12.33</v>
       </c>
-      <c r="Q29" s="357">
+      <c r="Q29" s="362">
         <v>-9.89</v>
       </c>
-      <c r="R29" s="353">
+      <c r="R29" s="357">
         <v>-0.91</v>
       </c>
-      <c r="S29" s="361">
+      <c r="S29" s="363">
         <v>8.98</v>
       </c>
-      <c r="T29" s="354">
-        <v>-9.59</v>
+      <c r="T29" s="359">
+        <v>-13.09</v>
       </c>
     </row>
     <row r="30">
@@ -9794,7 +9794,7 @@
       <c r="C30" t="str">
         <v>603069</v>
       </c>
-      <c r="D30" s="369" t="str">
+      <c r="D30" s="366" t="str">
         <v>净买: 2184.48万</v>
       </c>
       <c r="E30">
@@ -9809,41 +9809,41 @@
       <c r="H30">
         <v>10.02</v>
       </c>
-      <c r="I30" s="375">
+      <c r="I30" s="372">
         <v>0</v>
       </c>
-      <c r="J30" s="370">
+      <c r="J30" s="367">
         <v>1.25</v>
       </c>
-      <c r="K30" s="376">
+      <c r="K30" s="375">
         <v>-4.36</v>
       </c>
-      <c r="L30" s="371">
+      <c r="L30" s="365">
         <v>5.19</v>
       </c>
-      <c r="M30" s="366">
+      <c r="M30" s="368">
         <v>-1.42</v>
       </c>
-      <c r="N30" s="377">
+      <c r="N30" s="376">
         <v>-5.96</v>
       </c>
-      <c r="O30" s="372">
+      <c r="O30" s="369">
         <v>-5.99</v>
       </c>
-      <c r="P30" s="373">
+      <c r="P30" s="370">
         <v>-13.57</v>
       </c>
-      <c r="Q30" s="365">
+      <c r="Q30" s="377">
         <v>-13.64</v>
       </c>
-      <c r="R30" s="367">
+      <c r="R30" s="373">
         <v>-14.16</v>
       </c>
-      <c r="S30" s="368">
+      <c r="S30" s="374">
         <v>-15.27</v>
       </c>
-      <c r="T30" s="374">
-        <v>-40.13</v>
+      <c r="T30" s="371">
+        <v>-42.11</v>
       </c>
     </row>
     <row r="31">
@@ -9856,7 +9856,7 @@
       <c r="C31" t="str">
         <v>002009</v>
       </c>
-      <c r="D31" s="385" t="str">
+      <c r="D31" s="388" t="str">
         <v>净买: 3463.54万</v>
       </c>
       <c r="E31">
@@ -9871,41 +9871,41 @@
       <c r="H31">
         <v>10</v>
       </c>
-      <c r="I31" s="382">
+      <c r="I31" s="385">
         <v>0</v>
       </c>
-      <c r="J31" s="383">
+      <c r="J31" s="382">
         <v>10.02</v>
       </c>
-      <c r="K31" s="379">
+      <c r="K31" s="386">
         <v>21.02</v>
       </c>
-      <c r="L31" s="386">
+      <c r="L31" s="389">
         <v>16.84</v>
       </c>
-      <c r="M31" s="388">
+      <c r="M31" s="383">
         <v>14.72</v>
       </c>
-      <c r="N31" s="384">
+      <c r="N31" s="390">
         <v>8.01</v>
       </c>
-      <c r="O31" s="389">
+      <c r="O31" s="380">
         <v>12.24</v>
       </c>
-      <c r="P31" s="380">
+      <c r="P31" s="387">
         <v>12.65</v>
       </c>
-      <c r="Q31" s="381">
+      <c r="Q31" s="378">
         <v>15.19</v>
       </c>
-      <c r="R31" s="390">
+      <c r="R31" s="379">
         <v>18.85</v>
       </c>
-      <c r="S31" s="387">
+      <c r="S31" s="381">
         <v>11.93</v>
       </c>
-      <c r="T31" s="378">
-        <v>29.65</v>
+      <c r="T31" s="384">
+        <v>22.99</v>
       </c>
     </row>
     <row r="32">
@@ -9918,7 +9918,7 @@
       <c r="C32" t="str">
         <v>002009</v>
       </c>
-      <c r="D32" s="394" t="str">
+      <c r="D32" s="396" t="str">
         <v>净卖: -4207.08万</v>
       </c>
       <c r="E32">
@@ -9936,38 +9936,38 @@
       <c r="I32" s="397">
         <v>0.09</v>
       </c>
-      <c r="J32" s="401">
+      <c r="J32" s="398">
         <v>10.1</v>
       </c>
       <c r="K32" s="391">
         <v>6.3</v>
       </c>
-      <c r="L32" s="398">
+      <c r="L32" s="399">
         <v>4.37</v>
       </c>
-      <c r="M32" s="392">
+      <c r="M32" s="400">
         <v>-1.74</v>
       </c>
-      <c r="N32" s="402">
+      <c r="N32" s="401">
         <v>2.11</v>
       </c>
-      <c r="O32" s="393">
+      <c r="O32" s="392">
         <v>2.49</v>
       </c>
-      <c r="P32" s="395">
+      <c r="P32" s="393">
         <v>4.79</v>
       </c>
-      <c r="Q32" s="399">
+      <c r="Q32" s="395">
         <v>8.13</v>
       </c>
-      <c r="R32" s="396">
+      <c r="R32" s="402">
         <v>1.83</v>
       </c>
       <c r="S32" s="403">
         <v>2.63</v>
       </c>
-      <c r="T32" s="400">
-        <v>17.95</v>
+      <c r="T32" s="394">
+        <v>11.89</v>
       </c>
     </row>
     <row r="33">
@@ -9980,7 +9980,7 @@
       <c r="C33" t="str">
         <v>002009</v>
       </c>
-      <c r="D33" s="407" t="str">
+      <c r="D33" s="409" t="str">
         <v>净卖: -4209.56万</v>
       </c>
       <c r="E33">
@@ -9995,41 +9995,41 @@
       <c r="H33">
         <v>2.21</v>
       </c>
-      <c r="I33" s="408">
+      <c r="I33" s="410">
         <v>7.63</v>
       </c>
-      <c r="J33" s="409">
+      <c r="J33" s="411">
         <v>3.9</v>
       </c>
-      <c r="K33" s="415">
+      <c r="K33" s="412">
         <v>2.02</v>
       </c>
-      <c r="L33" s="410">
+      <c r="L33" s="416">
         <v>-3.95</v>
       </c>
-      <c r="M33" s="412">
+      <c r="M33" s="404">
         <v>-0.18</v>
       </c>
-      <c r="N33" s="406">
+      <c r="N33" s="413">
         <v>0.18</v>
       </c>
-      <c r="O33" s="413">
+      <c r="O33" s="414">
         <v>2.43</v>
       </c>
-      <c r="P33" s="416">
+      <c r="P33" s="408">
         <v>5.7</v>
       </c>
-      <c r="Q33" s="414">
+      <c r="Q33" s="415">
         <v>-0.46</v>
       </c>
-      <c r="R33" s="404">
+      <c r="R33" s="405">
         <v>0.32</v>
       </c>
-      <c r="S33" s="411">
+      <c r="S33" s="406">
         <v>-1.52</v>
       </c>
-      <c r="T33" s="405">
-        <v>15.3</v>
+      <c r="T33" s="407">
+        <v>9.37</v>
       </c>
     </row>
     <row r="34">
@@ -10042,7 +10042,7 @@
       <c r="C34" t="str">
         <v>002969</v>
       </c>
-      <c r="D34" s="417" t="str">
+      <c r="D34" s="424" t="str">
         <v>净卖: -2752.13万</v>
       </c>
       <c r="E34">
@@ -10057,41 +10057,41 @@
       <c r="H34">
         <v>0.55</v>
       </c>
-      <c r="I34" s="428">
+      <c r="I34" s="421">
         <v>7.62</v>
       </c>
-      <c r="J34" s="418">
+      <c r="J34" s="417">
         <v>18.38</v>
       </c>
-      <c r="K34" s="429">
+      <c r="K34" s="418">
         <v>30.24</v>
       </c>
-      <c r="L34" s="419">
+      <c r="L34" s="425">
         <v>37.86</v>
       </c>
-      <c r="M34" s="423">
+      <c r="M34" s="426">
         <v>51.69</v>
       </c>
-      <c r="N34" s="426">
+      <c r="N34" s="427">
         <v>36.53</v>
       </c>
-      <c r="O34" s="420">
+      <c r="O34" s="422">
         <v>22.86</v>
       </c>
-      <c r="P34" s="421">
+      <c r="P34" s="428">
         <v>35.11</v>
       </c>
-      <c r="Q34" s="424">
+      <c r="Q34" s="423">
         <v>48.63</v>
       </c>
-      <c r="R34" s="422">
+      <c r="R34" s="429">
         <v>52.47</v>
       </c>
-      <c r="S34" s="425">
+      <c r="S34" s="419">
         <v>67.71</v>
       </c>
-      <c r="T34" s="427">
-        <v>71.17</v>
+      <c r="T34" s="420">
+        <v>69.76</v>
       </c>
     </row>
     <row r="35">
@@ -10104,7 +10104,7 @@
       <c r="C35" t="str">
         <v>600683</v>
       </c>
-      <c r="D35" s="438" t="str">
+      <c r="D35" s="439" t="str">
         <v>净买: 819.30万</v>
       </c>
       <c r="E35">
@@ -10119,13 +10119,13 @@
       <c r="H35">
         <v>10.1</v>
       </c>
-      <c r="I35" s="432">
+      <c r="I35" s="436">
         <v>0</v>
       </c>
-      <c r="J35" s="442">
+      <c r="J35" s="431">
         <v>10.09</v>
       </c>
-      <c r="K35" s="439">
+      <c r="K35" s="432">
         <v>21.1</v>
       </c>
       <c r="L35" s="440">
@@ -10134,26 +10134,26 @@
       <c r="M35" s="433">
         <v>22.2</v>
       </c>
-      <c r="N35" s="437">
+      <c r="N35" s="434">
         <v>22.57</v>
       </c>
-      <c r="O35" s="430">
+      <c r="O35" s="441">
         <v>32.29</v>
       </c>
-      <c r="P35" s="431">
+      <c r="P35" s="437">
         <v>27.16</v>
       </c>
-      <c r="Q35" s="441">
+      <c r="Q35" s="442">
         <v>23.12</v>
       </c>
-      <c r="R35" s="434">
+      <c r="R35" s="435">
         <v>30.46</v>
       </c>
-      <c r="S35" s="435">
+      <c r="S35" s="430">
         <v>37.06</v>
       </c>
-      <c r="T35" s="436">
-        <v>119.27</v>
+      <c r="T35" s="438">
+        <v>151.56</v>
       </c>
     </row>
     <row r="36">
@@ -10166,7 +10166,7 @@
       <c r="C36" t="str">
         <v>002056</v>
       </c>
-      <c r="D36" s="450" t="str">
+      <c r="D36" s="449" t="str">
         <v>净卖: -2838.92万</v>
       </c>
       <c r="E36">
@@ -10181,41 +10181,41 @@
       <c r="H36">
         <v>1.28</v>
       </c>
-      <c r="I36" s="451">
+      <c r="I36" s="443">
         <v>8.62</v>
       </c>
-      <c r="J36" s="444">
+      <c r="J36" s="450">
         <v>-0.42</v>
       </c>
-      <c r="K36" s="445">
+      <c r="K36" s="444">
         <v>-4.25</v>
       </c>
-      <c r="L36" s="455">
+      <c r="L36" s="445">
         <v>-5.84</v>
       </c>
-      <c r="M36" s="452">
+      <c r="M36" s="453">
         <v>-8.66</v>
       </c>
       <c r="N36" s="446">
         <v>-6.43</v>
       </c>
-      <c r="O36" s="447">
+      <c r="O36" s="451">
         <v>-9.21</v>
       </c>
-      <c r="P36" s="443">
+      <c r="P36" s="454">
         <v>-9.21</v>
       </c>
-      <c r="Q36" s="453">
+      <c r="Q36" s="448">
         <v>-7.78</v>
       </c>
-      <c r="R36" s="448">
+      <c r="R36" s="447">
         <v>-9.46</v>
       </c>
-      <c r="S36" s="449">
+      <c r="S36" s="452">
         <v>-9.92</v>
       </c>
-      <c r="T36" s="454">
-        <v>-16.35</v>
+      <c r="T36" s="455">
+        <v>-20.09</v>
       </c>
     </row>
     <row r="37">
@@ -10277,41 +10277,41 @@
       <c r="F38" t="str"/>
       <c r="G38" t="str"/>
       <c r="H38" t="str"/>
-      <c r="I38" s="463">
+      <c r="I38" s="467">
         <v>31.43</v>
       </c>
-      <c r="J38" s="460">
+      <c r="J38" s="462">
         <v>62.86</v>
       </c>
-      <c r="K38" s="464">
+      <c r="K38" s="459">
         <v>54.29</v>
       </c>
-      <c r="L38" s="457">
+      <c r="L38" s="456">
         <v>54.29</v>
       </c>
-      <c r="M38" s="465">
+      <c r="M38" s="464">
         <v>42.86</v>
       </c>
-      <c r="N38" s="458">
+      <c r="N38" s="465">
         <v>42.86</v>
       </c>
-      <c r="O38" s="459">
+      <c r="O38" s="463">
         <v>48.57</v>
       </c>
-      <c r="P38" s="466">
+      <c r="P38" s="457">
         <v>37.14</v>
       </c>
-      <c r="Q38" s="461">
+      <c r="Q38" s="466">
         <v>31.43</v>
       </c>
-      <c r="R38" s="462">
+      <c r="R38" s="460">
         <v>34.29</v>
       </c>
-      <c r="S38" s="467">
+      <c r="S38" s="461">
         <v>31.43</v>
       </c>
-      <c r="T38" s="456">
-        <v>48.57</v>
+      <c r="T38" s="458">
+        <v>45.71</v>
       </c>
     </row>
     <row r="39">
@@ -10325,41 +10325,41 @@
       <c r="F39" t="str"/>
       <c r="G39" t="str"/>
       <c r="H39" t="str"/>
-      <c r="I39" s="470">
+      <c r="I39" s="476">
         <v>0.72</v>
       </c>
-      <c r="J39" s="471">
+      <c r="J39" s="468">
         <v>1.7</v>
       </c>
-      <c r="K39" s="474">
+      <c r="K39" s="473">
         <v>1.83</v>
       </c>
-      <c r="L39" s="475">
+      <c r="L39" s="477">
         <v>1.8</v>
       </c>
-      <c r="M39" s="477">
+      <c r="M39" s="470">
         <v>1.64</v>
       </c>
-      <c r="N39" s="472">
+      <c r="N39" s="474">
         <v>0.36</v>
       </c>
-      <c r="O39" s="478">
+      <c r="O39" s="469">
         <v>0.46</v>
       </c>
-      <c r="P39" s="468">
+      <c r="P39" s="471">
         <v>-2.04</v>
       </c>
-      <c r="Q39" s="479">
+      <c r="Q39" s="478">
         <v>-3.24</v>
       </c>
-      <c r="R39" s="473">
+      <c r="R39" s="479">
         <v>-2.68</v>
       </c>
-      <c r="S39" s="476">
+      <c r="S39" s="475">
         <v>-2.27</v>
       </c>
-      <c r="T39" s="469">
-        <v>10.96</v>
+      <c r="T39" s="472">
+        <v>8.33</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/正经哥/index.xlsx
+++ b/youzi/正经哥/index.xlsx
@@ -39,37 +39,889 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF36AC51"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A8"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,79 +933,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF36AC51"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,13 +981,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,6 +1059,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA91E2B"/>
         <bgColor/>
       </patternFill>
@@ -219,6 +1131,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -249,6 +1287,882 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -261,37 +2175,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,19 +2271,211 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBF8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -333,13 +2487,193 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,13 +2685,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -369,2341 +2739,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7FBF8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB52331"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF48B460"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2715,55 +2817,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1B7431"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2775,67 +2829,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEFA8AF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE0F2E4"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4654"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2847,67 +2901,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D4"/>
+        <fgColor rgb="FFDF4957"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4654"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8058,7 +8058,7 @@
       <c r="C2" t="str">
         <v>000665</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -2301.68万</v>
       </c>
       <c r="E2">
@@ -8073,41 +8073,41 @@
       <c r="H2">
         <v>10.06</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="4">
         <v>0</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="7">
         <v>10</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="9">
         <v>21.03</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="12">
         <v>30</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="13">
         <v>18.79</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="10">
         <v>10</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="5">
         <v>11.72</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="8">
         <v>10.17</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="1">
         <v>2.07</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="2">
         <v>-4.66</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="3">
         <v>-8.45</v>
       </c>
-      <c r="T2" s="5">
-        <v>-20</v>
+      <c r="T2" s="6">
+        <v>-18.97</v>
       </c>
     </row>
     <row r="3">
@@ -8120,7 +8120,7 @@
       <c r="C3" t="str">
         <v>002300</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="18" t="str">
         <v>净买: 2299.17万</v>
       </c>
       <c r="E3">
@@ -8135,41 +8135,41 @@
       <c r="H3">
         <v>9.95</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="19">
         <v>0</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="25">
         <v>10.06</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="26">
         <v>21.12</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="20">
         <v>9.77</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="14">
         <v>-1.15</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="15">
         <v>-8.76</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="21">
         <v>-11.35</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="22">
         <v>-12.36</v>
       </c>
       <c r="Q3" s="23">
         <v>-13.22</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="16">
         <v>-21.84</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="17">
         <v>-23.99</v>
       </c>
-      <c r="T3" s="20">
-        <v>48.28</v>
+      <c r="T3" s="24">
+        <v>47.99</v>
       </c>
     </row>
     <row r="4">
@@ -8182,7 +8182,7 @@
       <c r="C4" t="str">
         <v>002300</v>
       </c>
-      <c r="D4" s="34" t="str">
+      <c r="D4" s="35" t="str">
         <v>净卖: -2576.68万</v>
       </c>
       <c r="E4">
@@ -8197,10 +8197,10 @@
       <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="31">
         <v>9.34</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="36">
         <v>-0.91</v>
       </c>
       <c r="K4" s="32">
@@ -8209,29 +8209,29 @@
       <c r="L4" s="27">
         <v>-17.64</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="33">
         <v>-19.97</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="28">
         <v>-20.88</v>
       </c>
       <c r="O4" s="29">
         <v>-21.66</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="37">
         <v>-29.44</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="34">
         <v>-31.39</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="38">
         <v>-28.92</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="30">
         <v>-27.63</v>
       </c>
-      <c r="T4" s="38">
-        <v>33.85</v>
+      <c r="T4" s="39">
+        <v>33.59</v>
       </c>
     </row>
     <row r="5">
@@ -8244,7 +8244,7 @@
       <c r="C5" t="str">
         <v>002688</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="47" t="str">
         <v>净买: 5775.20万</v>
       </c>
       <c r="E5">
@@ -8259,41 +8259,41 @@
       <c r="H5">
         <v>9.93</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="48">
         <v>0</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="52">
         <v>9.95</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="41">
         <v>20.98</v>
       </c>
       <c r="L5" s="40">
         <v>30.17</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="49">
         <v>17.15</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="50">
         <v>8.58</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="43">
         <v>10.57</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="51">
         <v>-0.46</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="44">
         <v>-5.36</v>
       </c>
       <c r="R5" s="42">
         <v>-5.05</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="45">
         <v>-4.29</v>
       </c>
-      <c r="T5" s="44">
-        <v>-11.03</v>
+      <c r="T5" s="46">
+        <v>-10.87</v>
       </c>
     </row>
     <row r="6">
@@ -8306,7 +8306,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="56" t="str">
         <v>净卖: -7396.08万</v>
       </c>
       <c r="E6">
@@ -8321,41 +8321,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="61">
         <v>7.59</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="57">
         <v>-3.16</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="64">
         <v>-10.25</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="62">
         <v>-8.61</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="65">
         <v>-17.72</v>
       </c>
-      <c r="N6" s="62">
+      <c r="N6" s="63">
         <v>-21.77</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="59">
         <v>-21.52</v>
       </c>
-      <c r="P6" s="64">
+      <c r="P6" s="58">
         <v>-20.89</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="60">
         <v>-16.71</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="53">
         <v>-20.76</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="54">
         <v>-17.09</v>
       </c>
-      <c r="T6" s="61">
-        <v>-26.46</v>
+      <c r="T6" s="55">
+        <v>-26.33</v>
       </c>
     </row>
     <row r="7">
@@ -8368,7 +8368,7 @@
       <c r="C7" t="str">
         <v>600697</v>
       </c>
-      <c r="D7" s="69" t="str">
+      <c r="D7" s="77" t="str">
         <v>净卖: -2819.93万</v>
       </c>
       <c r="E7">
@@ -8383,41 +8383,41 @@
       <c r="H7">
         <v>-9.28</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="72">
         <v>3.2</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="73">
         <v>6.95</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="78">
         <v>17.66</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="67">
         <v>13.12</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="74">
         <v>1.95</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="68">
         <v>0</v>
       </c>
-      <c r="O7" s="73">
+      <c r="O7" s="69">
         <v>4.3</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="70">
         <v>-1.72</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="75">
         <v>-5.31</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="66">
         <v>-5.23</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="71">
         <v>-7.97</v>
       </c>
-      <c r="T7" s="77">
-        <v>-8.44</v>
+      <c r="T7" s="76">
+        <v>-5.78</v>
       </c>
     </row>
     <row r="8">
@@ -8430,7 +8430,7 @@
       <c r="C8" t="str">
         <v>600828</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="91" t="str">
         <v>净买: 1425.83万</v>
       </c>
       <c r="E8">
@@ -8445,41 +8445,41 @@
       <c r="H8">
         <v>10.11</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="82">
         <v>0</v>
       </c>
-      <c r="J8" s="80">
+      <c r="J8" s="87">
         <v>10.02</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="83">
         <v>7.31</v>
       </c>
       <c r="L8" s="88">
         <v>5.01</v>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="84">
         <v>10.65</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8" s="85">
         <v>5.43</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="79">
         <v>-5.01</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="86">
         <v>-10.02</v>
       </c>
-      <c r="Q8" s="85">
+      <c r="Q8" s="80">
         <v>-12.73</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="81">
         <v>-11.69</v>
       </c>
-      <c r="S8" s="90">
+      <c r="S8" s="89">
         <v>-10.65</v>
       </c>
-      <c r="T8" s="91">
-        <v>5.01</v>
+      <c r="T8" s="90">
+        <v>7.52</v>
       </c>
     </row>
     <row r="9">
@@ -8492,7 +8492,7 @@
       <c r="C9" t="str">
         <v>600828</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="103" t="str">
         <v>净卖: -1514.63万</v>
       </c>
       <c r="E9">
@@ -8507,41 +8507,41 @@
       <c r="H9">
         <v>-0.21</v>
       </c>
-      <c r="I9" s="97">
+      <c r="I9" s="104">
         <v>10.25</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="92">
         <v>7.53</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="98">
         <v>5.23</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="100">
         <v>10.88</v>
       </c>
-      <c r="M9" s="92">
+      <c r="M9" s="93">
         <v>5.65</v>
       </c>
       <c r="N9" s="94">
         <v>-4.81</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="99">
         <v>-9.83</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="95">
         <v>-12.55</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="96">
         <v>-11.51</v>
       </c>
-      <c r="R9" s="96">
+      <c r="R9" s="101">
         <v>-10.46</v>
       </c>
-      <c r="S9" s="93">
+      <c r="S9" s="102">
         <v>-12.34</v>
       </c>
-      <c r="T9" s="100">
-        <v>5.23</v>
+      <c r="T9" s="97">
+        <v>7.74</v>
       </c>
     </row>
     <row r="10">
@@ -8554,7 +8554,7 @@
       <c r="C10" t="str">
         <v>002909</v>
       </c>
-      <c r="D10" s="107" t="str">
+      <c r="D10" s="111" t="str">
         <v>净卖: -879.53万</v>
       </c>
       <c r="E10">
@@ -8569,41 +8569,41 @@
       <c r="H10">
         <v>-1.91</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="105">
         <v>-8.28</v>
       </c>
-      <c r="J10" s="111">
+      <c r="J10" s="109">
         <v>-16.44</v>
       </c>
-      <c r="K10" s="113">
+      <c r="K10" s="112">
         <v>-21.07</v>
       </c>
-      <c r="L10" s="114">
+      <c r="L10" s="110">
         <v>-21.8</v>
       </c>
-      <c r="M10" s="109">
+      <c r="M10" s="106">
         <v>-23.39</v>
       </c>
-      <c r="N10" s="112">
+      <c r="N10" s="116">
         <v>-23.02</v>
       </c>
-      <c r="O10" s="115">
+      <c r="O10" s="113">
         <v>-22.66</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="114">
         <v>-23.87</v>
       </c>
       <c r="Q10" s="117">
         <v>-23.26</v>
       </c>
-      <c r="R10" s="105">
+      <c r="R10" s="107">
         <v>-24.12</v>
       </c>
-      <c r="S10" s="110">
+      <c r="S10" s="115">
         <v>-23.87</v>
       </c>
-      <c r="T10" s="106">
-        <v>-22.17</v>
+      <c r="T10" s="108">
+        <v>-20.34</v>
       </c>
     </row>
     <row r="11">
@@ -8616,7 +8616,7 @@
       <c r="C11" t="str">
         <v>603639</v>
       </c>
-      <c r="D11" s="127" t="str">
+      <c r="D11" s="129" t="str">
         <v>净买: 1633.37万</v>
       </c>
       <c r="E11">
@@ -8631,41 +8631,41 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="128">
+      <c r="I11" s="127">
         <v>0</v>
       </c>
-      <c r="J11" s="129">
+      <c r="J11" s="118">
         <v>-6.63</v>
       </c>
       <c r="K11" s="119">
         <v>-12.9</v>
       </c>
-      <c r="L11" s="130">
+      <c r="L11" s="123">
         <v>-12.16</v>
       </c>
-      <c r="M11" s="120">
+      <c r="M11" s="124">
         <v>-13.76</v>
       </c>
-      <c r="N11" s="123">
+      <c r="N11" s="120">
         <v>-9.83</v>
       </c>
-      <c r="O11" s="124">
+      <c r="O11" s="121">
         <v>-10.63</v>
       </c>
-      <c r="P11" s="121">
+      <c r="P11" s="125">
         <v>-9.46</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="130">
         <v>-10.44</v>
       </c>
-      <c r="R11" s="125">
+      <c r="R11" s="122">
         <v>-10.01</v>
       </c>
       <c r="S11" s="126">
         <v>-8.17</v>
       </c>
-      <c r="T11" s="118">
-        <v>-15.23</v>
+      <c r="T11" s="128">
+        <v>-15.48</v>
       </c>
     </row>
     <row r="12">
@@ -8678,7 +8678,7 @@
       <c r="C12" t="str">
         <v>002235</v>
       </c>
-      <c r="D12" s="133" t="str">
+      <c r="D12" s="140" t="str">
         <v>净买: 1768.35万</v>
       </c>
       <c r="E12">
@@ -8693,41 +8693,41 @@
       <c r="H12">
         <v>10.05</v>
       </c>
-      <c r="I12" s="139">
+      <c r="I12" s="137">
         <v>0</v>
       </c>
-      <c r="J12" s="134">
+      <c r="J12" s="135">
         <v>3.19</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="141">
         <v>6.23</v>
       </c>
-      <c r="L12" s="141">
+      <c r="L12" s="138">
         <v>16.81</v>
       </c>
-      <c r="M12" s="143">
+      <c r="M12" s="142">
         <v>18.99</v>
       </c>
-      <c r="N12" s="135">
+      <c r="N12" s="131">
         <v>30.87</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="143">
         <v>43.91</v>
       </c>
-      <c r="P12" s="137">
+      <c r="P12" s="132">
         <v>42.17</v>
       </c>
-      <c r="Q12" s="142">
+      <c r="Q12" s="133">
         <v>36.52</v>
       </c>
-      <c r="R12" s="131">
+      <c r="R12" s="134">
         <v>43.48</v>
       </c>
-      <c r="S12" s="132">
+      <c r="S12" s="136">
         <v>44.93</v>
       </c>
-      <c r="T12" s="138">
-        <v>36.67</v>
+      <c r="T12" s="139">
+        <v>41.59</v>
       </c>
     </row>
     <row r="13">
@@ -8740,7 +8740,7 @@
       <c r="C13" t="str">
         <v>603776</v>
       </c>
-      <c r="D13" s="148" t="str">
+      <c r="D13" s="155" t="str">
         <v>净买: 1894.22万</v>
       </c>
       <c r="E13">
@@ -8755,41 +8755,41 @@
       <c r="H13">
         <v>10</v>
       </c>
-      <c r="I13" s="149">
+      <c r="I13" s="146">
         <v>0</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="156">
         <v>-9.72</v>
       </c>
-      <c r="K13" s="150">
+      <c r="K13" s="147">
         <v>-10.95</v>
       </c>
-      <c r="L13" s="151">
+      <c r="L13" s="149">
         <v>-8.45</v>
       </c>
-      <c r="M13" s="152">
+      <c r="M13" s="150">
         <v>-7.04</v>
       </c>
-      <c r="N13" s="145">
+      <c r="N13" s="154">
         <v>-11.27</v>
       </c>
-      <c r="O13" s="146">
+      <c r="O13" s="151">
         <v>-2.41</v>
       </c>
-      <c r="P13" s="153">
+      <c r="P13" s="152">
         <v>2.36</v>
       </c>
-      <c r="Q13" s="147">
+      <c r="Q13" s="144">
         <v>-2.64</v>
       </c>
-      <c r="R13" s="144">
+      <c r="R13" s="148">
         <v>-2.32</v>
       </c>
-      <c r="S13" s="155">
+      <c r="S13" s="153">
         <v>-2.23</v>
       </c>
-      <c r="T13" s="156">
-        <v>-5.41</v>
+      <c r="T13" s="145">
+        <v>-6.18</v>
       </c>
     </row>
     <row r="14">
@@ -8802,7 +8802,7 @@
       <c r="C14" t="str">
         <v>603776</v>
       </c>
-      <c r="D14" s="167" t="str">
+      <c r="D14" s="159" t="str">
         <v>净卖: -2197.25万</v>
       </c>
       <c r="E14">
@@ -8817,25 +8817,25 @@
       <c r="H14">
         <v>-2.32</v>
       </c>
-      <c r="I14" s="163">
+      <c r="I14" s="168">
         <v>-7.58</v>
       </c>
-      <c r="J14" s="166">
+      <c r="J14" s="165">
         <v>-8.84</v>
       </c>
-      <c r="K14" s="168">
+      <c r="K14" s="166">
         <v>-6.28</v>
       </c>
-      <c r="L14" s="169">
+      <c r="L14" s="160">
         <v>-4.84</v>
       </c>
-      <c r="M14" s="164">
+      <c r="M14" s="169">
         <v>-9.16</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="162">
         <v>-0.09</v>
       </c>
-      <c r="O14" s="160">
+      <c r="O14" s="163">
         <v>4.79</v>
       </c>
       <c r="P14" s="161">
@@ -8847,11 +8847,11 @@
       <c r="R14" s="158">
         <v>0.09</v>
       </c>
-      <c r="S14" s="162">
+      <c r="S14" s="167">
         <v>0</v>
       </c>
-      <c r="T14" s="159">
-        <v>-3.16</v>
+      <c r="T14" s="164">
+        <v>-3.95</v>
       </c>
     </row>
     <row r="15">
@@ -8864,7 +8864,7 @@
       <c r="C15" t="str">
         <v>001360</v>
       </c>
-      <c r="D15" s="173" t="str">
+      <c r="D15" s="170" t="str">
         <v>净买: 1803.24万</v>
       </c>
       <c r="E15">
@@ -8879,41 +8879,41 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="174">
+      <c r="I15" s="171">
         <v>0</v>
       </c>
-      <c r="J15" s="180">
+      <c r="J15" s="173">
         <v>10.01</v>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="174">
         <v>-0.95</v>
       </c>
-      <c r="L15" s="171">
+      <c r="L15" s="178">
         <v>-10.85</v>
       </c>
-      <c r="M15" s="176">
+      <c r="M15" s="179">
         <v>-13.18</v>
       </c>
-      <c r="N15" s="177">
+      <c r="N15" s="180">
         <v>-14.29</v>
       </c>
       <c r="O15" s="172">
         <v>-15.25</v>
       </c>
-      <c r="P15" s="182">
+      <c r="P15" s="181">
         <v>-14.56</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="175">
         <v>-16.52</v>
       </c>
-      <c r="R15" s="178">
+      <c r="R15" s="176">
         <v>-16.36</v>
       </c>
-      <c r="S15" s="179">
+      <c r="S15" s="182">
         <v>-16.15</v>
       </c>
-      <c r="T15" s="170">
-        <v>6.46</v>
+      <c r="T15" s="177">
+        <v>9.79</v>
       </c>
     </row>
     <row r="16">
@@ -8944,38 +8944,38 @@
       <c r="I16" s="190">
         <v>0</v>
       </c>
-      <c r="J16" s="191">
+      <c r="J16" s="184">
         <v>10.04</v>
       </c>
-      <c r="K16" s="184">
+      <c r="K16" s="188">
         <v>6.65</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="189">
         <v>3.84</v>
       </c>
-      <c r="M16" s="187">
+      <c r="M16" s="193">
         <v>5.76</v>
       </c>
-      <c r="N16" s="192">
+      <c r="N16" s="191">
         <v>0.44</v>
       </c>
-      <c r="O16" s="186">
+      <c r="O16" s="194">
         <v>0.89</v>
       </c>
-      <c r="P16" s="195">
+      <c r="P16" s="185">
         <v>-3.69</v>
       </c>
-      <c r="Q16" s="193">
+      <c r="Q16" s="186">
         <v>-4.58</v>
       </c>
-      <c r="R16" s="188">
+      <c r="R16" s="192">
         <v>-5.17</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="195">
         <v>-6.5</v>
       </c>
-      <c r="T16" s="194">
-        <v>-14.62</v>
+      <c r="T16" s="187">
+        <v>-16.1</v>
       </c>
     </row>
     <row r="17">
@@ -8988,7 +8988,7 @@
       <c r="C17" t="str">
         <v>001360</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="207" t="str">
         <v>净卖: -1800.16万</v>
       </c>
       <c r="E17">
@@ -9003,41 +9003,41 @@
       <c r="H17">
         <v>0.1</v>
       </c>
-      <c r="I17" s="207">
+      <c r="I17" s="196">
         <v>-10.05</v>
       </c>
-      <c r="J17" s="200">
+      <c r="J17" s="208">
         <v>-19.04</v>
       </c>
-      <c r="K17" s="201">
+      <c r="K17" s="202">
         <v>-21.15</v>
       </c>
-      <c r="L17" s="208">
+      <c r="L17" s="203">
         <v>-22.16</v>
       </c>
-      <c r="M17" s="203">
+      <c r="M17" s="204">
         <v>-23.03</v>
       </c>
-      <c r="N17" s="196">
+      <c r="N17" s="198">
         <v>-22.4</v>
       </c>
-      <c r="O17" s="205">
+      <c r="O17" s="199">
         <v>-24.18</v>
       </c>
-      <c r="P17" s="197">
+      <c r="P17" s="205">
         <v>-24.04</v>
       </c>
-      <c r="Q17" s="206">
+      <c r="Q17" s="197">
         <v>-23.85</v>
       </c>
-      <c r="R17" s="202">
+      <c r="R17" s="206">
         <v>-24.28</v>
       </c>
-      <c r="S17" s="204">
+      <c r="S17" s="200">
         <v>-24.47</v>
       </c>
-      <c r="T17" s="198">
-        <v>-3.32</v>
+      <c r="T17" s="201">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="18">
@@ -9050,7 +9050,7 @@
       <c r="C18" t="str">
         <v>001360</v>
       </c>
-      <c r="D18" s="211" t="str">
+      <c r="D18" s="216" t="str">
         <v>净卖: -1799.99万</v>
       </c>
       <c r="E18">
@@ -9065,41 +9065,41 @@
       <c r="H18">
         <v>-9.14</v>
       </c>
-      <c r="I18" s="217">
+      <c r="I18" s="212">
         <v>-0.94</v>
       </c>
-      <c r="J18" s="212">
+      <c r="J18" s="217">
         <v>-3.53</v>
       </c>
-      <c r="K18" s="221">
+      <c r="K18" s="213">
         <v>-4.76</v>
       </c>
-      <c r="L18" s="210">
+      <c r="L18" s="214">
         <v>-5.82</v>
       </c>
-      <c r="M18" s="213">
+      <c r="M18" s="209">
         <v>-5.06</v>
       </c>
-      <c r="N18" s="214">
+      <c r="N18" s="219">
         <v>-7.24</v>
       </c>
-      <c r="O18" s="218">
+      <c r="O18" s="220">
         <v>-7.06</v>
       </c>
-      <c r="P18" s="219">
+      <c r="P18" s="221">
         <v>-6.82</v>
       </c>
       <c r="Q18" s="215">
         <v>-7.35</v>
       </c>
-      <c r="R18" s="220">
+      <c r="R18" s="210">
         <v>-7.59</v>
       </c>
-      <c r="S18" s="209">
+      <c r="S18" s="211">
         <v>-6.59</v>
       </c>
-      <c r="T18" s="216">
-        <v>18.29</v>
+      <c r="T18" s="218">
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -9112,7 +9112,7 @@
       <c r="C19" t="str">
         <v>300620</v>
       </c>
-      <c r="D19" s="233" t="str">
+      <c r="D19" s="223" t="str">
         <v>净买: 1215.21万</v>
       </c>
       <c r="E19">
@@ -9127,41 +9127,41 @@
       <c r="H19">
         <v>19.99</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="234">
         <v>0</v>
       </c>
-      <c r="J19" s="229">
+      <c r="J19" s="224">
         <v>20.01</v>
       </c>
-      <c r="K19" s="224">
+      <c r="K19" s="231">
         <v>21.14</v>
       </c>
-      <c r="L19" s="230">
+      <c r="L19" s="226">
         <v>24.09</v>
       </c>
-      <c r="M19" s="234">
+      <c r="M19" s="227">
         <v>46.79</v>
       </c>
-      <c r="N19" s="226">
+      <c r="N19" s="228">
         <v>50.73</v>
       </c>
-      <c r="O19" s="227">
+      <c r="O19" s="229">
         <v>40.57</v>
       </c>
-      <c r="P19" s="225">
+      <c r="P19" s="232">
         <v>31.96</v>
       </c>
-      <c r="Q19" s="228">
+      <c r="Q19" s="230">
         <v>34.41</v>
       </c>
-      <c r="R19" s="231">
+      <c r="R19" s="225">
         <v>39.6</v>
       </c>
-      <c r="S19" s="232">
+      <c r="S19" s="222">
         <v>34.69</v>
       </c>
-      <c r="T19" s="222">
-        <v>259.93</v>
+      <c r="T19" s="233">
+        <v>262.74</v>
       </c>
     </row>
     <row r="20">
@@ -9189,41 +9189,41 @@
       <c r="H20">
         <v>3.85</v>
       </c>
-      <c r="I20" s="243">
+      <c r="I20" s="239">
         <v>5.93</v>
       </c>
-      <c r="J20" s="244">
+      <c r="J20" s="243">
         <v>1.38</v>
       </c>
-      <c r="K20" s="245">
+      <c r="K20" s="244">
         <v>-1.17</v>
       </c>
-      <c r="L20" s="235">
+      <c r="L20" s="240">
         <v>-10.91</v>
       </c>
-      <c r="M20" s="236">
+      <c r="M20" s="246">
         <v>-11.76</v>
       </c>
-      <c r="N20" s="239">
+      <c r="N20" s="241">
         <v>-12.39</v>
       </c>
-      <c r="O20" s="237">
+      <c r="O20" s="236">
         <v>-9.96</v>
       </c>
-      <c r="P20" s="246">
+      <c r="P20" s="237">
         <v>-15.15</v>
       </c>
-      <c r="Q20" s="240">
+      <c r="Q20" s="245">
         <v>-17.9</v>
       </c>
       <c r="R20" s="247">
         <v>-19.39</v>
       </c>
-      <c r="S20" s="241">
+      <c r="S20" s="242">
         <v>-18.11</v>
       </c>
-      <c r="T20" s="242">
-        <v>-20.44</v>
+      <c r="T20" s="235">
+        <v>-19.92</v>
       </c>
     </row>
     <row r="21">
@@ -9236,7 +9236,7 @@
       <c r="C21" t="str">
         <v>301517</v>
       </c>
-      <c r="D21" s="251" t="str">
+      <c r="D21" s="256" t="str">
         <v>净买: 1391.15万</v>
       </c>
       <c r="E21">
@@ -9251,41 +9251,41 @@
       <c r="H21">
         <v>20</v>
       </c>
-      <c r="I21" s="252">
+      <c r="I21" s="248">
         <v>-14.18</v>
       </c>
-      <c r="J21" s="259">
+      <c r="J21" s="249">
         <v>-19.79</v>
       </c>
-      <c r="K21" s="249">
+      <c r="K21" s="250">
         <v>-18.67</v>
       </c>
-      <c r="L21" s="253">
+      <c r="L21" s="257">
         <v>-21.09</v>
       </c>
-      <c r="M21" s="254">
+      <c r="M21" s="258">
         <v>-22.21</v>
       </c>
-      <c r="N21" s="255">
+      <c r="N21" s="251">
         <v>-18.54</v>
       </c>
-      <c r="O21" s="260">
+      <c r="O21" s="252">
         <v>-22.58</v>
       </c>
-      <c r="P21" s="256">
+      <c r="P21" s="259">
         <v>-27.04</v>
       </c>
-      <c r="Q21" s="248">
+      <c r="Q21" s="253">
         <v>-25.09</v>
       </c>
-      <c r="R21" s="257">
+      <c r="R21" s="254">
         <v>-21.88</v>
       </c>
-      <c r="S21" s="250">
+      <c r="S21" s="255">
         <v>-25.85</v>
       </c>
-      <c r="T21" s="258">
-        <v>13.64</v>
+      <c r="T21" s="260">
+        <v>9.3</v>
       </c>
     </row>
     <row r="22">
@@ -9298,7 +9298,7 @@
       <c r="C22" t="str">
         <v>002547</v>
       </c>
-      <c r="D22" s="269" t="str">
+      <c r="D22" s="268" t="str">
         <v>净买: 4862.70万</v>
       </c>
       <c r="E22">
@@ -9313,41 +9313,41 @@
       <c r="H22">
         <v>10.1</v>
       </c>
-      <c r="I22" s="263">
+      <c r="I22" s="271">
         <v>0</v>
       </c>
       <c r="J22" s="273">
         <v>7.01</v>
       </c>
-      <c r="K22" s="264">
+      <c r="K22" s="261">
         <v>0.36</v>
       </c>
-      <c r="L22" s="270">
+      <c r="L22" s="266">
         <v>4.68</v>
       </c>
-      <c r="M22" s="271">
+      <c r="M22" s="267">
         <v>15.11</v>
       </c>
-      <c r="N22" s="265">
+      <c r="N22" s="262">
         <v>21.76</v>
       </c>
-      <c r="O22" s="266">
+      <c r="O22" s="263">
         <v>22.66</v>
       </c>
-      <c r="P22" s="272">
+      <c r="P22" s="269">
         <v>17.81</v>
       </c>
-      <c r="Q22" s="261">
+      <c r="Q22" s="270">
         <v>9.17</v>
       </c>
-      <c r="R22" s="267">
+      <c r="R22" s="264">
         <v>12.59</v>
       </c>
-      <c r="S22" s="262">
+      <c r="S22" s="265">
         <v>7.01</v>
       </c>
-      <c r="T22" s="268">
-        <v>-44.78</v>
+      <c r="T22" s="272">
+        <v>-43.35</v>
       </c>
     </row>
     <row r="23">
@@ -9360,7 +9360,7 @@
       <c r="C23" t="str">
         <v>002547</v>
       </c>
-      <c r="D23" s="282" t="str">
+      <c r="D23" s="278" t="str">
         <v>净卖: -5175.09万</v>
       </c>
       <c r="E23">
@@ -9375,41 +9375,41 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23" s="286">
+      <c r="I23" s="283">
         <v>7.01</v>
       </c>
-      <c r="J23" s="274">
+      <c r="J23" s="284">
         <v>0.36</v>
       </c>
-      <c r="K23" s="283">
+      <c r="K23" s="286">
         <v>4.68</v>
       </c>
-      <c r="L23" s="284">
+      <c r="L23" s="279">
         <v>15.11</v>
       </c>
-      <c r="M23" s="278">
+      <c r="M23" s="280">
         <v>21.76</v>
       </c>
-      <c r="N23" s="280">
+      <c r="N23" s="281">
         <v>22.66</v>
       </c>
-      <c r="O23" s="275">
+      <c r="O23" s="285">
         <v>17.81</v>
       </c>
-      <c r="P23" s="276">
+      <c r="P23" s="274">
         <v>9.17</v>
       </c>
-      <c r="Q23" s="277">
+      <c r="Q23" s="282">
         <v>12.59</v>
       </c>
-      <c r="R23" s="281">
+      <c r="R23" s="275">
         <v>7.01</v>
       </c>
-      <c r="S23" s="285">
+      <c r="S23" s="276">
         <v>8.09</v>
       </c>
-      <c r="T23" s="279">
-        <v>-44.78</v>
+      <c r="T23" s="277">
+        <v>-43.35</v>
       </c>
     </row>
     <row r="24">
@@ -9422,7 +9422,7 @@
       <c r="C24" t="str">
         <v>920020</v>
       </c>
-      <c r="D24" s="290" t="str">
+      <c r="D24" s="292" t="str">
         <v>净卖: -668.61万</v>
       </c>
       <c r="E24">
@@ -9437,19 +9437,19 @@
       <c r="H24">
         <v>-9.66</v>
       </c>
-      <c r="I24" s="296">
+      <c r="I24" s="293">
         <v>14.02</v>
       </c>
-      <c r="J24" s="293">
+      <c r="J24" s="297">
         <v>2.92</v>
       </c>
-      <c r="K24" s="291">
+      <c r="K24" s="288">
         <v>1.38</v>
       </c>
-      <c r="L24" s="294">
+      <c r="L24" s="298">
         <v>0.51</v>
       </c>
-      <c r="M24" s="297">
+      <c r="M24" s="294">
         <v>-0.82</v>
       </c>
       <c r="N24" s="299">
@@ -9458,20 +9458,20 @@
       <c r="O24" s="287">
         <v>0.87</v>
       </c>
-      <c r="P24" s="298">
+      <c r="P24" s="295">
         <v>-2.4</v>
       </c>
-      <c r="Q24" s="288">
+      <c r="Q24" s="289">
         <v>-5.17</v>
       </c>
-      <c r="R24" s="289">
+      <c r="R24" s="296">
         <v>-4.76</v>
       </c>
-      <c r="S24" s="292">
+      <c r="S24" s="291">
         <v>-4.35</v>
       </c>
-      <c r="T24" s="295">
-        <v>-19.54</v>
+      <c r="T24" s="290">
+        <v>-20.72</v>
       </c>
     </row>
     <row r="25">
@@ -9484,7 +9484,7 @@
       <c r="C25" t="str">
         <v>605178</v>
       </c>
-      <c r="D25" s="301" t="str">
+      <c r="D25" s="307" t="str">
         <v>净买: 3874.18万</v>
       </c>
       <c r="E25">
@@ -9499,41 +9499,41 @@
       <c r="H25">
         <v>10</v>
       </c>
-      <c r="I25" s="302">
+      <c r="I25" s="308">
         <v>0</v>
       </c>
-      <c r="J25" s="307">
+      <c r="J25" s="301">
         <v>10</v>
       </c>
-      <c r="K25" s="308">
+      <c r="K25" s="309">
         <v>0.58</v>
       </c>
-      <c r="L25" s="311">
+      <c r="L25" s="302">
         <v>4.74</v>
       </c>
-      <c r="M25" s="306">
+      <c r="M25" s="312">
         <v>13.42</v>
       </c>
       <c r="N25" s="303">
         <v>19.72</v>
       </c>
-      <c r="O25" s="304">
+      <c r="O25" s="310">
         <v>26.01</v>
       </c>
-      <c r="P25" s="305">
+      <c r="P25" s="311">
         <v>16.89</v>
       </c>
-      <c r="Q25" s="309">
+      <c r="Q25" s="305">
         <v>6.52</v>
       </c>
-      <c r="R25" s="310">
+      <c r="R25" s="300">
         <v>10.9</v>
       </c>
-      <c r="S25" s="312">
+      <c r="S25" s="304">
         <v>12.81</v>
       </c>
-      <c r="T25" s="300">
-        <v>2.39</v>
+      <c r="T25" s="306">
+        <v>11.77</v>
       </c>
     </row>
     <row r="26">
@@ -9546,7 +9546,7 @@
       <c r="C26" t="str">
         <v>000407</v>
       </c>
-      <c r="D26" s="325" t="str">
+      <c r="D26" s="319" t="str">
         <v>净买: 788.81万</v>
       </c>
       <c r="E26">
@@ -9561,41 +9561,41 @@
       <c r="H26">
         <v>10.1</v>
       </c>
-      <c r="I26" s="315">
+      <c r="I26" s="320">
         <v>0</v>
       </c>
-      <c r="J26" s="313">
+      <c r="J26" s="323">
         <v>10.04</v>
       </c>
-      <c r="K26" s="320">
+      <c r="K26" s="321">
         <v>20.96</v>
       </c>
-      <c r="L26" s="314">
+      <c r="L26" s="316">
         <v>32.97</v>
       </c>
-      <c r="M26" s="316">
+      <c r="M26" s="322">
         <v>46.29</v>
       </c>
       <c r="N26" s="317">
         <v>31.66</v>
       </c>
-      <c r="O26" s="321">
+      <c r="O26" s="324">
         <v>30.35</v>
       </c>
-      <c r="P26" s="318">
+      <c r="P26" s="325">
         <v>17.25</v>
       </c>
-      <c r="Q26" s="319">
+      <c r="Q26" s="314">
         <v>5.46</v>
       </c>
-      <c r="R26" s="322">
+      <c r="R26" s="313">
         <v>5.9</v>
       </c>
-      <c r="S26" s="323">
+      <c r="S26" s="318">
         <v>12.45</v>
       </c>
-      <c r="T26" s="324">
-        <v>2.4</v>
+      <c r="T26" s="315">
+        <v>3.28</v>
       </c>
     </row>
     <row r="27">
@@ -9608,7 +9608,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="337" t="str">
+      <c r="D27" s="330" t="str">
         <v>净买: 3123.85万</v>
       </c>
       <c r="E27">
@@ -9623,41 +9623,41 @@
       <c r="H27">
         <v>9.96</v>
       </c>
-      <c r="I27" s="338">
+      <c r="I27" s="334">
         <v>0</v>
       </c>
-      <c r="J27" s="335">
+      <c r="J27" s="336">
         <v>-9.95</v>
       </c>
-      <c r="K27" s="326">
+      <c r="K27" s="331">
         <v>-19.01</v>
       </c>
-      <c r="L27" s="333">
+      <c r="L27" s="332">
         <v>-27.04</v>
       </c>
-      <c r="M27" s="327">
+      <c r="M27" s="337">
         <v>-30.61</v>
       </c>
-      <c r="N27" s="328">
+      <c r="N27" s="335">
         <v>-28.7</v>
       </c>
-      <c r="O27" s="329">
+      <c r="O27" s="338">
         <v>-31.89</v>
       </c>
-      <c r="P27" s="334">
+      <c r="P27" s="326">
         <v>-31.63</v>
       </c>
-      <c r="Q27" s="331">
+      <c r="Q27" s="328">
         <v>-28.95</v>
       </c>
-      <c r="R27" s="330">
+      <c r="R27" s="333">
         <v>-26.53</v>
       </c>
-      <c r="S27" s="336">
+      <c r="S27" s="329">
         <v>-24.49</v>
       </c>
-      <c r="T27" s="332">
-        <v>-27.17</v>
+      <c r="T27" s="327">
+        <v>-26.4</v>
       </c>
     </row>
     <row r="28">
@@ -9670,7 +9670,7 @@
       <c r="C28" t="str">
         <v>300094</v>
       </c>
-      <c r="D28" s="340" t="str">
+      <c r="D28" s="346" t="str">
         <v>净卖: -3846.51万</v>
       </c>
       <c r="E28">
@@ -9685,41 +9685,41 @@
       <c r="H28">
         <v>0.37</v>
       </c>
-      <c r="I28" s="341">
+      <c r="I28" s="344">
         <v>-11.85</v>
       </c>
-      <c r="J28" s="342">
+      <c r="J28" s="347">
         <v>-12.41</v>
       </c>
-      <c r="K28" s="347">
+      <c r="K28" s="339">
         <v>-8.33</v>
       </c>
-      <c r="L28" s="348">
+      <c r="L28" s="340">
         <v>-17.96</v>
       </c>
-      <c r="M28" s="351">
+      <c r="M28" s="341">
         <v>-23.89</v>
       </c>
-      <c r="N28" s="349">
+      <c r="N28" s="342">
         <v>-22.96</v>
       </c>
-      <c r="O28" s="343">
+      <c r="O28" s="348">
         <v>-24.26</v>
       </c>
-      <c r="P28" s="344">
+      <c r="P28" s="343">
         <v>-23.15</v>
       </c>
-      <c r="Q28" s="345">
+      <c r="Q28" s="350">
         <v>-21.48</v>
       </c>
-      <c r="R28" s="346">
+      <c r="R28" s="349">
         <v>-21.85</v>
       </c>
-      <c r="S28" s="350">
+      <c r="S28" s="351">
         <v>-27.78</v>
       </c>
-      <c r="T28" s="339">
-        <v>-44.44</v>
+      <c r="T28" s="345">
+        <v>-43.89</v>
       </c>
     </row>
     <row r="29">
@@ -9732,7 +9732,7 @@
       <c r="C29" t="str">
         <v>002682</v>
       </c>
-      <c r="D29" s="360" t="str">
+      <c r="D29" s="363" t="str">
         <v>净卖: -2565.97万</v>
       </c>
       <c r="E29">
@@ -9747,41 +9747,41 @@
       <c r="H29">
         <v>-6.94</v>
       </c>
-      <c r="I29" s="353">
+      <c r="I29" s="360">
         <v>-3.35</v>
       </c>
       <c r="J29" s="361">
         <v>-12.94</v>
       </c>
-      <c r="K29" s="358">
+      <c r="K29" s="354">
         <v>-17.2</v>
       </c>
-      <c r="L29" s="364">
+      <c r="L29" s="355">
         <v>-14.92</v>
       </c>
-      <c r="M29" s="354">
+      <c r="M29" s="358">
         <v>-18.72</v>
       </c>
-      <c r="N29" s="355">
+      <c r="N29" s="364">
         <v>-18.42</v>
       </c>
-      <c r="O29" s="352">
+      <c r="O29" s="362">
         <v>-15.22</v>
       </c>
-      <c r="P29" s="356">
+      <c r="P29" s="352">
         <v>-12.33</v>
       </c>
-      <c r="Q29" s="362">
+      <c r="Q29" s="353">
         <v>-9.89</v>
       </c>
-      <c r="R29" s="357">
+      <c r="R29" s="356">
         <v>-0.91</v>
       </c>
-      <c r="S29" s="363">
+      <c r="S29" s="357">
         <v>8.98</v>
       </c>
       <c r="T29" s="359">
-        <v>-13.09</v>
+        <v>-12.18</v>
       </c>
     </row>
     <row r="30">
@@ -9794,7 +9794,7 @@
       <c r="C30" t="str">
         <v>603069</v>
       </c>
-      <c r="D30" s="366" t="str">
+      <c r="D30" s="372" t="str">
         <v>净买: 2184.48万</v>
       </c>
       <c r="E30">
@@ -9809,10 +9809,10 @@
       <c r="H30">
         <v>10.02</v>
       </c>
-      <c r="I30" s="372">
+      <c r="I30" s="377">
         <v>0</v>
       </c>
-      <c r="J30" s="367">
+      <c r="J30" s="374">
         <v>1.25</v>
       </c>
       <c r="K30" s="375">
@@ -9824,26 +9824,26 @@
       <c r="M30" s="368">
         <v>-1.42</v>
       </c>
-      <c r="N30" s="376">
+      <c r="N30" s="366">
         <v>-5.96</v>
       </c>
-      <c r="O30" s="369">
+      <c r="O30" s="376">
         <v>-5.99</v>
       </c>
-      <c r="P30" s="370">
+      <c r="P30" s="369">
         <v>-13.57</v>
       </c>
-      <c r="Q30" s="377">
+      <c r="Q30" s="373">
         <v>-13.64</v>
       </c>
-      <c r="R30" s="373">
+      <c r="R30" s="367">
         <v>-14.16</v>
       </c>
-      <c r="S30" s="374">
+      <c r="S30" s="370">
         <v>-15.27</v>
       </c>
       <c r="T30" s="371">
-        <v>-42.11</v>
+        <v>-41.79</v>
       </c>
     </row>
     <row r="31">
@@ -9856,7 +9856,7 @@
       <c r="C31" t="str">
         <v>002009</v>
       </c>
-      <c r="D31" s="388" t="str">
+      <c r="D31" s="378" t="str">
         <v>净买: 3463.54万</v>
       </c>
       <c r="E31">
@@ -9871,41 +9871,41 @@
       <c r="H31">
         <v>10</v>
       </c>
-      <c r="I31" s="385">
+      <c r="I31" s="382">
         <v>0</v>
       </c>
-      <c r="J31" s="382">
+      <c r="J31" s="389">
         <v>10.02</v>
       </c>
-      <c r="K31" s="386">
+      <c r="K31" s="383">
         <v>21.02</v>
       </c>
-      <c r="L31" s="389">
+      <c r="L31" s="386">
         <v>16.84</v>
       </c>
-      <c r="M31" s="383">
+      <c r="M31" s="387">
         <v>14.72</v>
       </c>
-      <c r="N31" s="390">
+      <c r="N31" s="388">
         <v>8.01</v>
       </c>
-      <c r="O31" s="380">
+      <c r="O31" s="390">
         <v>12.24</v>
       </c>
-      <c r="P31" s="387">
+      <c r="P31" s="379">
         <v>12.65</v>
       </c>
-      <c r="Q31" s="378">
+      <c r="Q31" s="380">
         <v>15.19</v>
       </c>
-      <c r="R31" s="379">
+      <c r="R31" s="384">
         <v>18.85</v>
       </c>
-      <c r="S31" s="381">
+      <c r="S31" s="385">
         <v>11.93</v>
       </c>
-      <c r="T31" s="384">
-        <v>22.99</v>
+      <c r="T31" s="381">
+        <v>22.42</v>
       </c>
     </row>
     <row r="32">
@@ -9918,7 +9918,7 @@
       <c r="C32" t="str">
         <v>002009</v>
       </c>
-      <c r="D32" s="396" t="str">
+      <c r="D32" s="401" t="str">
         <v>净卖: -4207.08万</v>
       </c>
       <c r="E32">
@@ -9933,41 +9933,41 @@
       <c r="H32">
         <v>9.92</v>
       </c>
-      <c r="I32" s="397">
+      <c r="I32" s="396">
         <v>0.09</v>
       </c>
-      <c r="J32" s="398">
+      <c r="J32" s="397">
         <v>10.1</v>
       </c>
       <c r="K32" s="391">
         <v>6.3</v>
       </c>
-      <c r="L32" s="399">
+      <c r="L32" s="392">
         <v>4.37</v>
       </c>
-      <c r="M32" s="400">
+      <c r="M32" s="393">
         <v>-1.74</v>
       </c>
-      <c r="N32" s="401">
+      <c r="N32" s="394">
         <v>2.11</v>
       </c>
-      <c r="O32" s="392">
+      <c r="O32" s="398">
         <v>2.49</v>
       </c>
-      <c r="P32" s="393">
+      <c r="P32" s="399">
         <v>4.79</v>
       </c>
-      <c r="Q32" s="395">
+      <c r="Q32" s="400">
         <v>8.13</v>
       </c>
-      <c r="R32" s="402">
+      <c r="R32" s="395">
         <v>1.83</v>
       </c>
-      <c r="S32" s="403">
+      <c r="S32" s="402">
         <v>2.63</v>
       </c>
-      <c r="T32" s="394">
-        <v>11.89</v>
+      <c r="T32" s="403">
+        <v>11.37</v>
       </c>
     </row>
     <row r="33">
@@ -9980,7 +9980,7 @@
       <c r="C33" t="str">
         <v>002009</v>
       </c>
-      <c r="D33" s="409" t="str">
+      <c r="D33" s="415" t="str">
         <v>净卖: -4209.56万</v>
       </c>
       <c r="E33">
@@ -9995,41 +9995,41 @@
       <c r="H33">
         <v>2.21</v>
       </c>
-      <c r="I33" s="410">
+      <c r="I33" s="409">
         <v>7.63</v>
       </c>
-      <c r="J33" s="411">
+      <c r="J33" s="412">
         <v>3.9</v>
       </c>
-      <c r="K33" s="412">
+      <c r="K33" s="416">
         <v>2.02</v>
       </c>
-      <c r="L33" s="416">
+      <c r="L33" s="404">
         <v>-3.95</v>
       </c>
-      <c r="M33" s="404">
+      <c r="M33" s="405">
         <v>-0.18</v>
       </c>
-      <c r="N33" s="413">
+      <c r="N33" s="410">
         <v>0.18</v>
       </c>
-      <c r="O33" s="414">
+      <c r="O33" s="411">
         <v>2.43</v>
       </c>
-      <c r="P33" s="408">
+      <c r="P33" s="406">
         <v>5.7</v>
       </c>
-      <c r="Q33" s="415">
+      <c r="Q33" s="408">
         <v>-0.46</v>
       </c>
-      <c r="R33" s="405">
+      <c r="R33" s="413">
         <v>0.32</v>
       </c>
-      <c r="S33" s="406">
+      <c r="S33" s="407">
         <v>-1.52</v>
       </c>
-      <c r="T33" s="407">
-        <v>9.37</v>
+      <c r="T33" s="414">
+        <v>8.87</v>
       </c>
     </row>
     <row r="34">
@@ -10042,7 +10042,7 @@
       <c r="C34" t="str">
         <v>002969</v>
       </c>
-      <c r="D34" s="424" t="str">
+      <c r="D34" s="423" t="str">
         <v>净卖: -2752.13万</v>
       </c>
       <c r="E34">
@@ -10057,41 +10057,41 @@
       <c r="H34">
         <v>0.55</v>
       </c>
-      <c r="I34" s="421">
+      <c r="I34" s="419">
         <v>7.62</v>
       </c>
-      <c r="J34" s="417">
+      <c r="J34" s="420">
         <v>18.38</v>
       </c>
-      <c r="K34" s="418">
+      <c r="K34" s="424">
         <v>30.24</v>
       </c>
-      <c r="L34" s="425">
+      <c r="L34" s="421">
         <v>37.86</v>
       </c>
-      <c r="M34" s="426">
+      <c r="M34" s="422">
         <v>51.69</v>
       </c>
-      <c r="N34" s="427">
+      <c r="N34" s="425">
         <v>36.53</v>
       </c>
-      <c r="O34" s="422">
+      <c r="O34" s="426">
         <v>22.86</v>
       </c>
-      <c r="P34" s="428">
+      <c r="P34" s="427">
         <v>35.11</v>
       </c>
-      <c r="Q34" s="423">
+      <c r="Q34" s="428">
         <v>48.63</v>
       </c>
       <c r="R34" s="429">
         <v>52.47</v>
       </c>
-      <c r="S34" s="419">
+      <c r="S34" s="417">
         <v>67.71</v>
       </c>
-      <c r="T34" s="420">
-        <v>69.76</v>
+      <c r="T34" s="418">
+        <v>70.38</v>
       </c>
     </row>
     <row r="35">
@@ -10104,7 +10104,7 @@
       <c r="C35" t="str">
         <v>600683</v>
       </c>
-      <c r="D35" s="439" t="str">
+      <c r="D35" s="440" t="str">
         <v>净买: 819.30万</v>
       </c>
       <c r="E35">
@@ -10119,41 +10119,41 @@
       <c r="H35">
         <v>10.1</v>
       </c>
-      <c r="I35" s="436">
+      <c r="I35" s="441">
         <v>0</v>
       </c>
-      <c r="J35" s="431">
+      <c r="J35" s="439">
         <v>10.09</v>
       </c>
-      <c r="K35" s="432">
+      <c r="K35" s="442">
         <v>21.1</v>
       </c>
-      <c r="L35" s="440">
+      <c r="L35" s="433">
         <v>11.01</v>
       </c>
-      <c r="M35" s="433">
+      <c r="M35" s="430">
         <v>22.2</v>
       </c>
       <c r="N35" s="434">
         <v>22.57</v>
       </c>
-      <c r="O35" s="441">
+      <c r="O35" s="436">
         <v>32.29</v>
       </c>
-      <c r="P35" s="437">
+      <c r="P35" s="435">
         <v>27.16</v>
       </c>
-      <c r="Q35" s="442">
+      <c r="Q35" s="431">
         <v>23.12</v>
       </c>
-      <c r="R35" s="435">
+      <c r="R35" s="437">
         <v>30.46</v>
       </c>
-      <c r="S35" s="430">
+      <c r="S35" s="438">
         <v>37.06</v>
       </c>
-      <c r="T35" s="438">
-        <v>151.56</v>
+      <c r="T35" s="432">
+        <v>148.81</v>
       </c>
     </row>
     <row r="36">
@@ -10166,7 +10166,7 @@
       <c r="C36" t="str">
         <v>002056</v>
       </c>
-      <c r="D36" s="449" t="str">
+      <c r="D36" s="450" t="str">
         <v>净卖: -2838.92万</v>
       </c>
       <c r="E36">
@@ -10181,41 +10181,41 @@
       <c r="H36">
         <v>1.28</v>
       </c>
-      <c r="I36" s="443">
+      <c r="I36" s="451">
         <v>8.62</v>
       </c>
-      <c r="J36" s="450">
+      <c r="J36" s="452">
         <v>-0.42</v>
       </c>
-      <c r="K36" s="444">
+      <c r="K36" s="453">
         <v>-4.25</v>
       </c>
-      <c r="L36" s="445">
+      <c r="L36" s="444">
         <v>-5.84</v>
       </c>
-      <c r="M36" s="453">
+      <c r="M36" s="454">
         <v>-8.66</v>
       </c>
-      <c r="N36" s="446">
+      <c r="N36" s="448">
         <v>-6.43</v>
       </c>
-      <c r="O36" s="451">
+      <c r="O36" s="445">
         <v>-9.21</v>
       </c>
-      <c r="P36" s="454">
+      <c r="P36" s="446">
         <v>-9.21</v>
       </c>
-      <c r="Q36" s="448">
+      <c r="Q36" s="447">
         <v>-7.78</v>
       </c>
-      <c r="R36" s="447">
+      <c r="R36" s="449">
         <v>-9.46</v>
       </c>
-      <c r="S36" s="452">
+      <c r="S36" s="455">
         <v>-9.92</v>
       </c>
-      <c r="T36" s="455">
-        <v>-20.09</v>
+      <c r="T36" s="443">
+        <v>-21.06</v>
       </c>
     </row>
     <row r="37">
@@ -10277,31 +10277,31 @@
       <c r="F38" t="str"/>
       <c r="G38" t="str"/>
       <c r="H38" t="str"/>
-      <c r="I38" s="467">
+      <c r="I38" s="464">
         <v>31.43</v>
       </c>
       <c r="J38" s="462">
         <v>62.86</v>
       </c>
-      <c r="K38" s="459">
+      <c r="K38" s="465">
         <v>54.29</v>
       </c>
-      <c r="L38" s="456">
+      <c r="L38" s="466">
         <v>54.29</v>
       </c>
-      <c r="M38" s="464">
+      <c r="M38" s="459">
         <v>42.86</v>
       </c>
-      <c r="N38" s="465">
+      <c r="N38" s="457">
         <v>42.86</v>
       </c>
-      <c r="O38" s="463">
+      <c r="O38" s="467">
         <v>48.57</v>
       </c>
-      <c r="P38" s="457">
+      <c r="P38" s="463">
         <v>37.14</v>
       </c>
-      <c r="Q38" s="466">
+      <c r="Q38" s="458">
         <v>31.43</v>
       </c>
       <c r="R38" s="460">
@@ -10310,7 +10310,7 @@
       <c r="S38" s="461">
         <v>31.43</v>
       </c>
-      <c r="T38" s="458">
+      <c r="T38" s="456">
         <v>45.71</v>
       </c>
     </row>
@@ -10325,41 +10325,41 @@
       <c r="F39" t="str"/>
       <c r="G39" t="str"/>
       <c r="H39" t="str"/>
-      <c r="I39" s="476">
+      <c r="I39" s="470">
         <v>0.72</v>
       </c>
-      <c r="J39" s="468">
+      <c r="J39" s="477">
         <v>1.7</v>
       </c>
-      <c r="K39" s="473">
+      <c r="K39" s="472">
         <v>1.83</v>
       </c>
-      <c r="L39" s="477">
+      <c r="L39" s="478">
         <v>1.8</v>
       </c>
-      <c r="M39" s="470">
+      <c r="M39" s="479">
         <v>1.64</v>
       </c>
-      <c r="N39" s="474">
+      <c r="N39" s="475">
         <v>0.36</v>
       </c>
-      <c r="O39" s="469">
+      <c r="O39" s="476">
         <v>0.46</v>
       </c>
-      <c r="P39" s="471">
+      <c r="P39" s="468">
         <v>-2.04</v>
       </c>
-      <c r="Q39" s="478">
+      <c r="Q39" s="471">
         <v>-3.24</v>
       </c>
-      <c r="R39" s="479">
+      <c r="R39" s="473">
         <v>-2.68</v>
       </c>
-      <c r="S39" s="475">
+      <c r="S39" s="469">
         <v>-2.27</v>
       </c>
-      <c r="T39" s="472">
-        <v>8.33</v>
+      <c r="T39" s="474">
+        <v>9.21</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/正经哥/index.xlsx
+++ b/youzi/正经哥/index.xlsx
@@ -39,6 +39,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0ABB1"/>
         <bgColor/>
       </patternFill>
@@ -57,6 +117,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -69,31 +159,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,37 +267,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,79 +315,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -249,6 +429,1788 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4554"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD7EEDD"/>
         <bgColor/>
       </patternFill>
@@ -261,49 +2223,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -321,19 +2253,217 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -345,91 +2475,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBF8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -447,43 +2667,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -495,2275 +2769,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7FBF8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF23963E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2775,139 +2811,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF65C07A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE0F2E4"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF27A544"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDE4654"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8058,7 +8058,7 @@
       <c r="C2" t="str">
         <v>000665</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="2" t="str">
         <v>净卖: -2301.68万</v>
       </c>
       <c r="E2">
@@ -8073,41 +8073,41 @@
       <c r="H2">
         <v>10.06</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="3">
         <v>0</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <v>10</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="4">
         <v>21.03</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="7">
         <v>30</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="8">
         <v>18.79</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="5">
         <v>10</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="9">
         <v>11.72</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="10">
         <v>10.17</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="11">
         <v>2.07</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="12">
         <v>-4.66</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="13">
         <v>-8.45</v>
       </c>
-      <c r="T2" s="6">
-        <v>-18.97</v>
+      <c r="T2" s="1">
+        <v>-17.59</v>
       </c>
     </row>
     <row r="3">
@@ -8141,35 +8141,35 @@
       <c r="J3" s="25">
         <v>10.06</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="20">
         <v>21.12</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="26">
         <v>9.77</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="15">
         <v>-1.15</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="21">
         <v>-8.76</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="22">
         <v>-11.35</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="23">
         <v>-12.36</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="24">
         <v>-13.22</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="14">
         <v>-21.84</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="16">
         <v>-23.99</v>
       </c>
-      <c r="T3" s="24">
-        <v>47.99</v>
+      <c r="T3" s="17">
+        <v>40.37</v>
       </c>
     </row>
     <row r="4">
@@ -8182,7 +8182,7 @@
       <c r="C4" t="str">
         <v>002300</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="38" t="str">
         <v>净卖: -2576.68万</v>
       </c>
       <c r="E4">
@@ -8197,19 +8197,19 @@
       <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="39">
         <v>9.34</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="32">
         <v>-0.91</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="27">
         <v>-10.77</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="33">
         <v>-17.64</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="36">
         <v>-19.97</v>
       </c>
       <c r="N4" s="28">
@@ -8218,20 +8218,20 @@
       <c r="O4" s="29">
         <v>-21.66</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="34">
         <v>-29.44</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="37">
         <v>-31.39</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="30">
         <v>-28.92</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="31">
         <v>-27.63</v>
       </c>
-      <c r="T4" s="39">
-        <v>33.59</v>
+      <c r="T4" s="35">
+        <v>26.72</v>
       </c>
     </row>
     <row r="5">
@@ -8244,7 +8244,7 @@
       <c r="C5" t="str">
         <v>002688</v>
       </c>
-      <c r="D5" s="47" t="str">
+      <c r="D5" s="46" t="str">
         <v>净买: 5775.20万</v>
       </c>
       <c r="E5">
@@ -8259,41 +8259,41 @@
       <c r="H5">
         <v>9.93</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="50">
         <v>0</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="51">
         <v>9.95</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="47">
         <v>20.98</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="44">
         <v>30.17</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="52">
         <v>17.15</v>
       </c>
-      <c r="N5" s="50">
+      <c r="N5" s="48">
         <v>8.58</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="45">
         <v>10.57</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="49">
         <v>-0.46</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="40">
         <v>-5.36</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="41">
         <v>-5.05</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="42">
         <v>-4.29</v>
       </c>
-      <c r="T5" s="46">
-        <v>-10.87</v>
+      <c r="T5" s="43">
+        <v>-9.95</v>
       </c>
     </row>
     <row r="6">
@@ -8306,7 +8306,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="65" t="str">
         <v>净卖: -7396.08万</v>
       </c>
       <c r="E6">
@@ -8321,41 +8321,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="53">
         <v>7.59</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="59">
         <v>-3.16</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="54">
         <v>-10.25</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="55">
         <v>-8.61</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="60">
         <v>-17.72</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="62">
         <v>-21.77</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="63">
         <v>-21.52</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="56">
         <v>-20.89</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="57">
         <v>-16.71</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="61">
         <v>-20.76</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="58">
         <v>-17.09</v>
       </c>
-      <c r="T6" s="55">
-        <v>-26.33</v>
+      <c r="T6" s="64">
+        <v>-25.57</v>
       </c>
     </row>
     <row r="7">
@@ -8368,7 +8368,7 @@
       <c r="C7" t="str">
         <v>600697</v>
       </c>
-      <c r="D7" s="77" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -2819.93万</v>
       </c>
       <c r="E7">
@@ -8383,41 +8383,41 @@
       <c r="H7">
         <v>-9.28</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="76">
         <v>3.2</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="68">
         <v>6.95</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="72">
         <v>17.66</v>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="73">
         <v>13.12</v>
       </c>
-      <c r="M7" s="74">
+      <c r="M7" s="77">
         <v>1.95</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="71">
         <v>0</v>
       </c>
-      <c r="O7" s="69">
+      <c r="O7" s="78">
         <v>4.3</v>
       </c>
-      <c r="P7" s="70">
+      <c r="P7" s="74">
         <v>-1.72</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="69">
         <v>-5.31</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="75">
         <v>-5.23</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="66">
         <v>-7.97</v>
       </c>
-      <c r="T7" s="76">
-        <v>-5.78</v>
+      <c r="T7" s="70">
+        <v>-6.02</v>
       </c>
     </row>
     <row r="8">
@@ -8430,7 +8430,7 @@
       <c r="C8" t="str">
         <v>600828</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="83" t="str">
         <v>净买: 1425.83万</v>
       </c>
       <c r="E8">
@@ -8445,41 +8445,41 @@
       <c r="H8">
         <v>10.11</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="90">
         <v>0</v>
       </c>
       <c r="J8" s="87">
         <v>10.02</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="88">
         <v>7.31</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="80">
         <v>5.01</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="81">
         <v>10.65</v>
       </c>
-      <c r="N8" s="85">
+      <c r="N8" s="84">
         <v>5.43</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="85">
         <v>-5.01</v>
       </c>
       <c r="P8" s="86">
         <v>-10.02</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="82">
         <v>-12.73</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="91">
         <v>-11.69</v>
       </c>
       <c r="S8" s="89">
         <v>-10.65</v>
       </c>
-      <c r="T8" s="90">
-        <v>7.52</v>
+      <c r="T8" s="79">
+        <v>6.26</v>
       </c>
     </row>
     <row r="9">
@@ -8492,7 +8492,7 @@
       <c r="C9" t="str">
         <v>600828</v>
       </c>
-      <c r="D9" s="103" t="str">
+      <c r="D9" s="97" t="str">
         <v>净卖: -1514.63万</v>
       </c>
       <c r="E9">
@@ -8507,25 +8507,25 @@
       <c r="H9">
         <v>-0.21</v>
       </c>
-      <c r="I9" s="104">
+      <c r="I9" s="102">
         <v>10.25</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="93">
         <v>7.53</v>
       </c>
       <c r="K9" s="98">
         <v>5.23</v>
       </c>
-      <c r="L9" s="100">
+      <c r="L9" s="103">
         <v>10.88</v>
       </c>
-      <c r="M9" s="93">
+      <c r="M9" s="99">
         <v>5.65</v>
       </c>
-      <c r="N9" s="94">
+      <c r="N9" s="100">
         <v>-4.81</v>
       </c>
-      <c r="O9" s="99">
+      <c r="O9" s="94">
         <v>-9.83</v>
       </c>
       <c r="P9" s="95">
@@ -8537,11 +8537,11 @@
       <c r="R9" s="101">
         <v>-10.46</v>
       </c>
-      <c r="S9" s="102">
+      <c r="S9" s="104">
         <v>-12.34</v>
       </c>
-      <c r="T9" s="97">
-        <v>7.74</v>
+      <c r="T9" s="92">
+        <v>6.49</v>
       </c>
     </row>
     <row r="10">
@@ -8554,7 +8554,7 @@
       <c r="C10" t="str">
         <v>002909</v>
       </c>
-      <c r="D10" s="111" t="str">
+      <c r="D10" s="106" t="str">
         <v>净卖: -879.53万</v>
       </c>
       <c r="E10">
@@ -8569,41 +8569,41 @@
       <c r="H10">
         <v>-1.91</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="111">
         <v>-8.28</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="117">
         <v>-16.44</v>
       </c>
       <c r="K10" s="112">
         <v>-21.07</v>
       </c>
-      <c r="L10" s="110">
+      <c r="L10" s="113">
         <v>-21.8</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="105">
         <v>-23.39</v>
       </c>
-      <c r="N10" s="116">
+      <c r="N10" s="107">
         <v>-23.02</v>
       </c>
-      <c r="O10" s="113">
+      <c r="O10" s="108">
         <v>-22.66</v>
       </c>
       <c r="P10" s="114">
         <v>-23.87</v>
       </c>
-      <c r="Q10" s="117">
+      <c r="Q10" s="109">
         <v>-23.26</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="110">
         <v>-24.12</v>
       </c>
       <c r="S10" s="115">
         <v>-23.87</v>
       </c>
-      <c r="T10" s="108">
-        <v>-20.34</v>
+      <c r="T10" s="116">
+        <v>-19.73</v>
       </c>
     </row>
     <row r="11">
@@ -8631,19 +8631,19 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="127">
+      <c r="I11" s="118">
         <v>0</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="124">
         <v>-6.63</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="125">
         <v>-12.9</v>
       </c>
-      <c r="L11" s="123">
+      <c r="L11" s="130">
         <v>-12.16</v>
       </c>
-      <c r="M11" s="124">
+      <c r="M11" s="119">
         <v>-13.76</v>
       </c>
       <c r="N11" s="120">
@@ -8652,20 +8652,20 @@
       <c r="O11" s="121">
         <v>-10.63</v>
       </c>
-      <c r="P11" s="125">
+      <c r="P11" s="128">
         <v>-9.46</v>
       </c>
-      <c r="Q11" s="130">
+      <c r="Q11" s="122">
         <v>-10.44</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="126">
         <v>-10.01</v>
       </c>
-      <c r="S11" s="126">
+      <c r="S11" s="127">
         <v>-8.17</v>
       </c>
-      <c r="T11" s="128">
-        <v>-15.48</v>
+      <c r="T11" s="123">
+        <v>-15.29</v>
       </c>
     </row>
     <row r="12">
@@ -8693,28 +8693,28 @@
       <c r="H12">
         <v>10.05</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="135">
         <v>0</v>
       </c>
-      <c r="J12" s="135">
+      <c r="J12" s="136">
         <v>3.19</v>
       </c>
       <c r="K12" s="141">
         <v>6.23</v>
       </c>
-      <c r="L12" s="138">
+      <c r="L12" s="137">
         <v>16.81</v>
       </c>
       <c r="M12" s="142">
         <v>18.99</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="138">
         <v>30.87</v>
       </c>
-      <c r="O12" s="143">
+      <c r="O12" s="132">
         <v>43.91</v>
       </c>
-      <c r="P12" s="132">
+      <c r="P12" s="143">
         <v>42.17</v>
       </c>
       <c r="Q12" s="133">
@@ -8723,11 +8723,11 @@
       <c r="R12" s="134">
         <v>43.48</v>
       </c>
-      <c r="S12" s="136">
+      <c r="S12" s="131">
         <v>44.93</v>
       </c>
       <c r="T12" s="139">
-        <v>41.59</v>
+        <v>42.61</v>
       </c>
     </row>
     <row r="13">
@@ -8740,7 +8740,7 @@
       <c r="C13" t="str">
         <v>603776</v>
       </c>
-      <c r="D13" s="155" t="str">
+      <c r="D13" s="150" t="str">
         <v>净买: 1894.22万</v>
       </c>
       <c r="E13">
@@ -8755,41 +8755,41 @@
       <c r="H13">
         <v>10</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="155">
         <v>0</v>
       </c>
-      <c r="J13" s="156">
+      <c r="J13" s="151">
         <v>-9.72</v>
       </c>
       <c r="K13" s="147">
         <v>-10.95</v>
       </c>
-      <c r="L13" s="149">
+      <c r="L13" s="156">
         <v>-8.45</v>
       </c>
-      <c r="M13" s="150">
+      <c r="M13" s="152">
         <v>-7.04</v>
       </c>
-      <c r="N13" s="154">
+      <c r="N13" s="144">
         <v>-11.27</v>
       </c>
-      <c r="O13" s="151">
+      <c r="O13" s="148">
         <v>-2.41</v>
       </c>
-      <c r="P13" s="152">
+      <c r="P13" s="145">
         <v>2.36</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="149">
         <v>-2.64</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="153">
         <v>-2.32</v>
       </c>
-      <c r="S13" s="153">
+      <c r="S13" s="154">
         <v>-2.23</v>
       </c>
-      <c r="T13" s="145">
-        <v>-6.18</v>
+      <c r="T13" s="146">
+        <v>-11.36</v>
       </c>
     </row>
     <row r="14">
@@ -8817,41 +8817,41 @@
       <c r="H14">
         <v>-2.32</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="160">
         <v>-7.58</v>
       </c>
-      <c r="J14" s="165">
+      <c r="J14" s="161">
         <v>-8.84</v>
       </c>
-      <c r="K14" s="166">
+      <c r="K14" s="167">
         <v>-6.28</v>
       </c>
-      <c r="L14" s="160">
+      <c r="L14" s="163">
         <v>-4.84</v>
       </c>
-      <c r="M14" s="169">
+      <c r="M14" s="157">
         <v>-9.16</v>
       </c>
       <c r="N14" s="162">
         <v>-0.09</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="164">
         <v>4.79</v>
       </c>
-      <c r="P14" s="161">
+      <c r="P14" s="158">
         <v>-0.33</v>
       </c>
-      <c r="Q14" s="157">
+      <c r="Q14" s="165">
         <v>0</v>
       </c>
-      <c r="R14" s="158">
+      <c r="R14" s="166">
         <v>0.09</v>
       </c>
-      <c r="S14" s="167">
+      <c r="S14" s="168">
         <v>0</v>
       </c>
-      <c r="T14" s="164">
-        <v>-3.95</v>
+      <c r="T14" s="169">
+        <v>-9.26</v>
       </c>
     </row>
     <row r="15">
@@ -8864,7 +8864,7 @@
       <c r="C15" t="str">
         <v>001360</v>
       </c>
-      <c r="D15" s="170" t="str">
+      <c r="D15" s="177" t="str">
         <v>净买: 1803.24万</v>
       </c>
       <c r="E15">
@@ -8879,41 +8879,41 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="174">
         <v>0</v>
       </c>
-      <c r="J15" s="173">
+      <c r="J15" s="179">
         <v>10.01</v>
       </c>
-      <c r="K15" s="174">
+      <c r="K15" s="170">
         <v>-0.95</v>
       </c>
-      <c r="L15" s="178">
+      <c r="L15" s="171">
         <v>-10.85</v>
       </c>
-      <c r="M15" s="179">
+      <c r="M15" s="175">
         <v>-13.18</v>
       </c>
-      <c r="N15" s="180">
+      <c r="N15" s="176">
         <v>-14.29</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="180">
         <v>-15.25</v>
       </c>
-      <c r="P15" s="181">
+      <c r="P15" s="178">
         <v>-14.56</v>
       </c>
-      <c r="Q15" s="175">
+      <c r="Q15" s="181">
         <v>-16.52</v>
       </c>
-      <c r="R15" s="176">
+      <c r="R15" s="172">
         <v>-16.36</v>
       </c>
       <c r="S15" s="182">
         <v>-16.15</v>
       </c>
-      <c r="T15" s="177">
-        <v>9.79</v>
+      <c r="T15" s="173">
+        <v>9.16</v>
       </c>
     </row>
     <row r="16">
@@ -8926,7 +8926,7 @@
       <c r="C16" t="str">
         <v>601669</v>
       </c>
-      <c r="D16" s="183" t="str">
+      <c r="D16" s="187" t="str">
         <v>净买: 9396.35万</v>
       </c>
       <c r="E16">
@@ -8941,41 +8941,41 @@
       <c r="H16">
         <v>10.08</v>
       </c>
-      <c r="I16" s="190">
+      <c r="I16" s="193">
         <v>0</v>
       </c>
-      <c r="J16" s="184">
+      <c r="J16" s="191">
         <v>10.04</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="194">
         <v>6.65</v>
       </c>
-      <c r="L16" s="189">
+      <c r="L16" s="184">
         <v>3.84</v>
       </c>
-      <c r="M16" s="193">
+      <c r="M16" s="185">
         <v>5.76</v>
       </c>
-      <c r="N16" s="191">
+      <c r="N16" s="192">
         <v>0.44</v>
       </c>
-      <c r="O16" s="194">
+      <c r="O16" s="188">
         <v>0.89</v>
       </c>
-      <c r="P16" s="185">
+      <c r="P16" s="195">
         <v>-3.69</v>
       </c>
-      <c r="Q16" s="186">
+      <c r="Q16" s="183">
         <v>-4.58</v>
       </c>
-      <c r="R16" s="192">
+      <c r="R16" s="189">
         <v>-5.17</v>
       </c>
-      <c r="S16" s="195">
+      <c r="S16" s="186">
         <v>-6.5</v>
       </c>
-      <c r="T16" s="187">
-        <v>-16.1</v>
+      <c r="T16" s="190">
+        <v>-16.99</v>
       </c>
     </row>
     <row r="17">
@@ -8988,7 +8988,7 @@
       <c r="C17" t="str">
         <v>001360</v>
       </c>
-      <c r="D17" s="207" t="str">
+      <c r="D17" s="197" t="str">
         <v>净卖: -1800.16万</v>
       </c>
       <c r="E17">
@@ -9003,41 +9003,41 @@
       <c r="H17">
         <v>0.1</v>
       </c>
-      <c r="I17" s="196">
+      <c r="I17" s="198">
         <v>-10.05</v>
       </c>
-      <c r="J17" s="208">
+      <c r="J17" s="199">
         <v>-19.04</v>
       </c>
-      <c r="K17" s="202">
+      <c r="K17" s="206">
         <v>-21.15</v>
       </c>
-      <c r="L17" s="203">
+      <c r="L17" s="207">
         <v>-22.16</v>
       </c>
-      <c r="M17" s="204">
+      <c r="M17" s="200">
         <v>-23.03</v>
       </c>
-      <c r="N17" s="198">
+      <c r="N17" s="203">
         <v>-22.4</v>
       </c>
-      <c r="O17" s="199">
+      <c r="O17" s="204">
         <v>-24.18</v>
       </c>
-      <c r="P17" s="205">
+      <c r="P17" s="201">
         <v>-24.04</v>
       </c>
-      <c r="Q17" s="197">
+      <c r="Q17" s="202">
         <v>-23.85</v>
       </c>
-      <c r="R17" s="206">
+      <c r="R17" s="208">
         <v>-24.28</v>
       </c>
-      <c r="S17" s="200">
+      <c r="S17" s="196">
         <v>-24.47</v>
       </c>
-      <c r="T17" s="201">
-        <v>-0.29</v>
+      <c r="T17" s="205">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="18">
@@ -9050,7 +9050,7 @@
       <c r="C18" t="str">
         <v>001360</v>
       </c>
-      <c r="D18" s="216" t="str">
+      <c r="D18" s="213" t="str">
         <v>净卖: -1799.99万</v>
       </c>
       <c r="E18">
@@ -9065,41 +9065,41 @@
       <c r="H18">
         <v>-9.14</v>
       </c>
-      <c r="I18" s="212">
+      <c r="I18" s="209">
         <v>-0.94</v>
       </c>
-      <c r="J18" s="217">
+      <c r="J18" s="216">
         <v>-3.53</v>
       </c>
-      <c r="K18" s="213">
+      <c r="K18" s="210">
         <v>-4.76</v>
       </c>
-      <c r="L18" s="214">
+      <c r="L18" s="211">
         <v>-5.82</v>
       </c>
-      <c r="M18" s="209">
+      <c r="M18" s="219">
         <v>-5.06</v>
       </c>
-      <c r="N18" s="219">
+      <c r="N18" s="214">
         <v>-7.24</v>
       </c>
-      <c r="O18" s="220">
+      <c r="O18" s="215">
         <v>-7.06</v>
       </c>
-      <c r="P18" s="221">
+      <c r="P18" s="220">
         <v>-6.82</v>
       </c>
-      <c r="Q18" s="215">
+      <c r="Q18" s="221">
         <v>-7.35</v>
       </c>
-      <c r="R18" s="210">
+      <c r="R18" s="217">
         <v>-7.59</v>
       </c>
-      <c r="S18" s="211">
+      <c r="S18" s="218">
         <v>-6.59</v>
       </c>
-      <c r="T18" s="218">
-        <v>22</v>
+      <c r="T18" s="212">
+        <v>21.29</v>
       </c>
     </row>
     <row r="19">
@@ -9112,7 +9112,7 @@
       <c r="C19" t="str">
         <v>300620</v>
       </c>
-      <c r="D19" s="223" t="str">
+      <c r="D19" s="231" t="str">
         <v>净买: 1215.21万</v>
       </c>
       <c r="E19">
@@ -9127,41 +9127,41 @@
       <c r="H19">
         <v>19.99</v>
       </c>
-      <c r="I19" s="234">
+      <c r="I19" s="227">
         <v>0</v>
       </c>
-      <c r="J19" s="224">
+      <c r="J19" s="228">
         <v>20.01</v>
       </c>
-      <c r="K19" s="231">
+      <c r="K19" s="223">
         <v>21.14</v>
       </c>
-      <c r="L19" s="226">
+      <c r="L19" s="229">
         <v>24.09</v>
       </c>
-      <c r="M19" s="227">
+      <c r="M19" s="232">
         <v>46.79</v>
       </c>
-      <c r="N19" s="228">
+      <c r="N19" s="224">
         <v>50.73</v>
       </c>
-      <c r="O19" s="229">
+      <c r="O19" s="233">
         <v>40.57</v>
       </c>
-      <c r="P19" s="232">
+      <c r="P19" s="234">
         <v>31.96</v>
       </c>
-      <c r="Q19" s="230">
+      <c r="Q19" s="225">
         <v>34.41</v>
       </c>
-      <c r="R19" s="225">
+      <c r="R19" s="230">
         <v>39.6</v>
       </c>
-      <c r="S19" s="222">
+      <c r="S19" s="226">
         <v>34.69</v>
       </c>
-      <c r="T19" s="233">
-        <v>262.74</v>
+      <c r="T19" s="222">
+        <v>261.23</v>
       </c>
     </row>
     <row r="20">
@@ -9189,41 +9189,41 @@
       <c r="H20">
         <v>3.85</v>
       </c>
-      <c r="I20" s="239">
+      <c r="I20" s="243">
         <v>5.93</v>
       </c>
-      <c r="J20" s="243">
+      <c r="J20" s="247">
         <v>1.38</v>
       </c>
-      <c r="K20" s="244">
+      <c r="K20" s="239">
         <v>-1.17</v>
       </c>
       <c r="L20" s="240">
         <v>-10.91</v>
       </c>
-      <c r="M20" s="246">
+      <c r="M20" s="241">
         <v>-11.76</v>
       </c>
-      <c r="N20" s="241">
+      <c r="N20" s="235">
         <v>-12.39</v>
       </c>
-      <c r="O20" s="236">
+      <c r="O20" s="242">
         <v>-9.96</v>
       </c>
-      <c r="P20" s="237">
+      <c r="P20" s="244">
         <v>-15.15</v>
       </c>
       <c r="Q20" s="245">
         <v>-17.9</v>
       </c>
-      <c r="R20" s="247">
+      <c r="R20" s="246">
         <v>-19.39</v>
       </c>
-      <c r="S20" s="242">
+      <c r="S20" s="236">
         <v>-18.11</v>
       </c>
-      <c r="T20" s="235">
-        <v>-19.92</v>
+      <c r="T20" s="237">
+        <v>-22.46</v>
       </c>
     </row>
     <row r="21">
@@ -9236,7 +9236,7 @@
       <c r="C21" t="str">
         <v>301517</v>
       </c>
-      <c r="D21" s="256" t="str">
+      <c r="D21" s="253" t="str">
         <v>净买: 1391.15万</v>
       </c>
       <c r="E21">
@@ -9251,41 +9251,41 @@
       <c r="H21">
         <v>20</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="254">
         <v>-14.18</v>
       </c>
-      <c r="J21" s="249">
+      <c r="J21" s="257">
         <v>-19.79</v>
       </c>
-      <c r="K21" s="250">
+      <c r="K21" s="255">
         <v>-18.67</v>
       </c>
-      <c r="L21" s="257">
+      <c r="L21" s="259">
         <v>-21.09</v>
       </c>
-      <c r="M21" s="258">
+      <c r="M21" s="249">
         <v>-22.21</v>
       </c>
-      <c r="N21" s="251">
+      <c r="N21" s="260">
         <v>-18.54</v>
       </c>
-      <c r="O21" s="252">
+      <c r="O21" s="250">
         <v>-22.58</v>
       </c>
-      <c r="P21" s="259">
+      <c r="P21" s="251">
         <v>-27.04</v>
       </c>
-      <c r="Q21" s="253">
+      <c r="Q21" s="256">
         <v>-25.09</v>
       </c>
-      <c r="R21" s="254">
+      <c r="R21" s="252">
         <v>-21.88</v>
       </c>
-      <c r="S21" s="255">
+      <c r="S21" s="258">
         <v>-25.85</v>
       </c>
-      <c r="T21" s="260">
-        <v>9.3</v>
+      <c r="T21" s="248">
+        <v>5.81</v>
       </c>
     </row>
     <row r="22">
@@ -9298,7 +9298,7 @@
       <c r="C22" t="str">
         <v>002547</v>
       </c>
-      <c r="D22" s="268" t="str">
+      <c r="D22" s="266" t="str">
         <v>净买: 4862.70万</v>
       </c>
       <c r="E22">
@@ -9313,41 +9313,41 @@
       <c r="H22">
         <v>10.1</v>
       </c>
-      <c r="I22" s="271">
+      <c r="I22" s="264">
         <v>0</v>
       </c>
-      <c r="J22" s="273">
+      <c r="J22" s="267">
         <v>7.01</v>
       </c>
-      <c r="K22" s="261">
+      <c r="K22" s="262">
         <v>0.36</v>
       </c>
-      <c r="L22" s="266">
+      <c r="L22" s="268">
         <v>4.68</v>
       </c>
-      <c r="M22" s="267">
+      <c r="M22" s="269">
         <v>15.11</v>
       </c>
-      <c r="N22" s="262">
+      <c r="N22" s="270">
         <v>21.76</v>
       </c>
-      <c r="O22" s="263">
+      <c r="O22" s="271">
         <v>22.66</v>
       </c>
-      <c r="P22" s="269">
+      <c r="P22" s="263">
         <v>17.81</v>
       </c>
-      <c r="Q22" s="270">
+      <c r="Q22" s="272">
         <v>9.17</v>
       </c>
-      <c r="R22" s="264">
+      <c r="R22" s="265">
         <v>12.59</v>
       </c>
-      <c r="S22" s="265">
+      <c r="S22" s="273">
         <v>7.01</v>
       </c>
-      <c r="T22" s="272">
-        <v>-43.35</v>
+      <c r="T22" s="261">
+        <v>-42.81</v>
       </c>
     </row>
     <row r="23">
@@ -9360,7 +9360,7 @@
       <c r="C23" t="str">
         <v>002547</v>
       </c>
-      <c r="D23" s="278" t="str">
+      <c r="D23" s="286" t="str">
         <v>净卖: -5175.09万</v>
       </c>
       <c r="E23">
@@ -9375,41 +9375,41 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23" s="283">
+      <c r="I23" s="282">
         <v>7.01</v>
       </c>
-      <c r="J23" s="284">
+      <c r="J23" s="283">
         <v>0.36</v>
       </c>
-      <c r="K23" s="286">
+      <c r="K23" s="279">
         <v>4.68</v>
       </c>
-      <c r="L23" s="279">
+      <c r="L23" s="274">
         <v>15.11</v>
       </c>
-      <c r="M23" s="280">
+      <c r="M23" s="285">
         <v>21.76</v>
       </c>
-      <c r="N23" s="281">
+      <c r="N23" s="280">
         <v>22.66</v>
       </c>
-      <c r="O23" s="285">
+      <c r="O23" s="275">
         <v>17.81</v>
       </c>
-      <c r="P23" s="274">
+      <c r="P23" s="284">
         <v>9.17</v>
       </c>
-      <c r="Q23" s="282">
+      <c r="Q23" s="276">
         <v>12.59</v>
       </c>
-      <c r="R23" s="275">
+      <c r="R23" s="277">
         <v>7.01</v>
       </c>
-      <c r="S23" s="276">
+      <c r="S23" s="281">
         <v>8.09</v>
       </c>
-      <c r="T23" s="277">
-        <v>-43.35</v>
+      <c r="T23" s="278">
+        <v>-42.81</v>
       </c>
     </row>
     <row r="24">
@@ -9422,7 +9422,7 @@
       <c r="C24" t="str">
         <v>920020</v>
       </c>
-      <c r="D24" s="292" t="str">
+      <c r="D24" s="298" t="str">
         <v>净卖: -668.61万</v>
       </c>
       <c r="E24">
@@ -9437,41 +9437,41 @@
       <c r="H24">
         <v>-9.66</v>
       </c>
-      <c r="I24" s="293">
+      <c r="I24" s="299">
         <v>14.02</v>
       </c>
-      <c r="J24" s="297">
+      <c r="J24" s="287">
         <v>2.92</v>
       </c>
-      <c r="K24" s="288">
+      <c r="K24" s="295">
         <v>1.38</v>
       </c>
-      <c r="L24" s="298">
+      <c r="L24" s="296">
         <v>0.51</v>
       </c>
-      <c r="M24" s="294">
+      <c r="M24" s="289">
         <v>-0.82</v>
       </c>
-      <c r="N24" s="299">
+      <c r="N24" s="290">
         <v>-0.87</v>
       </c>
-      <c r="O24" s="287">
+      <c r="O24" s="291">
         <v>0.87</v>
       </c>
-      <c r="P24" s="295">
+      <c r="P24" s="292">
         <v>-2.4</v>
       </c>
-      <c r="Q24" s="289">
+      <c r="Q24" s="293">
         <v>-5.17</v>
       </c>
-      <c r="R24" s="296">
+      <c r="R24" s="288">
         <v>-4.76</v>
       </c>
-      <c r="S24" s="291">
+      <c r="S24" s="294">
         <v>-4.35</v>
       </c>
-      <c r="T24" s="290">
-        <v>-20.72</v>
+      <c r="T24" s="297">
+        <v>-20.61</v>
       </c>
     </row>
     <row r="25">
@@ -9484,7 +9484,7 @@
       <c r="C25" t="str">
         <v>605178</v>
       </c>
-      <c r="D25" s="307" t="str">
+      <c r="D25" s="300" t="str">
         <v>净买: 3874.18万</v>
       </c>
       <c r="E25">
@@ -9499,41 +9499,41 @@
       <c r="H25">
         <v>10</v>
       </c>
-      <c r="I25" s="308">
+      <c r="I25" s="306">
         <v>0</v>
       </c>
-      <c r="J25" s="301">
+      <c r="J25" s="307">
         <v>10</v>
       </c>
-      <c r="K25" s="309">
+      <c r="K25" s="301">
         <v>0.58</v>
       </c>
       <c r="L25" s="302">
         <v>4.74</v>
       </c>
-      <c r="M25" s="312">
+      <c r="M25" s="310">
         <v>13.42</v>
       </c>
       <c r="N25" s="303">
         <v>19.72</v>
       </c>
-      <c r="O25" s="310">
+      <c r="O25" s="308">
         <v>26.01</v>
       </c>
-      <c r="P25" s="311">
+      <c r="P25" s="304">
         <v>16.89</v>
       </c>
-      <c r="Q25" s="305">
+      <c r="Q25" s="309">
         <v>6.52</v>
       </c>
-      <c r="R25" s="300">
+      <c r="R25" s="311">
         <v>10.9</v>
       </c>
-      <c r="S25" s="304">
+      <c r="S25" s="305">
         <v>12.81</v>
       </c>
-      <c r="T25" s="306">
-        <v>11.77</v>
+      <c r="T25" s="312">
+        <v>7.67</v>
       </c>
     </row>
     <row r="26">
@@ -9546,7 +9546,7 @@
       <c r="C26" t="str">
         <v>000407</v>
       </c>
-      <c r="D26" s="319" t="str">
+      <c r="D26" s="324" t="str">
         <v>净买: 788.81万</v>
       </c>
       <c r="E26">
@@ -9561,41 +9561,41 @@
       <c r="H26">
         <v>10.1</v>
       </c>
-      <c r="I26" s="320">
+      <c r="I26" s="325">
         <v>0</v>
       </c>
-      <c r="J26" s="323">
+      <c r="J26" s="313">
         <v>10.04</v>
       </c>
-      <c r="K26" s="321">
+      <c r="K26" s="314">
         <v>20.96</v>
       </c>
-      <c r="L26" s="316">
+      <c r="L26" s="317">
         <v>32.97</v>
       </c>
-      <c r="M26" s="322">
+      <c r="M26" s="320">
         <v>46.29</v>
       </c>
-      <c r="N26" s="317">
+      <c r="N26" s="315">
         <v>31.66</v>
       </c>
-      <c r="O26" s="324">
+      <c r="O26" s="323">
         <v>30.35</v>
       </c>
-      <c r="P26" s="325">
+      <c r="P26" s="321">
         <v>17.25</v>
       </c>
-      <c r="Q26" s="314">
+      <c r="Q26" s="322">
         <v>5.46</v>
       </c>
-      <c r="R26" s="313">
+      <c r="R26" s="318">
         <v>5.9</v>
       </c>
-      <c r="S26" s="318">
+      <c r="S26" s="316">
         <v>12.45</v>
       </c>
-      <c r="T26" s="315">
-        <v>3.28</v>
+      <c r="T26" s="319">
+        <v>4.59</v>
       </c>
     </row>
     <row r="27">
@@ -9608,7 +9608,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="330" t="str">
+      <c r="D27" s="331" t="str">
         <v>净买: 3123.85万</v>
       </c>
       <c r="E27">
@@ -9623,41 +9623,41 @@
       <c r="H27">
         <v>9.96</v>
       </c>
-      <c r="I27" s="334">
+      <c r="I27" s="326">
         <v>0</v>
       </c>
-      <c r="J27" s="336">
+      <c r="J27" s="335">
         <v>-9.95</v>
       </c>
-      <c r="K27" s="331">
+      <c r="K27" s="337">
         <v>-19.01</v>
       </c>
-      <c r="L27" s="332">
+      <c r="L27" s="338">
         <v>-27.04</v>
       </c>
-      <c r="M27" s="337">
+      <c r="M27" s="336">
         <v>-30.61</v>
       </c>
-      <c r="N27" s="335">
+      <c r="N27" s="332">
         <v>-28.7</v>
       </c>
-      <c r="O27" s="338">
+      <c r="O27" s="333">
         <v>-31.89</v>
       </c>
-      <c r="P27" s="326">
+      <c r="P27" s="327">
         <v>-31.63</v>
       </c>
       <c r="Q27" s="328">
         <v>-28.95</v>
       </c>
-      <c r="R27" s="333">
+      <c r="R27" s="329">
         <v>-26.53</v>
       </c>
-      <c r="S27" s="329">
+      <c r="S27" s="330">
         <v>-24.49</v>
       </c>
-      <c r="T27" s="327">
-        <v>-26.4</v>
+      <c r="T27" s="334">
+        <v>-26.28</v>
       </c>
     </row>
     <row r="28">
@@ -9670,7 +9670,7 @@
       <c r="C28" t="str">
         <v>300094</v>
       </c>
-      <c r="D28" s="346" t="str">
+      <c r="D28" s="341" t="str">
         <v>净卖: -3846.51万</v>
       </c>
       <c r="E28">
@@ -9685,41 +9685,41 @@
       <c r="H28">
         <v>0.37</v>
       </c>
-      <c r="I28" s="344">
+      <c r="I28" s="346">
         <v>-11.85</v>
       </c>
-      <c r="J28" s="347">
+      <c r="J28" s="342">
         <v>-12.41</v>
       </c>
-      <c r="K28" s="339">
+      <c r="K28" s="347">
         <v>-8.33</v>
       </c>
-      <c r="L28" s="340">
+      <c r="L28" s="343">
         <v>-17.96</v>
       </c>
-      <c r="M28" s="341">
+      <c r="M28" s="344">
         <v>-23.89</v>
       </c>
-      <c r="N28" s="342">
+      <c r="N28" s="349">
         <v>-22.96</v>
       </c>
       <c r="O28" s="348">
         <v>-24.26</v>
       </c>
-      <c r="P28" s="343">
+      <c r="P28" s="350">
         <v>-23.15</v>
       </c>
-      <c r="Q28" s="350">
+      <c r="Q28" s="345">
         <v>-21.48</v>
       </c>
-      <c r="R28" s="349">
+      <c r="R28" s="351">
         <v>-21.85</v>
       </c>
-      <c r="S28" s="351">
+      <c r="S28" s="339">
         <v>-27.78</v>
       </c>
-      <c r="T28" s="345">
-        <v>-43.89</v>
+      <c r="T28" s="340">
+        <v>-45.37</v>
       </c>
     </row>
     <row r="29">
@@ -9732,7 +9732,7 @@
       <c r="C29" t="str">
         <v>002682</v>
       </c>
-      <c r="D29" s="363" t="str">
+      <c r="D29" s="360" t="str">
         <v>净卖: -2565.97万</v>
       </c>
       <c r="E29">
@@ -9747,41 +9747,41 @@
       <c r="H29">
         <v>-6.94</v>
       </c>
-      <c r="I29" s="360">
+      <c r="I29" s="357">
         <v>-3.35</v>
       </c>
-      <c r="J29" s="361">
+      <c r="J29" s="364">
         <v>-12.94</v>
       </c>
-      <c r="K29" s="354">
+      <c r="K29" s="352">
         <v>-17.2</v>
       </c>
-      <c r="L29" s="355">
+      <c r="L29" s="353">
         <v>-14.92</v>
       </c>
-      <c r="M29" s="358">
+      <c r="M29" s="361">
         <v>-18.72</v>
       </c>
-      <c r="N29" s="364">
+      <c r="N29" s="354">
         <v>-18.42</v>
       </c>
-      <c r="O29" s="362">
+      <c r="O29" s="355">
         <v>-15.22</v>
       </c>
-      <c r="P29" s="352">
+      <c r="P29" s="362">
         <v>-12.33</v>
       </c>
-      <c r="Q29" s="353">
+      <c r="Q29" s="358">
         <v>-9.89</v>
       </c>
-      <c r="R29" s="356">
+      <c r="R29" s="363">
         <v>-0.91</v>
       </c>
-      <c r="S29" s="357">
+      <c r="S29" s="359">
         <v>8.98</v>
       </c>
-      <c r="T29" s="359">
-        <v>-12.18</v>
+      <c r="T29" s="356">
+        <v>-12.02</v>
       </c>
     </row>
     <row r="30">
@@ -9794,7 +9794,7 @@
       <c r="C30" t="str">
         <v>603069</v>
       </c>
-      <c r="D30" s="372" t="str">
+      <c r="D30" s="369" t="str">
         <v>净买: 2184.48万</v>
       </c>
       <c r="E30">
@@ -9809,41 +9809,41 @@
       <c r="H30">
         <v>10.02</v>
       </c>
-      <c r="I30" s="377">
+      <c r="I30" s="373">
         <v>0</v>
       </c>
-      <c r="J30" s="374">
+      <c r="J30" s="365">
         <v>1.25</v>
       </c>
-      <c r="K30" s="375">
+      <c r="K30" s="372">
         <v>-4.36</v>
       </c>
-      <c r="L30" s="365">
+      <c r="L30" s="366">
         <v>5.19</v>
       </c>
-      <c r="M30" s="368">
+      <c r="M30" s="374">
         <v>-1.42</v>
       </c>
-      <c r="N30" s="366">
+      <c r="N30" s="375">
         <v>-5.96</v>
       </c>
       <c r="O30" s="376">
         <v>-5.99</v>
       </c>
-      <c r="P30" s="369">
+      <c r="P30" s="377">
         <v>-13.57</v>
       </c>
-      <c r="Q30" s="373">
+      <c r="Q30" s="367">
         <v>-13.64</v>
       </c>
-      <c r="R30" s="367">
+      <c r="R30" s="370">
         <v>-14.16</v>
       </c>
-      <c r="S30" s="370">
+      <c r="S30" s="368">
         <v>-15.27</v>
       </c>
       <c r="T30" s="371">
-        <v>-41.79</v>
+        <v>-42.42</v>
       </c>
     </row>
     <row r="31">
@@ -9856,7 +9856,7 @@
       <c r="C31" t="str">
         <v>002009</v>
       </c>
-      <c r="D31" s="378" t="str">
+      <c r="D31" s="384" t="str">
         <v>净买: 3463.54万</v>
       </c>
       <c r="E31">
@@ -9871,41 +9871,41 @@
       <c r="H31">
         <v>10</v>
       </c>
-      <c r="I31" s="382">
+      <c r="I31" s="385">
         <v>0</v>
       </c>
-      <c r="J31" s="389">
+      <c r="J31" s="386">
         <v>10.02</v>
       </c>
-      <c r="K31" s="383">
+      <c r="K31" s="388">
         <v>21.02</v>
       </c>
-      <c r="L31" s="386">
+      <c r="L31" s="389">
         <v>16.84</v>
       </c>
-      <c r="M31" s="387">
+      <c r="M31" s="390">
         <v>14.72</v>
       </c>
-      <c r="N31" s="388">
+      <c r="N31" s="378">
         <v>8.01</v>
       </c>
-      <c r="O31" s="390">
+      <c r="O31" s="379">
         <v>12.24</v>
       </c>
-      <c r="P31" s="379">
+      <c r="P31" s="382">
         <v>12.65</v>
       </c>
-      <c r="Q31" s="380">
+      <c r="Q31" s="383">
         <v>15.19</v>
       </c>
-      <c r="R31" s="384">
+      <c r="R31" s="380">
         <v>18.85</v>
       </c>
-      <c r="S31" s="385">
+      <c r="S31" s="381">
         <v>11.93</v>
       </c>
-      <c r="T31" s="381">
-        <v>22.42</v>
+      <c r="T31" s="387">
+        <v>16.43</v>
       </c>
     </row>
     <row r="32">
@@ -9918,7 +9918,7 @@
       <c r="C32" t="str">
         <v>002009</v>
       </c>
-      <c r="D32" s="401" t="str">
+      <c r="D32" s="399" t="str">
         <v>净卖: -4207.08万</v>
       </c>
       <c r="E32">
@@ -9933,41 +9933,41 @@
       <c r="H32">
         <v>9.92</v>
       </c>
-      <c r="I32" s="396">
+      <c r="I32" s="400">
         <v>0.09</v>
       </c>
-      <c r="J32" s="397">
+      <c r="J32" s="391">
         <v>10.1</v>
       </c>
-      <c r="K32" s="391">
+      <c r="K32" s="398">
         <v>6.3</v>
       </c>
       <c r="L32" s="392">
         <v>4.37</v>
       </c>
-      <c r="M32" s="393">
+      <c r="M32" s="396">
         <v>-1.74</v>
       </c>
-      <c r="N32" s="394">
+      <c r="N32" s="401">
         <v>2.11</v>
       </c>
-      <c r="O32" s="398">
+      <c r="O32" s="402">
         <v>2.49</v>
       </c>
-      <c r="P32" s="399">
+      <c r="P32" s="393">
         <v>4.79</v>
       </c>
-      <c r="Q32" s="400">
+      <c r="Q32" s="397">
         <v>8.13</v>
       </c>
-      <c r="R32" s="395">
+      <c r="R32" s="394">
         <v>1.83</v>
       </c>
-      <c r="S32" s="402">
+      <c r="S32" s="395">
         <v>2.63</v>
       </c>
       <c r="T32" s="403">
-        <v>11.37</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="33">
@@ -9980,7 +9980,7 @@
       <c r="C33" t="str">
         <v>002009</v>
       </c>
-      <c r="D33" s="415" t="str">
+      <c r="D33" s="407" t="str">
         <v>净卖: -4209.56万</v>
       </c>
       <c r="E33">
@@ -9995,41 +9995,41 @@
       <c r="H33">
         <v>2.21</v>
       </c>
-      <c r="I33" s="409">
+      <c r="I33" s="408">
         <v>7.63</v>
       </c>
-      <c r="J33" s="412">
+      <c r="J33" s="411">
         <v>3.9</v>
       </c>
-      <c r="K33" s="416">
+      <c r="K33" s="412">
         <v>2.02</v>
       </c>
-      <c r="L33" s="404">
+      <c r="L33" s="414">
         <v>-3.95</v>
       </c>
-      <c r="M33" s="405">
+      <c r="M33" s="415">
         <v>-0.18</v>
       </c>
-      <c r="N33" s="410">
+      <c r="N33" s="409">
         <v>0.18</v>
       </c>
-      <c r="O33" s="411">
+      <c r="O33" s="405">
         <v>2.43</v>
       </c>
-      <c r="P33" s="406">
+      <c r="P33" s="413">
         <v>5.7</v>
       </c>
-      <c r="Q33" s="408">
+      <c r="Q33" s="406">
         <v>-0.46</v>
       </c>
-      <c r="R33" s="413">
+      <c r="R33" s="416">
         <v>0.32</v>
       </c>
-      <c r="S33" s="407">
+      <c r="S33" s="404">
         <v>-1.52</v>
       </c>
-      <c r="T33" s="414">
-        <v>8.87</v>
+      <c r="T33" s="410">
+        <v>3.54</v>
       </c>
     </row>
     <row r="34">
@@ -10042,7 +10042,7 @@
       <c r="C34" t="str">
         <v>002969</v>
       </c>
-      <c r="D34" s="423" t="str">
+      <c r="D34" s="417" t="str">
         <v>净卖: -2752.13万</v>
       </c>
       <c r="E34">
@@ -10057,41 +10057,41 @@
       <c r="H34">
         <v>0.55</v>
       </c>
-      <c r="I34" s="419">
+      <c r="I34" s="424">
         <v>7.62</v>
       </c>
-      <c r="J34" s="420">
+      <c r="J34" s="425">
         <v>18.38</v>
       </c>
-      <c r="K34" s="424">
+      <c r="K34" s="418">
         <v>30.24</v>
       </c>
-      <c r="L34" s="421">
+      <c r="L34" s="419">
         <v>37.86</v>
       </c>
-      <c r="M34" s="422">
+      <c r="M34" s="420">
         <v>51.69</v>
       </c>
-      <c r="N34" s="425">
+      <c r="N34" s="423">
         <v>36.53</v>
       </c>
-      <c r="O34" s="426">
+      <c r="O34" s="421">
         <v>22.86</v>
       </c>
-      <c r="P34" s="427">
+      <c r="P34" s="426">
         <v>35.11</v>
       </c>
-      <c r="Q34" s="428">
+      <c r="Q34" s="422">
         <v>48.63</v>
       </c>
-      <c r="R34" s="429">
+      <c r="R34" s="427">
         <v>52.47</v>
       </c>
-      <c r="S34" s="417">
+      <c r="S34" s="428">
         <v>67.71</v>
       </c>
-      <c r="T34" s="418">
-        <v>70.38</v>
+      <c r="T34" s="429">
+        <v>62.22</v>
       </c>
     </row>
     <row r="35">
@@ -10104,7 +10104,7 @@
       <c r="C35" t="str">
         <v>600683</v>
       </c>
-      <c r="D35" s="440" t="str">
+      <c r="D35" s="433" t="str">
         <v>净买: 819.30万</v>
       </c>
       <c r="E35">
@@ -10119,41 +10119,41 @@
       <c r="H35">
         <v>10.1</v>
       </c>
-      <c r="I35" s="441">
+      <c r="I35" s="438">
         <v>0</v>
       </c>
       <c r="J35" s="439">
         <v>10.09</v>
       </c>
-      <c r="K35" s="442">
+      <c r="K35" s="440">
         <v>21.1</v>
       </c>
-      <c r="L35" s="433">
+      <c r="L35" s="442">
         <v>11.01</v>
       </c>
-      <c r="M35" s="430">
+      <c r="M35" s="434">
         <v>22.2</v>
       </c>
-      <c r="N35" s="434">
+      <c r="N35" s="435">
         <v>22.57</v>
       </c>
       <c r="O35" s="436">
         <v>32.29</v>
       </c>
-      <c r="P35" s="435">
+      <c r="P35" s="430">
         <v>27.16</v>
       </c>
-      <c r="Q35" s="431">
+      <c r="Q35" s="437">
         <v>23.12</v>
       </c>
-      <c r="R35" s="437">
+      <c r="R35" s="431">
         <v>30.46</v>
       </c>
-      <c r="S35" s="438">
+      <c r="S35" s="441">
         <v>37.06</v>
       </c>
       <c r="T35" s="432">
-        <v>148.81</v>
+        <v>146.61</v>
       </c>
     </row>
     <row r="36">
@@ -10166,7 +10166,7 @@
       <c r="C36" t="str">
         <v>002056</v>
       </c>
-      <c r="D36" s="450" t="str">
+      <c r="D36" s="447" t="str">
         <v>净卖: -2838.92万</v>
       </c>
       <c r="E36">
@@ -10181,41 +10181,41 @@
       <c r="H36">
         <v>1.28</v>
       </c>
-      <c r="I36" s="451">
+      <c r="I36" s="448">
         <v>8.62</v>
       </c>
-      <c r="J36" s="452">
+      <c r="J36" s="454">
         <v>-0.42</v>
       </c>
-      <c r="K36" s="453">
+      <c r="K36" s="449">
         <v>-4.25</v>
       </c>
-      <c r="L36" s="444">
+      <c r="L36" s="455">
         <v>-5.84</v>
       </c>
-      <c r="M36" s="454">
+      <c r="M36" s="450">
         <v>-8.66</v>
       </c>
-      <c r="N36" s="448">
+      <c r="N36" s="451">
         <v>-6.43</v>
       </c>
-      <c r="O36" s="445">
+      <c r="O36" s="452">
         <v>-9.21</v>
       </c>
-      <c r="P36" s="446">
+      <c r="P36" s="443">
         <v>-9.21</v>
       </c>
-      <c r="Q36" s="447">
+      <c r="Q36" s="444">
         <v>-7.78</v>
       </c>
-      <c r="R36" s="449">
+      <c r="R36" s="445">
         <v>-9.46</v>
       </c>
-      <c r="S36" s="455">
+      <c r="S36" s="446">
         <v>-9.92</v>
       </c>
-      <c r="T36" s="443">
-        <v>-21.06</v>
+      <c r="T36" s="453">
+        <v>-22.53</v>
       </c>
     </row>
     <row r="37">
@@ -10277,40 +10277,40 @@
       <c r="F38" t="str"/>
       <c r="G38" t="str"/>
       <c r="H38" t="str"/>
-      <c r="I38" s="464">
+      <c r="I38" s="463">
         <v>31.43</v>
       </c>
-      <c r="J38" s="462">
+      <c r="J38" s="464">
         <v>62.86</v>
       </c>
-      <c r="K38" s="465">
+      <c r="K38" s="458">
         <v>54.29</v>
       </c>
-      <c r="L38" s="466">
+      <c r="L38" s="465">
         <v>54.29</v>
       </c>
-      <c r="M38" s="459">
+      <c r="M38" s="466">
         <v>42.86</v>
       </c>
-      <c r="N38" s="457">
+      <c r="N38" s="459">
         <v>42.86</v>
       </c>
       <c r="O38" s="467">
         <v>48.57</v>
       </c>
-      <c r="P38" s="463">
+      <c r="P38" s="456">
         <v>37.14</v>
       </c>
-      <c r="Q38" s="458">
+      <c r="Q38" s="460">
         <v>31.43</v>
       </c>
-      <c r="R38" s="460">
+      <c r="R38" s="461">
         <v>34.29</v>
       </c>
-      <c r="S38" s="461">
+      <c r="S38" s="457">
         <v>31.43</v>
       </c>
-      <c r="T38" s="456">
+      <c r="T38" s="462">
         <v>45.71</v>
       </c>
     </row>
@@ -10325,41 +10325,41 @@
       <c r="F39" t="str"/>
       <c r="G39" t="str"/>
       <c r="H39" t="str"/>
-      <c r="I39" s="470">
+      <c r="I39" s="468">
         <v>0.72</v>
       </c>
-      <c r="J39" s="477">
+      <c r="J39" s="469">
         <v>1.7</v>
       </c>
-      <c r="K39" s="472">
+      <c r="K39" s="478">
         <v>1.83</v>
       </c>
-      <c r="L39" s="478">
+      <c r="L39" s="476">
         <v>1.8</v>
       </c>
-      <c r="M39" s="479">
+      <c r="M39" s="474">
         <v>1.64</v>
       </c>
-      <c r="N39" s="475">
+      <c r="N39" s="470">
         <v>0.36</v>
       </c>
-      <c r="O39" s="476">
+      <c r="O39" s="471">
         <v>0.46</v>
       </c>
-      <c r="P39" s="468">
+      <c r="P39" s="477">
         <v>-2.04</v>
       </c>
-      <c r="Q39" s="471">
+      <c r="Q39" s="472">
         <v>-3.24</v>
       </c>
       <c r="R39" s="473">
         <v>-2.68</v>
       </c>
-      <c r="S39" s="469">
+      <c r="S39" s="475">
         <v>-2.27</v>
       </c>
-      <c r="T39" s="474">
-        <v>9.21</v>
+      <c r="T39" s="479">
+        <v>7.34</v>
       </c>
     </row>
   </sheetData>
